--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="今日總覽" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="歷史紀錄" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +437,37 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>股票名稱</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>收盤價</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>漲跌價</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>漲跌幅</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>年報酬率</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>殖利率</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>本益比</t>
         </is>
       </c>
     </row>
@@ -446,8 +477,890 @@
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>125</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>181.63%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2.28%</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>31.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.64%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-7.92%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>30.05</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>11.81%</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>46.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-1.6%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>82.09%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3.03%</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>15.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.59%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>13.24%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3.55%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>15.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-0.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>12.27%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3.69%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>18.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>18</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-1.37%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>164.71%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>99.84999999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>116.22%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1.36%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>29.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>108.42%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>37.09</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.95%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>138.09%</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>6.17%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>33.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-0.89%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>45.30%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>31.71</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>股票名稱</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>收盤價</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>漲跌價</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>漲跌幅</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>年報酬率</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>殖利率</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>本益比</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>125</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>181.63%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2.28%</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>31.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.64%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-7.92%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>30.05</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>11.81%</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>46.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-1.6%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>82.09%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3.03%</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>15.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.59%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>13.24%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3.55%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>15.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-0.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>12.27%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3.69%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>18.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>18</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-1.37%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>164.71%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>116.22%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1.36%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>29.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>108.42%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>37.09</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.95%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>138.09%</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>6.17%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>33.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-0.89%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>45.30%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>31.71</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>125</v>
+        <v>133.5</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5.49%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>181.63%</t>
+          <t>200.46%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>31.81</t>
+          <t>33.88</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-7.92%</t>
+          <t>-9.88%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30.05</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.05</v>
+        <v>0.95</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>3.16%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.81%</t>
+          <t>11.45%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>48.44</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27.75</v>
+        <v>27.45</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.45</v>
+        <v>-0.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.08%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>82.09%</t>
+          <t>77.39%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>15.95</t>
+          <t>15.78</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33.85</v>
+        <v>34.35</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13.24%</t>
+          <t>14.92%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.49%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>15.97</t>
+          <t>16.20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12.27%</t>
+          <t>11.58%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>19.8</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.25</v>
+        <v>1.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>164.71%</t>
+          <t>194.21%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>99.84999999999999</v>
+        <v>101.95</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4</v>
+        <v>2.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>116.22%</t>
+          <t>120.76%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>29.16</t>
+          <t>29.77</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>85.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3</v>
+        <v>1.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>108.42%</t>
+          <t>114.22%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.36%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.24</t>
+          <t>30.91</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37.09</v>
+        <v>38.49</v>
       </c>
       <c r="D11" t="n">
-        <v>0.35</v>
+        <v>1.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>3.77%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>138.09%</t>
+          <t>148.97%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6.17%</t>
+          <t>5.95%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>34.57</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.53</v>
+        <v>14.9</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.13</v>
+        <v>0.37</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.89%</t>
+          <t>2.55%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>45.30%</t>
+          <t>49.00%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>31.71</t>
+          <t>32.51</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -977,10 +977,8 @@
           <t>2.28%</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>31.81</t>
-        </is>
+      <c r="H2" t="n">
+        <v>31.81</v>
       </c>
     </row>
     <row r="3">
@@ -1015,11 +1013,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1053,10 +1047,8 @@
           <t>11.81%</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>46.95</t>
-        </is>
+      <c r="H4" t="n">
+        <v>46.95</v>
       </c>
     </row>
     <row r="5">
@@ -1091,10 +1083,8 @@
           <t>3.03%</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>15.95</t>
-        </is>
+      <c r="H5" t="n">
+        <v>15.95</v>
       </c>
     </row>
     <row r="6">
@@ -1129,10 +1119,8 @@
           <t>3.55%</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>15.97</t>
-        </is>
+      <c r="H6" t="n">
+        <v>15.97</v>
       </c>
     </row>
     <row r="7">
@@ -1150,7 +1138,7 @@
         <v>43.4</v>
       </c>
       <c r="D7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1167,10 +1155,8 @@
           <t>3.69%</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>18.39</t>
-        </is>
+      <c r="H7" t="n">
+        <v>18.39</v>
       </c>
     </row>
     <row r="8">
@@ -1205,11 +1191,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1243,10 +1225,8 @@
           <t>1.36%</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>29.16</t>
-        </is>
+      <c r="H9" t="n">
+        <v>29.16</v>
       </c>
     </row>
     <row r="10">
@@ -1281,10 +1261,8 @@
           <t>3.43%</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>30.24</t>
-        </is>
+      <c r="H10" t="n">
+        <v>30.24</v>
       </c>
     </row>
     <row r="11">
@@ -1319,10 +1297,8 @@
           <t>6.17%</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>33.31</t>
-        </is>
+      <c r="H11" t="n">
+        <v>33.31</v>
       </c>
     </row>
     <row r="12">
@@ -1357,9 +1333,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>31.71</t>
+      <c r="H12" t="n">
+        <v>31.71</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>6.8%</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>200.46%</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2.13%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>33.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-1.27%</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-9.88%</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>31</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3.16%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.92%</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>11.45%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>48.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-1.08%</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>77.39%</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>15.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>14.92%</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3.49%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>16.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.0%</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>11.58%</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>3.69%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>18.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>194.21%</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>120.76%</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>29.77</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2.21%</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>114.22%</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3.36%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>30.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3.77%</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>148.97%</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>5.95%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>34.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2.55%</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>49.00%</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>32.51</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>133.5</v>
+        <v>141.5</v>
       </c>
       <c r="D2" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>5.99%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>200.46%</t>
+          <t>213.82%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>33.88</t>
+          <t>35.91</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15.5</v>
+        <v>15.95</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2</v>
+        <v>0.45</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.27%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-9.88%</t>
+          <t>-2.74%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>31.3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.95</v>
+        <v>0.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.45%</t>
+          <t>11.34%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>48.91</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27.45</v>
+        <v>28.8</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3</v>
+        <v>1.35</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.08%</t>
+          <t>4.92%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>77.39%</t>
+          <t>86.12%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>2.92%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>15.78</t>
+          <t>16.55</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.35</v>
+        <v>34.65</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14.92%</t>
+          <t>14.28%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.20</t>
+          <t>16.34</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>43.4</v>
+        <v>44</v>
       </c>
       <c r="D7" t="n">
-        <v>-0</v>
+        <v>0.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>11.58%</t>
+          <t>12.15%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>3.64%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.64</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.8</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>6.06%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>194.21%</t>
+          <t>212.97%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>101.95</v>
+        <v>105.25</v>
       </c>
       <c r="D9" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>3.24%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>120.76%</t>
+          <t>127.91%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>30.74</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>87.8</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>114.22%</t>
+          <t>121.11%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.36%</t>
+          <t>3.27%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>31.80</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38.49</v>
+        <v>39.61</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.77%</t>
+          <t>2.91%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>148.97%</t>
+          <t>158.19%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.95%</t>
+          <t>5.78%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>34.57</t>
+          <t>35.58</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.9</v>
+        <v>15.38</v>
       </c>
       <c r="D12" t="n">
-        <v>0.37</v>
+        <v>0.48</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>3.22%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>53.80%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32.51</t>
+          <t>33.56</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1369,10 +1369,8 @@
           <t>2.13%</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>33.88</t>
-        </is>
+      <c r="H13" t="n">
+        <v>33.88</v>
       </c>
     </row>
     <row r="14">
@@ -1407,11 +1405,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1445,10 +1439,8 @@
           <t>11.45%</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>48.44</t>
-        </is>
+      <c r="H15" t="n">
+        <v>48.44</v>
       </c>
     </row>
     <row r="16">
@@ -1483,10 +1475,8 @@
           <t>3.07%</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>15.78</t>
-        </is>
+      <c r="H16" t="n">
+        <v>15.78</v>
       </c>
     </row>
     <row r="17">
@@ -1521,10 +1511,8 @@
           <t>3.49%</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>16.20</t>
-        </is>
+      <c r="H17" t="n">
+        <v>16.2</v>
       </c>
     </row>
     <row r="18">
@@ -1542,7 +1530,7 @@
         <v>43.4</v>
       </c>
       <c r="D18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1559,10 +1547,8 @@
           <t>3.69%</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>18.39</t>
-        </is>
+      <c r="H18" t="n">
+        <v>18.39</v>
       </c>
     </row>
     <row r="19">
@@ -1597,11 +1583,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1635,10 +1617,8 @@
           <t>1.33%</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>29.77</t>
-        </is>
+      <c r="H20" t="n">
+        <v>29.77</v>
       </c>
     </row>
     <row r="21">
@@ -1673,10 +1653,8 @@
           <t>3.36%</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>30.91</t>
-        </is>
+      <c r="H21" t="n">
+        <v>30.91</v>
       </c>
     </row>
     <row r="22">
@@ -1711,10 +1689,8 @@
           <t>5.95%</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>34.57</t>
-        </is>
+      <c r="H22" t="n">
+        <v>34.57</v>
       </c>
     </row>
     <row r="23">
@@ -1749,9 +1725,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>32.51</t>
+      <c r="H23" t="n">
+        <v>32.51</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>5.99%</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>213.82%</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2.01%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>35.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-2.74%</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0.97%</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>4.90%</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>11.34%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>48.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>4.92%</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>86.12%</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2.92%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>16.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>34.65</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>14.28%</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>3.46%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>16.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>44</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.38%</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>12.15%</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>3.64%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>18.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>21</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>6.06%</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>212.97%</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3.24%</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>127.91%</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1.29%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>30.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>121.11%</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>3.27%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>31.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>39.61</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2.91%</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>158.19%</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>5.78%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>35.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3.22%</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>53.80%</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>33.56</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>141.5</v>
+        <v>141</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>-0.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5.99%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>213.82%</t>
+          <t>212.71%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>35.91</t>
+          <t>35.88</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15.95</v>
+        <v>16.6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.45</v>
+        <v>0.65</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>4.08%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-2.74%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31.3</v>
+        <v>30.2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3</v>
+        <v>-1.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.34%</t>
+          <t>11.75%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>48.91</t>
+          <t>47.19</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.8</v>
+        <v>29.7</v>
       </c>
       <c r="D5" t="n">
-        <v>1.35</v>
+        <v>0.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.92%</t>
+          <t>3.13%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>86.12%</t>
+          <t>91.93%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>17.07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.65</v>
+        <v>35.2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14.28%</t>
+          <t>16.09%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.41%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>16.60</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>44</v>
+        <v>44.5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12.15%</t>
+          <t>13.42%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.64%</t>
+          <t>3.60%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>18.86</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2</v>
+        <v>-2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6.06%</t>
+          <t>-9.52%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>212.97%</t>
+          <t>183.16%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>105.25</v>
+        <v>105.9</v>
       </c>
       <c r="D9" t="n">
-        <v>3.3</v>
+        <v>0.65</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>127.91%</t>
+          <t>129.32%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>30.93</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>90.34999999999999</v>
+        <v>91.05</v>
       </c>
       <c r="D10" t="n">
-        <v>2.55</v>
+        <v>0.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>121.11%</t>
+          <t>122.82%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>3.24%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.80</t>
+          <t>32.05</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>39.61</v>
+        <v>39.91</v>
       </c>
       <c r="D11" t="n">
-        <v>1.12</v>
+        <v>0.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>158.19%</t>
+          <t>160.14%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.78%</t>
+          <t>5.74%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>35.58</t>
+          <t>35.84</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.38</v>
+        <v>15.51</v>
       </c>
       <c r="D12" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53.80%</t>
+          <t>55.10%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.56</t>
+          <t>33.84</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1761,10 +1761,8 @@
           <t>2.01%</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>35.91</t>
-        </is>
+      <c r="H24" t="n">
+        <v>35.91</v>
       </c>
     </row>
     <row r="25">
@@ -1799,11 +1797,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1837,10 +1831,8 @@
           <t>11.34%</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>48.91</t>
-        </is>
+      <c r="H26" t="n">
+        <v>48.91</v>
       </c>
     </row>
     <row r="27">
@@ -1875,10 +1867,8 @@
           <t>2.92%</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>16.55</t>
-        </is>
+      <c r="H27" t="n">
+        <v>16.55</v>
       </c>
     </row>
     <row r="28">
@@ -1913,10 +1903,8 @@
           <t>3.46%</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>16.34</t>
-        </is>
+      <c r="H28" t="n">
+        <v>16.34</v>
       </c>
     </row>
     <row r="29">
@@ -1951,10 +1939,8 @@
           <t>3.64%</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>18.64</t>
-        </is>
+      <c r="H29" t="n">
+        <v>18.64</v>
       </c>
     </row>
     <row r="30">
@@ -1989,11 +1975,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2027,10 +2009,8 @@
           <t>1.29%</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>30.74</t>
-        </is>
+      <c r="H31" t="n">
+        <v>30.74</v>
       </c>
     </row>
     <row r="32">
@@ -2065,10 +2045,8 @@
           <t>3.27%</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>31.80</t>
-        </is>
+      <c r="H32" t="n">
+        <v>31.8</v>
       </c>
     </row>
     <row r="33">
@@ -2103,10 +2081,8 @@
           <t>5.78%</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>35.58</t>
-        </is>
+      <c r="H33" t="n">
+        <v>35.58</v>
       </c>
     </row>
     <row r="34">
@@ -2141,9 +2117,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>33.56</t>
+      <c r="H34" t="n">
+        <v>33.56</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>141</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>212.71%</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2.02%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>35.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>4.08%</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-3.51%</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1.21%</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>11.75%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>47.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>3.13%</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>91.93%</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2.83%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>17.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.59%</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>16.09%</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>3.41%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>16.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>13.42%</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3.60%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>18.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>19</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-9.52%</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>183.16%</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>129.32%</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1.28%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>30.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>91.05</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0.77%</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>122.82%</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>3.24%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>32.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>39.91</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>160.14%</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>5.74%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>35.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>55.10%</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>33.84</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>212.71%</t>
+          <t>213.76%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>35.62</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.6</v>
+        <v>18.25</v>
       </c>
       <c r="D3" t="n">
-        <v>0.65</v>
+        <v>1.65</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.08%</t>
+          <t>9.94%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>10.94%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30.2</v>
+        <v>30.8</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.1</v>
+        <v>0.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-3.51%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>4.57%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.75%</t>
+          <t>11.52%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>47.19</t>
+          <t>48.12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29.7</v>
+        <v>30.2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>91.93%</t>
+          <t>96.96%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.79%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>17.36</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35.2</v>
+        <v>35.5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16.09%</t>
+          <t>16.90%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>16.75</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>44.5</v>
+        <v>45.1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>13.42%</t>
+          <t>15.38%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.60%</t>
+          <t>3.55%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>19.11</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>19.15</v>
       </c>
       <c r="D8" t="n">
-        <v>-2</v>
+        <v>0.15</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-9.52%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>183.16%</t>
+          <t>187.97%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>105.9</v>
+        <v>106</v>
       </c>
       <c r="D9" t="n">
-        <v>0.65</v>
+        <v>0.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.09%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>129.32%</t>
+          <t>129.53%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -771,14 +771,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>30.96</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>91.05</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>122.82%</t>
+          <t>123.73%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>32.17</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>39.91</v>
+        <v>40.12</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>160.14%</t>
+          <t>160.28%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.74%</t>
+          <t>5.71%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>35.84</t>
+          <t>36.03</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.51</v>
+        <v>15.55</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>55.10%</t>
+          <t>55.50%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.84</t>
+          <t>33.93</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2153,10 +2153,8 @@
           <t>2.02%</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>35.88</t>
-        </is>
+      <c r="H35" t="n">
+        <v>35.88</v>
       </c>
     </row>
     <row r="36">
@@ -2191,11 +2189,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2229,10 +2223,8 @@
           <t>11.75%</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>47.19</t>
-        </is>
+      <c r="H37" t="n">
+        <v>47.19</v>
       </c>
     </row>
     <row r="38">
@@ -2267,10 +2259,8 @@
           <t>2.83%</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>17.07</t>
-        </is>
+      <c r="H38" t="n">
+        <v>17.07</v>
       </c>
     </row>
     <row r="39">
@@ -2305,10 +2295,8 @@
           <t>3.41%</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>16.60</t>
-        </is>
+      <c r="H39" t="n">
+        <v>16.6</v>
       </c>
     </row>
     <row r="40">
@@ -2343,10 +2331,8 @@
           <t>3.60%</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
+      <c r="H40" t="n">
+        <v>18.86</v>
       </c>
     </row>
     <row r="41">
@@ -2381,11 +2367,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2419,10 +2401,8 @@
           <t>1.28%</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>30.93</t>
-        </is>
+      <c r="H42" t="n">
+        <v>30.93</v>
       </c>
     </row>
     <row r="43">
@@ -2457,10 +2437,8 @@
           <t>3.24%</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>32.05</t>
-        </is>
+      <c r="H43" t="n">
+        <v>32.05</v>
       </c>
     </row>
     <row r="44">
@@ -2495,10 +2473,8 @@
           <t>5.74%</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>35.84</t>
-        </is>
+      <c r="H44" t="n">
+        <v>35.84</v>
       </c>
     </row>
     <row r="45">
@@ -2533,9 +2509,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>33.84</t>
+      <c r="H45" t="n">
+        <v>33.84</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>140</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-0.71%</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>213.76%</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2.04%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>35.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>9.94%</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>10.94%</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.99%</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>4.57%</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>11.52%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>48.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.68%</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>96.96%</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2.79%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>17.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.85%</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>16.90%</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>3.38%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>16.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.35%</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>15.38%</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>3.55%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>19.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.79%</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>187.97%</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>106</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0.09%</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>129.53%</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1.28%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>30.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>123.73%</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>3.23%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>32.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>40.12</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0.53%</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>160.28%</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>5.71%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>36.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0.26%</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>55.50%</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>33.93</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>140</v>
+        <v>145.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-1</v>
+        <v>5.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>3.93%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>213.76%</t>
+          <t>220.69%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>35.62</t>
+          <t>37.02</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.25</v>
+        <v>20.05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.94%</t>
+          <t>9.86%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10.94%</t>
+          <t>21.52%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30.8</v>
+        <v>30.85</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6</v>
+        <v>0.05</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4.57%</t>
+          <t>4.74%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.52%</t>
+          <t>11.50%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>48.12</t>
+          <t>48.20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.2</v>
+        <v>30.75</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>96.96%</t>
+          <t>98.12%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.74%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.67</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16.90%</t>
+          <t>15.84%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.39%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>16.70</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>45.1</v>
+        <v>45.5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>15.38%</t>
+          <t>15.97%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.52%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>19.28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.15</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>0.15</v>
+        <v>-1.15</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>-6.01%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>187.97%</t>
+          <t>167.06%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>106</v>
+        <v>107.3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>129.53%</t>
+          <t>130.36%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>31.34</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>91.40000000000001</v>
+        <v>92.45</v>
       </c>
       <c r="D10" t="n">
-        <v>0.35</v>
+        <v>1.05</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>123.73%</t>
+          <t>125.19%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.19%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>32.54</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40.12</v>
+        <v>41.25</v>
       </c>
       <c r="D11" t="n">
-        <v>0.21</v>
+        <v>1.13</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>2.82%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>160.28%</t>
+          <t>166.51%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.71%</t>
+          <t>5.55%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>36.03</t>
+          <t>37.05</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.55</v>
+        <v>15.68</v>
       </c>
       <c r="D12" t="n">
-        <v>0.04</v>
+        <v>0.13</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>55.50%</t>
+          <t>56.80%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>34.22</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2545,10 +2545,8 @@
           <t>2.04%</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>35.62</t>
-        </is>
+      <c r="H46" t="n">
+        <v>35.62</v>
       </c>
     </row>
     <row r="47">
@@ -2583,11 +2581,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2621,10 +2615,8 @@
           <t>11.52%</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>48.12</t>
-        </is>
+      <c r="H48" t="n">
+        <v>48.12</v>
       </c>
     </row>
     <row r="49">
@@ -2659,10 +2651,8 @@
           <t>2.79%</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>17.36</t>
-        </is>
+      <c r="H49" t="n">
+        <v>17.36</v>
       </c>
     </row>
     <row r="50">
@@ -2697,10 +2687,8 @@
           <t>3.38%</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>16.75</t>
-        </is>
+      <c r="H50" t="n">
+        <v>16.75</v>
       </c>
     </row>
     <row r="51">
@@ -2735,10 +2723,8 @@
           <t>3.55%</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>19.11</t>
-        </is>
+      <c r="H51" t="n">
+        <v>19.11</v>
       </c>
     </row>
     <row r="52">
@@ -2773,11 +2759,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2811,10 +2793,8 @@
           <t>1.28%</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>30.96</t>
-        </is>
+      <c r="H53" t="n">
+        <v>30.96</v>
       </c>
     </row>
     <row r="54">
@@ -2849,10 +2829,8 @@
           <t>3.23%</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>32.17</t>
-        </is>
+      <c r="H54" t="n">
+        <v>32.17</v>
       </c>
     </row>
     <row r="55">
@@ -2887,10 +2865,8 @@
           <t>5.71%</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>36.03</t>
-        </is>
+      <c r="H55" t="n">
+        <v>36.03</v>
       </c>
     </row>
     <row r="56">
@@ -2925,9 +2901,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>33.93</t>
+      <c r="H56" t="n">
+        <v>33.93</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="D57" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>3.93%</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>220.69%</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1.96%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>37.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>9.86%</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>21.52%</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>4.74%</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>11.50%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>48.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.82%</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>98.12%</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2.74%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>17.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="D61" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-0.28%</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>15.84%</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>3.39%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>16.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0.89%</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>15.97%</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>3.52%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>19.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>18</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-6.01%</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>167.06%</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.23%</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>130.36%</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1.27%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>31.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.15%</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>125.19%</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>3.19%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>32.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2.82%</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>166.51%</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>5.55%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>37.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0.84%</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>56.80%</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>34.22</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -626,7 +626,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -664,7 +664,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -778,7 +778,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -854,7 +854,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2937,10 +2937,8 @@
           <t>1.96%</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>37.02</t>
-        </is>
+      <c r="H57" t="n">
+        <v>37.02</v>
       </c>
     </row>
     <row r="58">
@@ -2975,11 +2973,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3013,10 +3007,8 @@
           <t>11.50%</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>48.20</t>
-        </is>
+      <c r="H59" t="n">
+        <v>48.2</v>
       </c>
     </row>
     <row r="60">
@@ -3051,10 +3043,8 @@
           <t>2.74%</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>17.67</t>
-        </is>
+      <c r="H60" t="n">
+        <v>17.67</v>
       </c>
     </row>
     <row r="61">
@@ -3089,10 +3079,8 @@
           <t>3.39%</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>16.70</t>
-        </is>
+      <c r="H61" t="n">
+        <v>16.7</v>
       </c>
     </row>
     <row r="62">
@@ -3127,10 +3115,8 @@
           <t>3.52%</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>19.28</t>
-        </is>
+      <c r="H62" t="n">
+        <v>19.28</v>
       </c>
     </row>
     <row r="63">
@@ -3165,11 +3151,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3203,10 +3185,8 @@
           <t>1.27%</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>31.34</t>
-        </is>
+      <c r="H64" t="n">
+        <v>31.34</v>
       </c>
     </row>
     <row r="65">
@@ -3241,10 +3221,8 @@
           <t>3.19%</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>32.54</t>
-        </is>
+      <c r="H65" t="n">
+        <v>32.54</v>
       </c>
     </row>
     <row r="66">
@@ -3279,10 +3257,8 @@
           <t>5.55%</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>37.05</t>
-        </is>
+      <c r="H66" t="n">
+        <v>37.05</v>
       </c>
     </row>
     <row r="67">
@@ -3317,7 +3293,423 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H67" t="n">
+        <v>34.22</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="D68" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>3.93%</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>220.69%</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1.96%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>37.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>9.86%</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>21.52%</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>4.74%</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>11.50%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>48.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.82%</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>98.12%</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2.74%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>17.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="D72" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>-0.28%</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>15.84%</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>3.39%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>16.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0.89%</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>15.97%</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>3.52%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>19.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>18</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-6.01%</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>167.06%</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.23%</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>130.36%</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1.27%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>31.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1.15%</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>125.19%</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>3.19%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>32.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2.82%</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>166.51%</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>5.55%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>37.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0.84%</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>56.80%</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
         <is>
           <t>34.22</t>
         </is>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>145.5</v>
+        <v>160</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.93%</t>
+          <t>9.97%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>220.69%</t>
+          <t>262.40%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.78%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>37.02</t>
+          <t>40.61</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.05</v>
+        <v>18.95</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8</v>
+        <v>-1.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.86%</t>
+          <t>-5.49%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21.52%</t>
+          <t>23.05%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30.85</v>
+        <v>31.45</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05</v>
+        <v>0.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4.74%</t>
+          <t>11.56%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.50%</t>
+          <t>11.28%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>48.20</t>
+          <t>49.14</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.75</v>
+        <v>30.35</v>
       </c>
       <c r="D5" t="n">
-        <v>0.55</v>
+        <v>-0.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>98.12%</t>
+          <t>103.54%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.67</t>
+          <t>17.44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35.4</v>
+        <v>35.8</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1</v>
+        <v>0.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>15.84%</t>
+          <t>18.63%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.70</t>
+          <t>16.89</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>45.5</v>
+        <v>44.75</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4</v>
+        <v>-0.75</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>-1.65%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>15.97%</t>
+          <t>15.76%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.58%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>18.96</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>18.05</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.15</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-6.01%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>167.06%</t>
+          <t>174.73%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>107.3</v>
+        <v>111.15</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3</v>
+        <v>3.85</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>3.59%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>130.36%</t>
+          <t>143.38%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.34</t>
+          <t>32.46</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>92.45</v>
+        <v>95</v>
       </c>
       <c r="D10" t="n">
-        <v>1.05</v>
+        <v>2.55</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>2.76%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>125.19%</t>
+          <t>135.56%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>3.11%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>32.54</t>
+          <t>33.44</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>41.25</v>
+        <v>43.53</v>
       </c>
       <c r="D11" t="n">
-        <v>1.13</v>
+        <v>2.28</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>5.53%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>166.51%</t>
+          <t>186.63%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.55%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>39.10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.68</v>
+        <v>16.17</v>
       </c>
       <c r="D12" t="n">
-        <v>0.13</v>
+        <v>0.49</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>3.12%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>56.80%</t>
+          <t>61.70%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>34.22</t>
+          <t>35.28</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3329,10 +3329,8 @@
           <t>1.96%</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>37.02</t>
-        </is>
+      <c r="H68" t="n">
+        <v>37.02</v>
       </c>
     </row>
     <row r="69">
@@ -3367,11 +3365,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3405,10 +3399,8 @@
           <t>11.50%</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>48.20</t>
-        </is>
+      <c r="H70" t="n">
+        <v>48.2</v>
       </c>
     </row>
     <row r="71">
@@ -3443,10 +3435,8 @@
           <t>2.74%</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>17.67</t>
-        </is>
+      <c r="H71" t="n">
+        <v>17.67</v>
       </c>
     </row>
     <row r="72">
@@ -3481,10 +3471,8 @@
           <t>3.39%</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>16.70</t>
-        </is>
+      <c r="H72" t="n">
+        <v>16.7</v>
       </c>
     </row>
     <row r="73">
@@ -3519,10 +3507,8 @@
           <t>3.52%</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>19.28</t>
-        </is>
+      <c r="H73" t="n">
+        <v>19.28</v>
       </c>
     </row>
     <row r="74">
@@ -3557,11 +3543,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3595,10 +3577,8 @@
           <t>1.27%</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>31.34</t>
-        </is>
+      <c r="H75" t="n">
+        <v>31.34</v>
       </c>
     </row>
     <row r="76">
@@ -3633,10 +3613,8 @@
           <t>3.19%</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>32.54</t>
-        </is>
+      <c r="H76" t="n">
+        <v>32.54</v>
       </c>
     </row>
     <row r="77">
@@ -3671,10 +3649,8 @@
           <t>5.55%</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>37.05</t>
-        </is>
+      <c r="H77" t="n">
+        <v>37.05</v>
       </c>
     </row>
     <row r="78">
@@ -3709,9 +3685,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>34.22</t>
+      <c r="H78" t="n">
+        <v>34.22</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>160</v>
+      </c>
+      <c r="D79" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>9.97%</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>262.40%</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1.78%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>40.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-5.49%</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>23.05%</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1.94%</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>11.56%</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>11.28%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>49.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-1.3%</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>103.54%</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2.77%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>17.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1.13%</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>18.63%</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>3.35%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>16.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>44.75</v>
+      </c>
+      <c r="D84" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-1.65%</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>15.76%</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>3.58%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>18.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>174.73%</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>111.15</v>
+      </c>
+      <c r="D86" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>3.59%</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>143.38%</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>32.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>95</v>
+      </c>
+      <c r="D87" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2.76%</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>135.56%</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>3.11%</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>33.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>43.53</v>
+      </c>
+      <c r="D88" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>5.53%</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>186.63%</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>5.26%</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>39.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>3.12%</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>61.70%</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>35.28</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D2" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9.97%</t>
+          <t>6.25%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>262.40%</t>
+          <t>285.05%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>43.15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.95</v>
+        <v>18.35</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.1</v>
+        <v>-0.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-5.49%</t>
+          <t>-3.17%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.05%</t>
+          <t>19.16%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31.45</v>
+        <v>31.1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6</v>
+        <v>-0.35</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11.56%</t>
+          <t>10.32%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.28%</t>
+          <t>11.41%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.59</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.35</v>
+        <v>30.1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4</v>
+        <v>-0.25</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-0.82%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>103.54%</t>
+          <t>101.86%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.80%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>17.30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -638,11 +638,11 @@
         <v>35.8</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -664,7 +664,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>44.75</v>
+        <v>45.2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.75</v>
+        <v>0.45</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>1.01%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>15.76%</t>
+          <t>16.93%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>19.15</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18.05</v>
+        <v>17.45</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>-0.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>-3.32%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>174.73%</t>
+          <t>165.60%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>111.15</v>
+        <v>110.1</v>
       </c>
       <c r="D9" t="n">
-        <v>3.85</v>
+        <v>-1.05</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>143.38%</t>
+          <t>141.08%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.46</t>
+          <t>32.15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="D10" t="n">
-        <v>2.55</v>
+        <v>-1.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>135.56%</t>
+          <t>132.59%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.14%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>33.02</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>43.53</v>
+        <v>42.7</v>
       </c>
       <c r="D11" t="n">
-        <v>2.28</v>
+        <v>-0.83</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5.53%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>186.63%</t>
+          <t>181.16%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>5.36%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>39.10</t>
+          <t>38.35</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.17</v>
+        <v>15.97</v>
       </c>
       <c r="D12" t="n">
-        <v>0.49</v>
+        <v>-0.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>-1.24%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.70%</t>
+          <t>59.70%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>35.28</t>
+          <t>34.85</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3721,10 +3721,8 @@
           <t>1.78%</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>40.61</t>
-        </is>
+      <c r="H79" t="n">
+        <v>40.61</v>
       </c>
     </row>
     <row r="80">
@@ -3759,11 +3757,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3797,10 +3791,8 @@
           <t>11.28%</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>49.14</t>
-        </is>
+      <c r="H81" t="n">
+        <v>49.14</v>
       </c>
     </row>
     <row r="82">
@@ -3835,10 +3827,8 @@
           <t>2.77%</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>17.44</t>
-        </is>
+      <c r="H82" t="n">
+        <v>17.44</v>
       </c>
     </row>
     <row r="83">
@@ -3873,10 +3863,8 @@
           <t>3.35%</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>16.89</t>
-        </is>
+      <c r="H83" t="n">
+        <v>16.89</v>
       </c>
     </row>
     <row r="84">
@@ -3911,10 +3899,8 @@
           <t>3.58%</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>18.96</t>
-        </is>
+      <c r="H84" t="n">
+        <v>18.96</v>
       </c>
     </row>
     <row r="85">
@@ -3949,11 +3935,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3987,10 +3969,8 @@
           <t>1.22%</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>32.46</t>
-        </is>
+      <c r="H86" t="n">
+        <v>32.46</v>
       </c>
     </row>
     <row r="87">
@@ -4025,10 +4005,8 @@
           <t>3.11%</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>33.44</t>
-        </is>
+      <c r="H87" t="n">
+        <v>33.44</v>
       </c>
     </row>
     <row r="88">
@@ -4063,10 +4041,8 @@
           <t>5.26%</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>39.10</t>
-        </is>
+      <c r="H88" t="n">
+        <v>39.1</v>
       </c>
     </row>
     <row r="89">
@@ -4101,9 +4077,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>35.28</t>
+      <c r="H89" t="n">
+        <v>35.28</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>170</v>
+      </c>
+      <c r="D90" t="n">
+        <v>10</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>6.25%</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>285.05%</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1.68%</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>43.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-3.17%</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>19.16%</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-1.11%</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>10.32%</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>11.41%</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>48.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-0.82%</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>101.86%</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2.80%</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>17.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>18.63%</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>3.35%</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>16.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1.01%</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>16.93%</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>3.54%</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>19.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="D96" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-3.32%</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>165.60%</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-0.94%</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>141.08%</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>32.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="D98" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-1.26%</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>132.59%</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>3.14%</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>33.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="D99" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-1.91%</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>181.16%</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>5.36%</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>38.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>15.97</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-1.24%</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>59.70%</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>34.85</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6.25%</t>
+          <t>4.71%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>285.05%</t>
+          <t>292.50%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>45.18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.35</v>
+        <v>18.45</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.6</v>
+        <v>0.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-3.17%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.16%</t>
+          <t>9.17%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.35</v>
+        <v>-0.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.11%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.32%</t>
+          <t>6.07%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.41%</t>
+          <t>11.60%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>48.59</t>
+          <t>47.81</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.1</v>
+        <v>29.8</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.25</v>
+        <v>-0.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.82%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>101.86%</t>
+          <t>99.85%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.82%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.30</t>
+          <t>17.13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35.8</v>
+        <v>35</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-2.23%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.63%</t>
+          <t>14.89%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>16.51</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>45.2</v>
+        <v>44.55</v>
       </c>
       <c r="D7" t="n">
-        <v>0.45</v>
+        <v>-0.65</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16.93%</t>
+          <t>14.11%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>3.59%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>18.88</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.45</v>
+        <v>17.8</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6</v>
+        <v>0.35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-3.32%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>165.60%</t>
+          <t>165.67%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>110.1</v>
+        <v>107.15</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.05</v>
+        <v>-2.95</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>141.08%</t>
+          <t>130.42%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>31.29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>93.8</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2</v>
+        <v>-1.95</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-1.26%</t>
+          <t>-2.08%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>132.59%</t>
+          <t>123.63%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>33.02</t>
+          <t>32.33</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>42.7</v>
+        <v>42.15</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.83</v>
+        <v>-0.55</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>181.16%</t>
+          <t>173.12%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.36%</t>
+          <t>5.43%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>37.86</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.97</v>
+        <v>15.56</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2</v>
+        <v>-0.41</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-2.57%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>59.70%</t>
+          <t>55.60%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>33.95</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4113,10 +4113,8 @@
           <t>1.68%</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>43.15</t>
-        </is>
+      <c r="H90" t="n">
+        <v>43.15</v>
       </c>
     </row>
     <row r="91">
@@ -4151,11 +4149,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4189,10 +4183,8 @@
           <t>11.41%</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>48.59</t>
-        </is>
+      <c r="H92" t="n">
+        <v>48.59</v>
       </c>
     </row>
     <row r="93">
@@ -4227,10 +4219,8 @@
           <t>2.80%</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>17.30</t>
-        </is>
+      <c r="H93" t="n">
+        <v>17.3</v>
       </c>
     </row>
     <row r="94">
@@ -4265,10 +4255,8 @@
           <t>3.35%</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>16.89</t>
-        </is>
+      <c r="H94" t="n">
+        <v>16.89</v>
       </c>
     </row>
     <row r="95">
@@ -4303,10 +4291,8 @@
           <t>3.54%</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>19.15</t>
-        </is>
+      <c r="H95" t="n">
+        <v>19.15</v>
       </c>
     </row>
     <row r="96">
@@ -4341,11 +4327,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4379,10 +4361,8 @@
           <t>1.24%</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>32.15</t>
-        </is>
+      <c r="H97" t="n">
+        <v>32.15</v>
       </c>
     </row>
     <row r="98">
@@ -4417,10 +4397,8 @@
           <t>3.14%</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>33.02</t>
-        </is>
+      <c r="H98" t="n">
+        <v>33.02</v>
       </c>
     </row>
     <row r="99">
@@ -4455,10 +4433,8 @@
           <t>5.36%</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>38.35</t>
-        </is>
+      <c r="H99" t="n">
+        <v>38.35</v>
       </c>
     </row>
     <row r="100">
@@ -4493,9 +4469,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>34.85</t>
+      <c r="H100" t="n">
+        <v>34.85</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>178</v>
+      </c>
+      <c r="D101" t="n">
+        <v>8</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>4.71%</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>292.50%</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>45.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>9.17%</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-1.61%</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>6.07%</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>11.60%</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>47.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-1.0%</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>99.85%</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2.82%</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>17.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>35</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>-2.23%</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>14.89%</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>16.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>44.55</v>
+      </c>
+      <c r="D106" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>-1.44%</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>14.11%</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>3.59%</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>18.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2.01%</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>165.67%</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="D108" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>-2.68%</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>130.42%</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>1.27%</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>31.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>91.84999999999999</v>
+      </c>
+      <c r="D109" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>-2.08%</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>123.63%</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>3.21%</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>32.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>42.15</v>
+      </c>
+      <c r="D110" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>-1.29%</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>173.12%</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>5.43%</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>37.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="D111" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-2.57%</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>55.60%</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>33.95</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,19 +483,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>178</v>
+        <v>178.5</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4.71%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>292.50%</t>
+          <t>307.53%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -505,14 +505,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>45.18</t>
+          <t>45.42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.45</v>
+        <v>18.1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1</v>
+        <v>-0.35</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.17%</t>
+          <t>6.47%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>6.07%</t>
+          <t>6.33%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.60%</t>
+          <t>11.64%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>47.81</t>
+          <t>47.66</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29.8</v>
+        <v>30.5</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3</v>
+        <v>0.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>2.35%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>99.85%</t>
+          <t>102.00%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.76%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>17.53</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35</v>
+        <v>35.45</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8</v>
+        <v>0.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-2.23%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14.89%</t>
+          <t>14.92%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.39%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.72</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>44.55</v>
+        <v>46.65</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.65</v>
+        <v>2.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>4.71%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14.11%</t>
+          <t>18.32%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>19.77</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.8</v>
+        <v>17.25</v>
       </c>
       <c r="D8" t="n">
-        <v>0.35</v>
+        <v>-0.55</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>165.67%</t>
+          <t>160.97%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>107.15</v>
+        <v>107.2</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.95</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-2.68%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>130.42%</t>
+          <t>127.23%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -771,14 +771,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>31.31</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>91.84999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.95</v>
+        <v>0.35</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-2.08%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>123.63%</t>
+          <t>122.57%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.20%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>32.33</t>
+          <t>32.45</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>42.15</v>
+        <v>42.36</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.55</v>
+        <v>0.21</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>173.12%</t>
+          <t>171.76%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>5.41%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>37.86</t>
+          <t>38.05</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.56</v>
+        <v>15.59</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.41</v>
+        <v>0.03</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-2.57%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>55.60%</t>
+          <t>55.90%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>34.02</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H111"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4505,10 +4505,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>45.18</t>
-        </is>
+      <c r="H101" t="n">
+        <v>45.18</v>
       </c>
     </row>
     <row r="102">
@@ -4543,11 +4541,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4581,10 +4575,8 @@
           <t>11.60%</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>47.81</t>
-        </is>
+      <c r="H103" t="n">
+        <v>47.81</v>
       </c>
     </row>
     <row r="104">
@@ -4619,10 +4611,8 @@
           <t>2.82%</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>17.13</t>
-        </is>
+      <c r="H104" t="n">
+        <v>17.13</v>
       </c>
     </row>
     <row r="105">
@@ -4657,10 +4647,8 @@
           <t>3.43%</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>16.51</t>
-        </is>
+      <c r="H105" t="n">
+        <v>16.51</v>
       </c>
     </row>
     <row r="106">
@@ -4695,10 +4683,8 @@
           <t>3.59%</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>18.88</t>
-        </is>
+      <c r="H106" t="n">
+        <v>18.88</v>
       </c>
     </row>
     <row r="107">
@@ -4733,11 +4719,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4771,10 +4753,8 @@
           <t>1.27%</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>31.29</t>
-        </is>
+      <c r="H108" t="n">
+        <v>31.29</v>
       </c>
     </row>
     <row r="109">
@@ -4809,10 +4789,8 @@
           <t>3.21%</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>32.33</t>
-        </is>
+      <c r="H109" t="n">
+        <v>32.33</v>
       </c>
     </row>
     <row r="110">
@@ -4847,10 +4825,8 @@
           <t>5.43%</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>37.86</t>
-        </is>
+      <c r="H110" t="n">
+        <v>37.86</v>
       </c>
     </row>
     <row r="111">
@@ -4885,9 +4861,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>33.95</t>
+      <c r="H111" t="n">
+        <v>33.95</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>307.53%</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>45.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="D113" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-1.9%</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>6.47%</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="D114" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-0.33%</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>6.33%</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>11.64%</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>47.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2.35%</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>102.00%</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2.76%</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>17.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1.29%</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>14.92%</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>3.39%</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>16.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="D117" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>4.71%</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>18.32%</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>19.77</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="D118" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-3.09%</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>160.97%</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>127.23%</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>1.27%</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>31.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>122.57%</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>3.20%</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>32.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>42.36</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>171.76%</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>5.41%</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>38.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>55.90%</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>34.02</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,19 +483,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>178.5</v>
+        <v>164</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>-14.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>-8.12%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>307.53%</t>
+          <t>279.19%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -505,14 +505,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>41.62</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.1</v>
+        <v>17.15</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.35</v>
+        <v>-0.95</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-5.25%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>6.47%</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30.5</v>
+        <v>29.3</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1</v>
+        <v>-1.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>-3.93%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>6.33%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.64%</t>
+          <t>12.11%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>47.66</t>
+          <t>45.78</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.5</v>
+        <v>29.9</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7</v>
+        <v>-0.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>-1.97%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>102.00%</t>
+          <t>94.40%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.81%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35.45</v>
+        <v>34.55</v>
       </c>
       <c r="D6" t="n">
-        <v>0.45</v>
+        <v>-0.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>-2.54%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14.92%</t>
+          <t>11.66%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>3.47%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.72</t>
+          <t>16.30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.65</v>
+        <v>46.15</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1</v>
+        <v>-0.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4.71%</t>
+          <t>-1.07%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.32%</t>
+          <t>17.05%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.47%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.77</t>
+          <t>19.56</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.25</v>
+        <v>16.5</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.55</v>
+        <v>-0.75</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-4.35%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>160.97%</t>
+          <t>150.00%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>107.2</v>
+        <v>103.1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>-4.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>-3.82%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>127.23%</t>
+          <t>118.27%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.31</t>
+          <t>30.11</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>92.2</v>
+        <v>88.05</v>
       </c>
       <c r="D10" t="n">
-        <v>0.35</v>
+        <v>-4.15</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>122.57%</t>
+          <t>112.41%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>30.99</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>42.36</v>
+        <v>39.81</v>
       </c>
       <c r="D11" t="n">
-        <v>0.21</v>
+        <v>-2.55</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-6.02%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>171.76%</t>
+          <t>155.55%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.41%</t>
+          <t>5.75%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>35.75</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.59</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03</v>
+        <v>-0.59</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>-3.78%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>55.90%</t>
+          <t>50.00%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>34.02</t>
+          <t>32.73</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H122"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4897,10 +4897,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>45.42</t>
-        </is>
+      <c r="H112" t="n">
+        <v>45.42</v>
       </c>
     </row>
     <row r="113">
@@ -4935,11 +4933,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4973,10 +4967,8 @@
           <t>11.64%</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>47.66</t>
-        </is>
+      <c r="H114" t="n">
+        <v>47.66</v>
       </c>
     </row>
     <row r="115">
@@ -5011,10 +5003,8 @@
           <t>2.76%</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>17.53</t>
-        </is>
+      <c r="H115" t="n">
+        <v>17.53</v>
       </c>
     </row>
     <row r="116">
@@ -5049,10 +5039,8 @@
           <t>3.39%</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>16.72</t>
-        </is>
+      <c r="H116" t="n">
+        <v>16.72</v>
       </c>
     </row>
     <row r="117">
@@ -5087,10 +5075,8 @@
           <t>3.43%</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>19.77</t>
-        </is>
+      <c r="H117" t="n">
+        <v>19.77</v>
       </c>
     </row>
     <row r="118">
@@ -5125,11 +5111,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5163,10 +5145,8 @@
           <t>1.27%</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>31.31</t>
-        </is>
+      <c r="H119" t="n">
+        <v>31.31</v>
       </c>
     </row>
     <row r="120">
@@ -5201,10 +5181,8 @@
           <t>3.20%</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>32.45</t>
-        </is>
+      <c r="H120" t="n">
+        <v>32.45</v>
       </c>
     </row>
     <row r="121">
@@ -5239,10 +5217,8 @@
           <t>5.41%</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>38.05</t>
-        </is>
+      <c r="H121" t="n">
+        <v>38.05</v>
       </c>
     </row>
     <row r="122">
@@ -5277,9 +5253,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>34.02</t>
+      <c r="H122" t="n">
+        <v>34.02</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>164</v>
+      </c>
+      <c r="D123" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-8.12%</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>279.19%</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>41.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="D124" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>-5.25%</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>0.59%</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-3.93%</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>1.56%</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>12.11%</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>45.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>94.40%</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2.81%</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>17.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>34.55</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-2.54%</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>11.66%</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>3.47%</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>16.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>-1.07%</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>17.05%</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>3.47%</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>19.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-4.35%</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>150.00%</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-3.82%</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>118.27%</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>1.32%</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>30.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-4.15</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>-4.5%</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>112.41%</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>3.35%</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>30.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>39.81</v>
+      </c>
+      <c r="D132" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-6.02%</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>155.55%</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>5.75%</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>35.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>15</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-3.78%</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>50.00%</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>32.73</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,16 +486,16 @@
         <v>164</v>
       </c>
       <c r="D2" t="n">
-        <v>-14.5</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-8.12%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>279.19%</t>
+          <t>271.04%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.15</v>
+        <v>17.3</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.95</v>
+        <v>0.15</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-5.25%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.3</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.2</v>
+        <v>1.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-3.93%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>8.28%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>12.11%</t>
+          <t>11.45%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>45.78</t>
+          <t>48.44</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29.9</v>
+        <v>29.65</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6</v>
+        <v>-0.25</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>94.40%</t>
+          <t>100.31%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.55</v>
+        <v>34.5</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9</v>
+        <v>-0.05</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-2.54%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11.66%</t>
+          <t>9.97%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>3.48%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.30</t>
+          <t>16.27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.15</v>
+        <v>46.2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.07%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.05%</t>
+          <t>16.90%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.58</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.5</v>
+        <v>16.8</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.75</v>
+        <v>0.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-4.35%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>150.00%</t>
+          <t>158.06%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>103.1</v>
+        <v>104.45</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1</v>
+        <v>1.35</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-3.82%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>118.27%</t>
+          <t>120.58%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>30.50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>88.05</v>
+        <v>89.25</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.15</v>
+        <v>1.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>112.41%</t>
+          <t>114.76%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.31%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>31.42</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>39.81</v>
+        <v>40.15</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.55</v>
+        <v>0.34</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-6.02%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>155.55%</t>
+          <t>157.73%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.75%</t>
+          <t>5.70%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.06</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>15.05</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.59</v>
+        <v>0.05</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-3.78%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50.00%</t>
+          <t>50.50%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32.73</t>
+          <t>32.84</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5289,10 +5289,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>41.62</t>
-        </is>
+      <c r="H123" t="n">
+        <v>41.62</v>
       </c>
     </row>
     <row r="124">
@@ -5327,11 +5325,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5365,10 +5359,8 @@
           <t>12.11%</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>45.78</t>
-        </is>
+      <c r="H125" t="n">
+        <v>45.78</v>
       </c>
     </row>
     <row r="126">
@@ -5403,10 +5395,8 @@
           <t>2.81%</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>17.18</t>
-        </is>
+      <c r="H126" t="n">
+        <v>17.18</v>
       </c>
     </row>
     <row r="127">
@@ -5441,10 +5431,8 @@
           <t>3.47%</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>16.30</t>
-        </is>
+      <c r="H127" t="n">
+        <v>16.3</v>
       </c>
     </row>
     <row r="128">
@@ -5479,10 +5467,8 @@
           <t>3.47%</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>19.56</t>
-        </is>
+      <c r="H128" t="n">
+        <v>19.56</v>
       </c>
     </row>
     <row r="129">
@@ -5517,11 +5503,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5555,10 +5537,8 @@
           <t>1.32%</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>30.11</t>
-        </is>
+      <c r="H130" t="n">
+        <v>30.11</v>
       </c>
     </row>
     <row r="131">
@@ -5593,10 +5573,8 @@
           <t>3.35%</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>30.99</t>
-        </is>
+      <c r="H131" t="n">
+        <v>30.99</v>
       </c>
     </row>
     <row r="132">
@@ -5631,10 +5609,8 @@
           <t>5.75%</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>35.75</t>
-        </is>
+      <c r="H132" t="n">
+        <v>35.75</v>
       </c>
     </row>
     <row r="133">
@@ -5669,9 +5645,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>32.73</t>
+      <c r="H133" t="n">
+        <v>32.73</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>164</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>271.04%</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>41.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>31</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>8.28%</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>11.45%</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>48.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>29.65</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-0.84%</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>100.31%</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2.84%</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>17.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="D138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-0.14%</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>9.97%</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>3.48%</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>16.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>0.11%</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>16.90%</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>3.46%</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>19.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>1.82%</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>158.06%</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>1.31%</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>120.58%</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>1.30%</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>30.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>1.36%</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>114.76%</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>3.31%</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>31.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>0.85%</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>157.73%</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>5.70%</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>36.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>50.50%</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>32.84</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,19 +483,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>164</v>
+        <v>164.5</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>271.04%</t>
+          <t>272.17%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -505,14 +505,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>41.62</t>
+          <t>41.75</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.3</v>
+        <v>18.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>5.78%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>7.33%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>34.1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8.28%</t>
+          <t>19.11%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.45%</t>
+          <t>10.41%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>53.28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29.65</v>
+        <v>28.7</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.25</v>
+        <v>0.05</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>100.31%</t>
+          <t>100.66%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>3.48%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>16.49</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.5</v>
+        <v>34.45</v>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
@@ -647,7 +647,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.97%</t>
+          <t>9.81%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,14 +657,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.27</t>
+          <t>16.25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16.90%</t>
+          <t>16.64%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.47%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.58</t>
+          <t>19.53</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>158.06%</t>
+          <t>167.28%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>104.45</v>
+        <v>107.8</v>
       </c>
       <c r="D9" t="n">
-        <v>1.35</v>
+        <v>3.35</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>120.58%</t>
+          <t>127.65%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30.50</t>
+          <t>31.48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>89.25</v>
+        <v>92.05</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>3.14%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>114.76%</t>
+          <t>121.50%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>3.20%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>32.40</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40.15</v>
+        <v>41.75</v>
       </c>
       <c r="D11" t="n">
-        <v>0.34</v>
+        <v>1.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>3.99%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>157.73%</t>
+          <t>168.00%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.70%</t>
+          <t>5.49%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>37.50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.05</v>
+        <v>15.65</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05</v>
+        <v>0.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>3.99%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50.50%</t>
+          <t>56.50%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>34.15</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:H155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5681,10 +5681,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>41.62</t>
-        </is>
+      <c r="H134" t="n">
+        <v>41.62</v>
       </c>
     </row>
     <row r="135">
@@ -5719,11 +5717,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5757,10 +5751,8 @@
           <t>11.45%</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>48.44</t>
-        </is>
+      <c r="H136" t="n">
+        <v>48.44</v>
       </c>
     </row>
     <row r="137">
@@ -5795,10 +5787,8 @@
           <t>2.84%</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
+      <c r="H137" t="n">
+        <v>17.04</v>
       </c>
     </row>
     <row r="138">
@@ -5833,10 +5823,8 @@
           <t>3.48%</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>16.27</t>
-        </is>
+      <c r="H138" t="n">
+        <v>16.27</v>
       </c>
     </row>
     <row r="139">
@@ -5871,10 +5859,8 @@
           <t>3.46%</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>19.58</t>
-        </is>
+      <c r="H139" t="n">
+        <v>19.58</v>
       </c>
     </row>
     <row r="140">
@@ -5909,11 +5895,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5947,10 +5929,8 @@
           <t>1.30%</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>30.50</t>
-        </is>
+      <c r="H141" t="n">
+        <v>30.5</v>
       </c>
     </row>
     <row r="142">
@@ -5985,10 +5965,8 @@
           <t>3.31%</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>31.42</t>
-        </is>
+      <c r="H142" t="n">
+        <v>31.42</v>
       </c>
     </row>
     <row r="143">
@@ -6023,10 +6001,8 @@
           <t>5.70%</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>36.06</t>
-        </is>
+      <c r="H143" t="n">
+        <v>36.06</v>
       </c>
     </row>
     <row r="144">
@@ -6061,9 +6037,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>32.84</t>
+      <c r="H144" t="n">
+        <v>32.84</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>272.17%</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>41.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>5.78%</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>7.33%</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="D147" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>19.11%</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>10.41%</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>53.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>100.66%</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>3.48%</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>16.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="D149" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>-0.14%</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>9.81%</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>3.48%</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>16.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="D150" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>-0.22%</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>16.64%</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>3.47%</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>19.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>3.57%</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>167.28%</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="D152" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>3.21%</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>127.65%</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>31.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>92.05</v>
+      </c>
+      <c r="D153" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>3.14%</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>121.50%</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>3.20%</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>32.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>3.99%</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>168.00%</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>37.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>3.99%</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>56.50%</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>34.15</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,19 +483,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>164.5</v>
+        <v>169</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.74%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>272.17%</t>
+          <t>284.53%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -505,14 +505,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>42.78</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.3</v>
+        <v>17.5</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>-0.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5.78%</t>
+          <t>-4.37%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>7.33%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34.1</v>
+        <v>32.35</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1</v>
+        <v>-1.75</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>-5.13%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.11%</t>
+          <t>12.56%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.41%</t>
+          <t>10.97%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>53.28</t>
+          <t>50.55</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.7</v>
+        <v>28.3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05</v>
+        <v>-0.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>100.66%</t>
+          <t>92.71%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.53%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>16.49</t>
+          <t>16.26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.45</v>
+        <v>32.9</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.05</v>
+        <v>-0.15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.81%</t>
+          <t>8.65%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>7.90%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>15.52</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.1</v>
+        <v>46.15</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16.64%</t>
+          <t>15.36%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -695,14 +695,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>19.56</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.4</v>
+        <v>16.8</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6</v>
+        <v>-0.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>167.28%</t>
+          <t>153.39%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>107.8</v>
+        <v>109.35</v>
       </c>
       <c r="D9" t="n">
-        <v>3.35</v>
+        <v>1.55</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>127.65%</t>
+          <t>129.59%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>31.93</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>92.05</v>
+        <v>93</v>
       </c>
       <c r="D10" t="n">
-        <v>2.8</v>
+        <v>0.95</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>121.50%</t>
+          <t>122.61%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>32.40</t>
+          <t>32.74</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>41.75</v>
+        <v>42.48</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6</v>
+        <v>0.73</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>168.00%</t>
+          <t>173.01%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.49%</t>
+          <t>5.39%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>37.50</t>
+          <t>38.15</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.65</v>
+        <v>15.83</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6</v>
+        <v>0.18</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>56.50%</t>
+          <t>58.30%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>34.54</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H155"/>
+  <dimension ref="A1:H166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6073,10 +6073,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>41.75</t>
-        </is>
+      <c r="H145" t="n">
+        <v>41.75</v>
       </c>
     </row>
     <row r="146">
@@ -6111,11 +6109,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6149,10 +6143,8 @@
           <t>10.41%</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>53.28</t>
-        </is>
+      <c r="H147" t="n">
+        <v>53.28</v>
       </c>
     </row>
     <row r="148">
@@ -6187,10 +6179,8 @@
           <t>3.48%</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>16.49</t>
-        </is>
+      <c r="H148" t="n">
+        <v>16.49</v>
       </c>
     </row>
     <row r="149">
@@ -6225,10 +6215,8 @@
           <t>3.48%</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>16.25</t>
-        </is>
+      <c r="H149" t="n">
+        <v>16.25</v>
       </c>
     </row>
     <row r="150">
@@ -6263,10 +6251,8 @@
           <t>3.47%</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>19.53</t>
-        </is>
+      <c r="H150" t="n">
+        <v>19.53</v>
       </c>
     </row>
     <row r="151">
@@ -6301,11 +6287,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6339,10 +6321,8 @@
           <t>1.26%</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>31.48</t>
-        </is>
+      <c r="H152" t="n">
+        <v>31.48</v>
       </c>
     </row>
     <row r="153">
@@ -6377,10 +6357,8 @@
           <t>3.20%</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>32.40</t>
-        </is>
+      <c r="H153" t="n">
+        <v>32.4</v>
       </c>
     </row>
     <row r="154">
@@ -6415,10 +6393,8 @@
           <t>5.49%</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>37.50</t>
-        </is>
+      <c r="H154" t="n">
+        <v>37.5</v>
       </c>
     </row>
     <row r="155">
@@ -6453,9 +6429,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>34.15</t>
+      <c r="H155" t="n">
+        <v>34.15</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>169</v>
+      </c>
+      <c r="D156" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2.74%</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>284.53%</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>42.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D157" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>-4.37%</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>0.86%</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="D158" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>-5.13%</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>12.56%</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>10.97%</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>50.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="D159" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>-1.39%</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>92.71%</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>3.53%</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>16.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="D160" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>-0.45%</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>8.65%</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>7.90%</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>15.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>0.11%</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>15.36%</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>3.47%</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>19.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="D162" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>-3.45%</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>153.39%</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>1.44%</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>129.59%</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>31.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>93</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>1.03%</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>122.61%</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>32.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>42.48</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>1.75%</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>173.01%</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>5.39%</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>38.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>1.15%</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>58.30%</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>34.54</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,19 +483,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>169</v>
+        <v>165.5</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5</v>
+        <v>-3.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>284.53%</t>
+          <t>272.33%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -505,14 +505,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>42.78</t>
+          <t>42.01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.5</v>
+        <v>18.2</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-4.37%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32.35</v>
+        <v>31.9</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.75</v>
+        <v>-0.45</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-5.13%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.56%</t>
+          <t>10.15%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.97%</t>
+          <t>11.12%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>50.55</t>
+          <t>49.84</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.3</v>
+        <v>27.9</v>
       </c>
       <c r="D5" t="n">
         <v>-0.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.39%</t>
+          <t>-1.41%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>92.71%</t>
+          <t>95.07%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>3.58%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.03</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32.9</v>
+        <v>33.7</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.15</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>2.43%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>8.65%</t>
+          <t>11.46%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.90%</t>
+          <t>7.72%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>15.90</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.15</v>
+        <v>46</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>-0.15</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>15.36%</t>
+          <t>14.44%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>3.48%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.8</v>
+        <v>17.05</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6</v>
+        <v>0.25</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>153.39%</t>
+          <t>155.24%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>109.35</v>
+        <v>108.8</v>
       </c>
       <c r="D9" t="n">
-        <v>1.55</v>
+        <v>-0.89</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>129.59%</t>
+          <t>128.39%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.93</t>
+          <t>31.77</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>93</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.95</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>-0.74%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>122.61%</t>
+          <t>121.59%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.18%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>32.68</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>42.48</v>
+        <v>42.83</v>
       </c>
       <c r="D11" t="n">
-        <v>0.73</v>
+        <v>0.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>173.01%</t>
+          <t>173.50%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.39%</t>
+          <t>5.35%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.47</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.83</v>
+        <v>15.78</v>
       </c>
       <c r="D12" t="n">
-        <v>0.18</v>
+        <v>-0.09</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>-0.57%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>58.30%</t>
+          <t>57.80%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.43</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H166"/>
+  <dimension ref="A1:H177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6465,10 +6465,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>42.78</t>
-        </is>
+      <c r="H156" t="n">
+        <v>42.78</v>
       </c>
     </row>
     <row r="157">
@@ -6503,11 +6501,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6541,10 +6535,8 @@
           <t>10.97%</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>50.55</t>
-        </is>
+      <c r="H158" t="n">
+        <v>50.55</v>
       </c>
     </row>
     <row r="159">
@@ -6579,10 +6571,8 @@
           <t>3.53%</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>16.26</t>
-        </is>
+      <c r="H159" t="n">
+        <v>16.26</v>
       </c>
     </row>
     <row r="160">
@@ -6617,10 +6607,8 @@
           <t>7.90%</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>15.52</t>
-        </is>
+      <c r="H160" t="n">
+        <v>15.52</v>
       </c>
     </row>
     <row r="161">
@@ -6655,10 +6643,8 @@
           <t>3.47%</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>19.56</t>
-        </is>
+      <c r="H161" t="n">
+        <v>19.56</v>
       </c>
     </row>
     <row r="162">
@@ -6693,11 +6679,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6731,10 +6713,8 @@
           <t>1.24%</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>31.93</t>
-        </is>
+      <c r="H163" t="n">
+        <v>31.93</v>
       </c>
     </row>
     <row r="164">
@@ -6769,10 +6749,8 @@
           <t>3.17%</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>32.74</t>
-        </is>
+      <c r="H164" t="n">
+        <v>32.74</v>
       </c>
     </row>
     <row r="165">
@@ -6807,10 +6785,8 @@
           <t>5.39%</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>38.15</t>
-        </is>
+      <c r="H165" t="n">
+        <v>38.15</v>
       </c>
     </row>
     <row r="166">
@@ -6845,9 +6821,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>34.54</t>
+      <c r="H166" t="n">
+        <v>34.54</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="D167" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>-2.07%</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>272.33%</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>42.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>1.68%</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="D169" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>-1.39%</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>10.15%</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>11.12%</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>49.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="D170" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>-1.41%</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>95.07%</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>3.58%</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>16.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>2.43%</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>11.46%</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>7.72%</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>15.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>46</v>
+      </c>
+      <c r="D172" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>-0.33%</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>14.44%</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>3.48%</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>19.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>1.49%</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>155.24%</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="D174" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>-0.81%</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>128.39%</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>1.25%</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>31.77</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>92.84999999999999</v>
+      </c>
+      <c r="D175" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-0.74%</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>121.59%</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>3.18%</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>32.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>42.83</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0.94%</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>173.50%</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>5.35%</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>38.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="D177" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>-0.57%</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>57.80%</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>34.43</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,19 +483,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>165.5</v>
+        <v>170.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.5</v>
+        <v>5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>3.02%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>272.33%</t>
+          <t>284.01%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -505,14 +505,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>43.27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.2</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>9.89%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>11.73%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31.9</v>
+        <v>32.2</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.45</v>
+        <v>0.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.39%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.15%</t>
+          <t>9.32%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.12%</t>
+          <t>11.02%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>50.31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27.9</v>
+        <v>28.45</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4</v>
+        <v>0.55</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.41%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>95.07%</t>
+          <t>96.29%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>3.51%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>16.35</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -638,16 +638,16 @@
         <v>33.7</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>-0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11.46%</t>
+          <t>10.96%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -664,7 +664,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14.44%</t>
+          <t>13.33%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.52%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -714,16 +714,16 @@
         <v>17.05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>155.24%</t>
+          <t>149.63%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>108.8</v>
+        <v>108.35</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.89</v>
+        <v>-0.45</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>128.39%</t>
+          <t>124.36%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.77</t>
+          <t>31.64</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,19 +787,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>92.84999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.15</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.74%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>121.59%</t>
+          <t>119.14%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -809,14 +809,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>32.68</t>
+          <t>32.63</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>42.83</v>
+        <v>42.52</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4</v>
+        <v>-0.31</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>-0.72%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>173.50%</t>
+          <t>167.94%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.35%</t>
+          <t>5.39%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>38.19</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.78</v>
+        <v>15.75</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.09</v>
+        <v>-0.03</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>57.80%</t>
+          <t>57.50%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.37</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6857,10 +6857,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>42.01</t>
-        </is>
+      <c r="H167" t="n">
+        <v>42.01</v>
       </c>
     </row>
     <row r="168">
@@ -6895,11 +6893,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6933,10 +6927,8 @@
           <t>11.12%</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>49.84</t>
-        </is>
+      <c r="H169" t="n">
+        <v>49.84</v>
       </c>
     </row>
     <row r="170">
@@ -6971,10 +6963,8 @@
           <t>3.58%</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>16.03</t>
-        </is>
+      <c r="H170" t="n">
+        <v>16.03</v>
       </c>
     </row>
     <row r="171">
@@ -7009,10 +6999,8 @@
           <t>7.72%</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>15.90</t>
-        </is>
+      <c r="H171" t="n">
+        <v>15.9</v>
       </c>
     </row>
     <row r="172">
@@ -7047,10 +7035,8 @@
           <t>3.48%</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>19.49</t>
-        </is>
+      <c r="H172" t="n">
+        <v>19.49</v>
       </c>
     </row>
     <row r="173">
@@ -7085,11 +7071,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7123,10 +7105,8 @@
           <t>1.25%</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>31.77</t>
-        </is>
+      <c r="H174" t="n">
+        <v>31.77</v>
       </c>
     </row>
     <row r="175">
@@ -7161,10 +7141,8 @@
           <t>3.18%</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>32.68</t>
-        </is>
+      <c r="H175" t="n">
+        <v>32.68</v>
       </c>
     </row>
     <row r="176">
@@ -7199,10 +7177,8 @@
           <t>5.35%</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>38.47</t>
-        </is>
+      <c r="H176" t="n">
+        <v>38.47</v>
       </c>
     </row>
     <row r="177">
@@ -7237,9 +7213,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>34.43</t>
+      <c r="H177" t="n">
+        <v>34.43</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="D178" t="n">
+        <v>5</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>3.02%</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>284.01%</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>43.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>20</v>
+      </c>
+      <c r="D179" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>9.89%</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>11.73%</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0.94%</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>9.32%</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>11.02%</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>50.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>1.97%</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>96.29%</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>3.51%</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>16.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="D182" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-0.0%</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>10.96%</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>7.72%</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>15.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="D183" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>-1.09%</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>13.33%</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>3.52%</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>19.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>149.63%</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="D185" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>124.36%</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>31.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="D186" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>-0.16%</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>119.14%</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>3.18%</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>32.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="D187" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>-0.72%</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>167.94%</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>5.39%</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>38.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="D188" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>-0.19%</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>57.50%</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>34.37</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,19 +483,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>170.5</v>
+        <v>166</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>-4.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>284.01%</t>
+          <t>282.05%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -505,14 +505,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>43.27</t>
+          <t>42.13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8</v>
+        <v>-0.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.89%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>11.73%</t>
+          <t>11.43%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32.2</v>
+        <v>35.4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>9.94%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.32%</t>
+          <t>22.71%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.02%</t>
+          <t>10.02%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>50.31</t>
+          <t>55.31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.45</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
         <v>0.55</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>96.29%</t>
+          <t>98.77%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.51%</t>
+          <t>3.45%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.67</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33.7</v>
+        <v>34.45</v>
       </c>
       <c r="D6" t="n">
-        <v>-0</v>
+        <v>0.75</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10.96%</t>
+          <t>10.59%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.72%</t>
+          <t>7.55%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>16.25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>45.5</v>
+        <v>46.3</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.09%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>13.33%</t>
+          <t>14.50%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.62</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.05</v>
+        <v>16.85</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>149.63%</t>
+          <t>145.99%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>108.35</v>
+        <v>108.25</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.45</v>
+        <v>-0.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>124.36%</t>
+          <t>127.61%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -771,14 +771,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.64</t>
+          <t>31.61</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>92.7</v>
+        <v>92.55</v>
       </c>
       <c r="D10" t="n">
         <v>-0.15</v>
@@ -799,24 +799,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>119.14%</t>
+          <t>121.23%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.19%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.58</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>42.52</v>
+        <v>42.6</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.31</v>
+        <v>0.08</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>167.94%</t>
+          <t>172.50%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.39%</t>
+          <t>5.38%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>38.19</t>
+          <t>38.26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.75</v>
+        <v>15.65</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.63%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>57.50%</t>
+          <t>56.50%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>34.15</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7249,10 +7249,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>43.27</t>
-        </is>
+      <c r="H178" t="n">
+        <v>43.27</v>
       </c>
     </row>
     <row r="179">
@@ -7287,11 +7285,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7325,10 +7319,8 @@
           <t>11.02%</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>50.31</t>
-        </is>
+      <c r="H180" t="n">
+        <v>50.31</v>
       </c>
     </row>
     <row r="181">
@@ -7363,10 +7355,8 @@
           <t>3.51%</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>16.35</t>
-        </is>
+      <c r="H181" t="n">
+        <v>16.35</v>
       </c>
     </row>
     <row r="182">
@@ -7384,7 +7374,7 @@
         <v>33.7</v>
       </c>
       <c r="D182" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -7401,10 +7391,8 @@
           <t>7.72%</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>15.90</t>
-        </is>
+      <c r="H182" t="n">
+        <v>15.9</v>
       </c>
     </row>
     <row r="183">
@@ -7439,10 +7427,8 @@
           <t>3.52%</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>19.28</t>
-        </is>
+      <c r="H183" t="n">
+        <v>19.28</v>
       </c>
     </row>
     <row r="184">
@@ -7477,11 +7463,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7515,10 +7497,8 @@
           <t>1.26%</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>31.64</t>
-        </is>
+      <c r="H185" t="n">
+        <v>31.64</v>
       </c>
     </row>
     <row r="186">
@@ -7553,10 +7533,8 @@
           <t>3.18%</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>32.63</t>
-        </is>
+      <c r="H186" t="n">
+        <v>32.63</v>
       </c>
     </row>
     <row r="187">
@@ -7591,10 +7569,8 @@
           <t>5.39%</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>38.19</t>
-        </is>
+      <c r="H187" t="n">
+        <v>38.19</v>
       </c>
     </row>
     <row r="188">
@@ -7629,9 +7605,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>34.37</t>
+      <c r="H188" t="n">
+        <v>34.37</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>166</v>
+      </c>
+      <c r="D189" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>-2.64%</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>282.05%</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>42.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D190" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>-2.5%</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>11.43%</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="D191" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>9.94%</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>22.71%</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>10.02%</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>55.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>29</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>1.93%</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>98.77%</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>16.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>10.59%</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>7.55%</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>16.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>1.76%</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>14.50%</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>3.46%</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>19.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="D195" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>-1.17%</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>145.99%</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="D196" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>127.61%</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>31.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="D197" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>-0.16%</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>121.23%</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>3.19%</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>32.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>172.50%</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>5.38%</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>38.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="D199" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>-0.63%</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>56.50%</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>34.15</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,19 +483,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.5</v>
+        <v>-11</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>-6.63%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>282.05%</t>
+          <t>256.73%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -505,14 +505,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>42.13</t>
+          <t>39.44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.5</v>
+        <v>19.95</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.5</v>
+        <v>0.45</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>2.31%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>11.43%</t>
+          <t>14.00%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>35.4</v>
+        <v>34.45</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2</v>
+        <v>-0.95</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9.94%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.71%</t>
+          <t>19.41%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.02%</t>
+          <t>10.30%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>55.31</t>
+          <t>53.83</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>30.1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.55</v>
+        <v>1.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>3.79%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>98.77%</t>
+          <t>106.31%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>17.30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.45</v>
+        <v>34.5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.75</v>
+        <v>0.05</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10.59%</t>
+          <t>10.75%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.55%</t>
+          <t>7.54%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>16.27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.3</v>
+        <v>46.8</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.08%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14.50%</t>
+          <t>15.73%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.42%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>19.83</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.85</v>
+        <v>16.1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2</v>
+        <v>-0.75</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>-4.45%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>145.99%</t>
+          <t>135.04%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>108.25</v>
+        <v>106.2</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1</v>
+        <v>-2.05</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-1.89%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>127.61%</t>
+          <t>123.30%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.61</t>
+          <t>31.01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>92.55</v>
+        <v>89.95</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.15</v>
+        <v>-2.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-2.81%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>121.23%</t>
+          <t>115.01%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>3.28%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>32.58</t>
+          <t>31.66</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>42.6</v>
+        <v>41.16</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08</v>
+        <v>-1.44</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>-3.38%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>172.50%</t>
+          <t>163.29%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.38%</t>
+          <t>5.56%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>36.97</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.65</v>
+        <v>15.29</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1</v>
+        <v>-0.36</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>56.50%</t>
+          <t>52.90%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>33.36</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H199"/>
+  <dimension ref="A1:H210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7641,10 +7641,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>42.13</t>
-        </is>
+      <c r="H189" t="n">
+        <v>42.13</v>
       </c>
     </row>
     <row r="190">
@@ -7679,11 +7677,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7717,10 +7711,8 @@
           <t>10.02%</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>55.31</t>
-        </is>
+      <c r="H191" t="n">
+        <v>55.31</v>
       </c>
     </row>
     <row r="192">
@@ -7755,10 +7747,8 @@
           <t>3.45%</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>16.67</t>
-        </is>
+      <c r="H192" t="n">
+        <v>16.67</v>
       </c>
     </row>
     <row r="193">
@@ -7793,10 +7783,8 @@
           <t>7.55%</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>16.25</t>
-        </is>
+      <c r="H193" t="n">
+        <v>16.25</v>
       </c>
     </row>
     <row r="194">
@@ -7831,10 +7819,8 @@
           <t>3.46%</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>19.62</t>
-        </is>
+      <c r="H194" t="n">
+        <v>19.62</v>
       </c>
     </row>
     <row r="195">
@@ -7869,11 +7855,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7907,10 +7889,8 @@
           <t>1.26%</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>31.61</t>
-        </is>
+      <c r="H196" t="n">
+        <v>31.61</v>
       </c>
     </row>
     <row r="197">
@@ -7945,10 +7925,8 @@
           <t>3.19%</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>32.58</t>
-        </is>
+      <c r="H197" t="n">
+        <v>32.58</v>
       </c>
     </row>
     <row r="198">
@@ -7983,10 +7961,8 @@
           <t>5.38%</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>38.26</t>
-        </is>
+      <c r="H198" t="n">
+        <v>38.26</v>
       </c>
     </row>
     <row r="199">
@@ -8021,9 +7997,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>34.15</t>
+      <c r="H199" t="n">
+        <v>34.15</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>155</v>
+      </c>
+      <c r="D200" t="n">
+        <v>-11</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>-6.63%</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>256.73%</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>39.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>2.31%</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>14.00%</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="D202" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>-2.68%</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>19.41%</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>10.30%</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>53.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="D203" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>3.79%</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>106.31%</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>3.32%</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>17.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>0.15%</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>10.75%</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>7.54%</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>16.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>1.08%</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>15.73%</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>3.42%</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>19.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="D206" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>-4.45%</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>135.04%</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="D207" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>-1.89%</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>123.30%</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>1.28%</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>31.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="D208" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>-2.81%</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>115.01%</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>3.28%</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>31.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>41.16</v>
+      </c>
+      <c r="D209" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>-3.38%</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>163.29%</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>5.56%</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>36.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="D210" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>-2.3%</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>52.90%</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>33.36</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="D2" t="n">
-        <v>-11</v>
+        <v>10.61</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-6.63%</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>256.73%</t>
+          <t>279.38%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>41.37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.95</v>
+        <v>21.9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.45</v>
+        <v>1.95</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>9.77%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14.00%</t>
+          <t>25.86%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34.45</v>
+        <v>34.4</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.95</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-2.68%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.41%</t>
+          <t>19.69%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.30%</t>
+          <t>10.32%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>53.83</t>
+          <t>53.75</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.1</v>
+        <v>30.7</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>106.31%</t>
+          <t>115.36%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.32%</t>
+          <t>3.26%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.30</t>
+          <t>17.64</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.5</v>
+        <v>34.75</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10.75%</t>
+          <t>11.56%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.54%</t>
+          <t>7.48%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.27</t>
+          <t>16.39</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -676,16 +676,16 @@
         <v>46.8</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>15.73%</t>
+          <t>14.78%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.1</v>
+        <v>16.05</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.75</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-4.45%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>135.04%</t>
+          <t>138.48%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>106.2</v>
+        <v>106.05</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.05</v>
+        <v>-0.15</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-1.89%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>123.30%</t>
+          <t>124.00%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -771,14 +771,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.01</t>
+          <t>30.97</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -790,16 +790,16 @@
         <v>89.95</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-2.81%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>115.01%</t>
+          <t>115.95%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -828,16 +828,16 @@
         <v>41.16</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.44</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-3.38%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>163.29%</t>
+          <t>165.92%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -854,7 +854,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.29</v>
+        <v>15.26</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.36</v>
+        <v>-0.03</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>52.90%</t>
+          <t>52.60%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.36</t>
+          <t>33.30</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H210"/>
+  <dimension ref="A1:H221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8033,10 +8033,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>39.44</t>
-        </is>
+      <c r="H200" t="n">
+        <v>39.44</v>
       </c>
     </row>
     <row r="201">
@@ -8071,11 +8069,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8109,10 +8103,8 @@
           <t>10.30%</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>53.83</t>
-        </is>
+      <c r="H202" t="n">
+        <v>53.83</v>
       </c>
     </row>
     <row r="203">
@@ -8147,10 +8139,8 @@
           <t>3.32%</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>17.30</t>
-        </is>
+      <c r="H203" t="n">
+        <v>17.3</v>
       </c>
     </row>
     <row r="204">
@@ -8185,10 +8175,8 @@
           <t>7.54%</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>16.27</t>
-        </is>
+      <c r="H204" t="n">
+        <v>16.27</v>
       </c>
     </row>
     <row r="205">
@@ -8223,10 +8211,8 @@
           <t>3.42%</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>19.83</t>
-        </is>
+      <c r="H205" t="n">
+        <v>19.83</v>
       </c>
     </row>
     <row r="206">
@@ -8261,11 +8247,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -8299,10 +8281,8 @@
           <t>1.28%</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>31.01</t>
-        </is>
+      <c r="H207" t="n">
+        <v>31.01</v>
       </c>
     </row>
     <row r="208">
@@ -8337,10 +8317,8 @@
           <t>3.28%</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>31.66</t>
-        </is>
+      <c r="H208" t="n">
+        <v>31.66</v>
       </c>
     </row>
     <row r="209">
@@ -8375,10 +8353,8 @@
           <t>5.56%</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>36.97</t>
-        </is>
+      <c r="H209" t="n">
+        <v>36.97</v>
       </c>
     </row>
     <row r="210">
@@ -8413,9 +8389,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>33.36</t>
+      <c r="H210" t="n">
+        <v>33.36</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>163</v>
+      </c>
+      <c r="D211" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>279.38%</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>1.60%</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>41.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="D212" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>9.77%</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>25.86%</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="D213" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>-0.15%</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>19.69%</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>10.32%</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>53.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>1.99%</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>115.36%</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>3.26%</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>17.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>0.72%</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>11.56%</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>7.48%</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>16.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>14.78%</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>3.42%</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>19.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="D217" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>-0.31%</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>138.48%</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="D218" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>-0.14%</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>124.00%</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>1.28%</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>30.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>115.95%</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>3.28%</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>31.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>41.16</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>165.92%</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>5.56%</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>36.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="D221" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>52.60%</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>33.30</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D2" t="n">
-        <v>10.61</v>
+        <v>-7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-4.29%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>279.38%</t>
+          <t>261.43%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>39.59</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.9</v>
+        <v>24.05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.77%</t>
+          <t>9.82%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.86%</t>
+          <t>37.82%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34.4</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.05</v>
+        <v>-1.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-4.07%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.69%</t>
+          <t>14.60%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.32%</t>
+          <t>10.75%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>53.75</t>
+          <t>51.56</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.7</v>
+        <v>30.05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6</v>
+        <v>-0.65</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>-2.12%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>115.36%</t>
+          <t>111.51%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.64</t>
+          <t>17.27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -638,16 +638,16 @@
         <v>34.75</v>
       </c>
       <c r="D6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11.56%</t>
+          <t>10.90%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -664,7 +664,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14.78%</t>
+          <t>15.63%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>19.79</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.05</v>
+        <v>16.4</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>0.35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>2.18%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>138.48%</t>
+          <t>147.36%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>106.05</v>
+        <v>105.8</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.15</v>
+        <v>-0.25</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>124.00%</t>
+          <t>121.19%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30.97</t>
+          <t>30.90</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>89.95</v>
+        <v>89.75</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>115.95%</t>
+          <t>113.18%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>31.59</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>41.16</v>
+        <v>41.61</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>165.92%</t>
+          <t>162.81%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.56%</t>
+          <t>5.50%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>37.37</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.26</v>
+        <v>15.23</v>
       </c>
       <c r="D12" t="n">
         <v>-0.03</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>52.60%</t>
+          <t>52.30%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.30</t>
+          <t>33.23</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H221"/>
+  <dimension ref="A1:H232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8425,10 +8425,8 @@
           <t>1.60%</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>41.37</t>
-        </is>
+      <c r="H211" t="n">
+        <v>41.37</v>
       </c>
     </row>
     <row r="212">
@@ -8463,11 +8461,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8501,10 +8495,8 @@
           <t>10.32%</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>53.75</t>
-        </is>
+      <c r="H213" t="n">
+        <v>53.75</v>
       </c>
     </row>
     <row r="214">
@@ -8539,10 +8531,8 @@
           <t>3.26%</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>17.64</t>
-        </is>
+      <c r="H214" t="n">
+        <v>17.64</v>
       </c>
     </row>
     <row r="215">
@@ -8577,10 +8567,8 @@
           <t>7.48%</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>16.39</t>
-        </is>
+      <c r="H215" t="n">
+        <v>16.39</v>
       </c>
     </row>
     <row r="216">
@@ -8615,10 +8603,8 @@
           <t>3.42%</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>19.83</t>
-        </is>
+      <c r="H216" t="n">
+        <v>19.83</v>
       </c>
     </row>
     <row r="217">
@@ -8653,11 +8639,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -8691,10 +8673,8 @@
           <t>1.28%</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>30.97</t>
-        </is>
+      <c r="H218" t="n">
+        <v>30.97</v>
       </c>
     </row>
     <row r="219">
@@ -8729,10 +8709,8 @@
           <t>3.28%</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>31.66</t>
-        </is>
+      <c r="H219" t="n">
+        <v>31.66</v>
       </c>
     </row>
     <row r="220">
@@ -8767,10 +8745,8 @@
           <t>5.56%</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>36.97</t>
-        </is>
+      <c r="H220" t="n">
+        <v>36.97</v>
       </c>
     </row>
     <row r="221">
@@ -8805,9 +8781,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>33.30</t>
+      <c r="H221" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>156</v>
+      </c>
+      <c r="D222" t="n">
+        <v>-7</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>-4.29%</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>261.43%</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>1.67%</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>39.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="D223" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>9.82%</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>37.82%</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>33</v>
+      </c>
+      <c r="D224" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>-4.07%</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>14.60%</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>10.75%</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>51.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>30.05</v>
+      </c>
+      <c r="D225" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>-2.12%</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>111.51%</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>3.33%</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>17.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>10.90%</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>7.48%</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>16.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="D227" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>15.63%</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>19.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>2.18%</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>147.36%</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="D229" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>121.19%</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>1.29%</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>30.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>89.75</v>
+      </c>
+      <c r="D230" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>-0.22%</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>3.29%</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>31.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>1.09%</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>162.81%</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>5.50%</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>37.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="D232" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>52.30%</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>33.23</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,16 +486,16 @@
         <v>156</v>
       </c>
       <c r="D2" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-4.29%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>261.43%</t>
+          <t>263.09%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -505,14 +505,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>39.59</t>
+          <t>39.49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -524,16 +524,16 @@
         <v>24.05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.82%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>37.82%</t>
+          <t>39.02%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -562,16 +562,16 @@
         <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-4.07%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14.60%</t>
+          <t>14.82%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -600,16 +600,16 @@
         <v>30.05</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.65</v>
+        <v>0</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-2.12%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>111.51%</t>
+          <t>108.70%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -626,7 +626,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10.90%</t>
+          <t>9.31%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -664,7 +664,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -676,16 +676,16 @@
         <v>46.7</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>15.63%</t>
+          <t>14.67%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -714,16 +714,16 @@
         <v>16.4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>147.36%</t>
+          <t>148.48%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -752,16 +752,16 @@
         <v>105.8</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>121.19%</t>
+          <t>118.68%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -778,7 +778,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -790,16 +790,16 @@
         <v>89.75</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>113.18%</t>
+          <t>111.03%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -828,16 +828,16 @@
         <v>41.61</v>
       </c>
       <c r="D11" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>162.81%</t>
+          <t>161.16%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -854,7 +854,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -866,11 +866,11 @@
         <v>15.23</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H232"/>
+  <dimension ref="A1:H243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8817,10 +8817,8 @@
           <t>1.67%</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>39.59</t>
-        </is>
+      <c r="H222" t="n">
+        <v>39.59</v>
       </c>
     </row>
     <row r="223">
@@ -8855,11 +8853,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8893,10 +8887,8 @@
           <t>10.75%</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>51.56</t>
-        </is>
+      <c r="H224" t="n">
+        <v>51.56</v>
       </c>
     </row>
     <row r="225">
@@ -8931,10 +8923,8 @@
           <t>3.33%</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>17.27</t>
-        </is>
+      <c r="H225" t="n">
+        <v>17.27</v>
       </c>
     </row>
     <row r="226">
@@ -8969,10 +8959,8 @@
           <t>7.48%</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>16.39</t>
-        </is>
+      <c r="H226" t="n">
+        <v>16.39</v>
       </c>
     </row>
     <row r="227">
@@ -9007,10 +8995,8 @@
           <t>3.43%</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>19.79</t>
-        </is>
+      <c r="H227" t="n">
+        <v>19.79</v>
       </c>
     </row>
     <row r="228">
@@ -9045,11 +9031,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -9083,10 +9065,8 @@
           <t>1.29%</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>30.90</t>
-        </is>
+      <c r="H229" t="n">
+        <v>30.9</v>
       </c>
     </row>
     <row r="230">
@@ -9121,10 +9101,8 @@
           <t>3.29%</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>31.59</t>
-        </is>
+      <c r="H230" t="n">
+        <v>31.59</v>
       </c>
     </row>
     <row r="231">
@@ -9159,10 +9137,8 @@
           <t>5.50%</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>37.37</t>
-        </is>
+      <c r="H231" t="n">
+        <v>37.37</v>
       </c>
     </row>
     <row r="232">
@@ -9197,7 +9173,423 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
+      <c r="H232" t="n">
+        <v>33.23</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>156</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>263.09%</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>1.67%</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>39.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>39.02%</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>33</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>14.82%</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>10.75%</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>51.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>30.05</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>108.70%</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>3.33%</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>17.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>9.31%</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>7.48%</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>16.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>14.67%</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>19.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>148.48%</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>118.68%</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>1.29%</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>30.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>89.75</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>111.03%</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>3.29%</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>31.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>161.16%</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>5.50%</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>37.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>52.30%</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
         <is>
           <t>33.23</t>
         </is>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>156</v>
+        <v>153.5</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>263.09%</t>
+          <t>261.82%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>39.49</t>
+          <t>38.86</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24.05</v>
+        <v>25.95</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39.02%</t>
+          <t>51.75%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-6.06%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14.82%</t>
+          <t>5.84%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.75%</t>
+          <t>11.45%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>51.56</t>
+          <t>48.44</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.05</v>
+        <v>29.8</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>108.70%</t>
+          <t>102.92%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.36%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.27</t>
+          <t>17.13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.75</v>
+        <v>34.6</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.31%</t>
+          <t>7.44%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.48%</t>
+          <t>7.51%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>16.32</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.7</v>
+        <v>47</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.64%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14.67%</t>
+          <t>14.86%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.40%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>19.92</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.4</v>
+        <v>16.7</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>148.48%</t>
+          <t>142.73%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>105.8</v>
+        <v>106</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>118.68%</t>
+          <t>119.45%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30.90</t>
+          <t>30.96</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,19 +787,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>89.75</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>111.03%</t>
+          <t>111.43%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -809,14 +809,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.59</t>
+          <t>31.54</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>41.61</v>
+        <v>41.03</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0.58</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>161.16%</t>
+          <t>158.55%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.50%</t>
+          <t>5.58%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>36.85</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.23</v>
+        <v>15.25</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>52.30%</t>
+          <t>52.50%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>33.28</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H243"/>
+  <dimension ref="A1:H254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9209,10 +9209,8 @@
           <t>1.67%</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>39.49</t>
-        </is>
+      <c r="H233" t="n">
+        <v>39.49</v>
       </c>
     </row>
     <row r="234">
@@ -9247,11 +9245,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -9285,10 +9279,8 @@
           <t>10.75%</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>51.56</t>
-        </is>
+      <c r="H235" t="n">
+        <v>51.56</v>
       </c>
     </row>
     <row r="236">
@@ -9323,10 +9315,8 @@
           <t>3.33%</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>17.27</t>
-        </is>
+      <c r="H236" t="n">
+        <v>17.27</v>
       </c>
     </row>
     <row r="237">
@@ -9361,10 +9351,8 @@
           <t>7.48%</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>16.39</t>
-        </is>
+      <c r="H237" t="n">
+        <v>16.39</v>
       </c>
     </row>
     <row r="238">
@@ -9399,10 +9387,8 @@
           <t>3.43%</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>19.79</t>
-        </is>
+      <c r="H238" t="n">
+        <v>19.79</v>
       </c>
     </row>
     <row r="239">
@@ -9437,11 +9423,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -9475,10 +9457,8 @@
           <t>1.29%</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>30.90</t>
-        </is>
+      <c r="H240" t="n">
+        <v>30.9</v>
       </c>
     </row>
     <row r="241">
@@ -9513,10 +9493,8 @@
           <t>3.29%</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>31.59</t>
-        </is>
+      <c r="H241" t="n">
+        <v>31.59</v>
       </c>
     </row>
     <row r="242">
@@ -9551,10 +9529,8 @@
           <t>5.50%</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>37.37</t>
-        </is>
+      <c r="H242" t="n">
+        <v>37.37</v>
       </c>
     </row>
     <row r="243">
@@ -9589,9 +9565,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>33.23</t>
+      <c r="H243" t="n">
+        <v>33.23</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="D244" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>-1.6%</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>261.82%</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>1.70%</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>38.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="D245" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>7.9%</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>51.75%</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>31</v>
+      </c>
+      <c r="D246" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>-6.06%</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>5.84%</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>11.45%</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>48.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="D247" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>-0.83%</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>102.92%</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>3.36%</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>17.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="D248" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>-0.43%</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>7.44%</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>7.51%</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>16.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>47</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>0.64%</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>14.86%</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>3.40%</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>19.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>1.83%</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>142.73%</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>106</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>119.45%</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>1.28%</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>30.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="D252" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>111.43%</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>3.29%</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>31.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>41.03</v>
+      </c>
+      <c r="D253" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>-1.39%</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>158.55%</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>5.58%</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>36.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>0.13%</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>52.50%</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>33.28</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>153.5</v>
+        <v>151</v>
       </c>
       <c r="D2" t="n">
         <v>-2.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>261.82%</t>
+          <t>255.93%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.73%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>37.94</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25.95</v>
+        <v>24.05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9</v>
+        <v>-1.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>-7.32%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>51.75%</t>
+          <t>40.64%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>30.6</v>
       </c>
       <c r="D4" t="n">
-        <v>-2</v>
+        <v>-0.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-6.06%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5.84%</t>
+          <t>4.48%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.45%</t>
+          <t>11.60%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>47.34</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29.8</v>
+        <v>29.5</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.25</v>
+        <v>-0.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.83%</t>
+          <t>-1.01%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>102.92%</t>
+          <t>100.88%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.36%</t>
+          <t>3.39%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>16.72</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>7.44%</t>
+          <t>7.13%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.51%</t>
+          <t>7.54%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -676,11 +676,11 @@
         <v>47</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -695,14 +695,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>19.81</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.7</v>
+        <v>17.5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>4.79%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>142.73%</t>
+          <t>154.36%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,24 +749,24 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>106</v>
+        <v>104.4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2</v>
+        <v>-1.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>119.45%</t>
+          <t>116.14%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -778,7 +778,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,24 +787,24 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>89.59999999999999</v>
+        <v>87.95</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.15</v>
+        <v>-1.65</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-1.84%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>111.43%</t>
+          <t>107.54%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,24 +825,24 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>41.03</v>
+        <v>40</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.58</v>
+        <v>-1.03</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-1.39%</t>
+          <t>-2.51%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>158.55%</t>
+          <t>152.06%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.58%</t>
+          <t>5.73%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -854,7 +854,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.25</v>
+        <v>14.97</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02</v>
+        <v>-0.28</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>-1.84%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>52.50%</t>
+          <t>49.70%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H254"/>
+  <dimension ref="A1:H265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9601,10 +9601,8 @@
           <t>1.70%</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>38.86</t>
-        </is>
+      <c r="H244" t="n">
+        <v>38.86</v>
       </c>
     </row>
     <row r="245">
@@ -9639,11 +9637,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -9677,10 +9671,8 @@
           <t>11.45%</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>48.44</t>
-        </is>
+      <c r="H246" t="n">
+        <v>48.44</v>
       </c>
     </row>
     <row r="247">
@@ -9715,10 +9707,8 @@
           <t>3.36%</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>17.13</t>
-        </is>
+      <c r="H247" t="n">
+        <v>17.13</v>
       </c>
     </row>
     <row r="248">
@@ -9753,10 +9743,8 @@
           <t>7.51%</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>16.32</t>
-        </is>
+      <c r="H248" t="n">
+        <v>16.32</v>
       </c>
     </row>
     <row r="249">
@@ -9791,10 +9779,8 @@
           <t>3.40%</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>19.92</t>
-        </is>
+      <c r="H249" t="n">
+        <v>19.92</v>
       </c>
     </row>
     <row r="250">
@@ -9829,11 +9815,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -9867,10 +9849,8 @@
           <t>1.28%</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>30.96</t>
-        </is>
+      <c r="H251" t="n">
+        <v>30.96</v>
       </c>
     </row>
     <row r="252">
@@ -9905,10 +9885,8 @@
           <t>3.29%</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>31.54</t>
-        </is>
+      <c r="H252" t="n">
+        <v>31.54</v>
       </c>
     </row>
     <row r="253">
@@ -9943,10 +9921,8 @@
           <t>5.58%</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>36.85</t>
-        </is>
+      <c r="H253" t="n">
+        <v>36.85</v>
       </c>
     </row>
     <row r="254">
@@ -9981,7 +9957,423 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
+      <c r="H254" t="n">
+        <v>33.28</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>151</v>
+      </c>
+      <c r="D255" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>-1.63%</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>255.93%</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>1.73%</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>37.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="D256" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>-7.32%</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>40.64%</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="D257" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>-1.29%</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>4.48%</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>11.60%</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>47.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="D258" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>-1.01%</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>100.88%</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>3.39%</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>16.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="D259" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>-0.29%</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>7.13%</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>7.54%</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>16.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>47</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>14.86%</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>3.40%</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>19.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>4.79%</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>154.36%</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="D262" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>116.14%</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>1.30%</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>30.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>87.95</v>
+      </c>
+      <c r="D263" t="n">
+        <v>-1.65</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>-1.84%</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>107.54%</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>3.35%</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>31.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>40</v>
+      </c>
+      <c r="D264" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>-2.51%</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>152.06%</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>5.73%</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>36.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="D265" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>-1.84%</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>49.70%</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
         <is>
           <t>33.28</t>
         </is>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.5</v>
+        <v>15</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>9.93%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>255.93%</t>
+          <t>287.69%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>42.13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24.05</v>
+        <v>23.55</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.9</v>
+        <v>-0.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-7.32%</t>
+          <t>-2.08%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40.64%</t>
+          <t>36.13%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30.6</v>
+        <v>31.5</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4</v>
+        <v>0.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4.48%</t>
+          <t>5.76%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.60%</t>
+          <t>11.27%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>47.34</t>
+          <t>49.22</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29.5</v>
+        <v>30.15</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3</v>
+        <v>0.65</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>100.88%</t>
+          <t>107.33%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>16.72</t>
+          <t>17.33</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.5</v>
+        <v>34.45</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>7.13%</t>
+          <t>6.52%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.54%</t>
+          <t>7.55%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>16.25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-2.13%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14.86%</t>
+          <t>13.76%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.48%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.81</t>
+          <t>19.49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4.79%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>154.36%</t>
+          <t>156.52%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>104.4</v>
+        <v>106.3</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6</v>
+        <v>1.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>116.14%</t>
+          <t>117.12%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>31.04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>87.95</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.65</v>
+        <v>1.95</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>107.54%</t>
+          <t>109.78%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.28%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>31.65</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40</v>
+        <v>41.29</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.03</v>
+        <v>1.29</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-2.51%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>152.06%</t>
+          <t>158.56%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.73%</t>
+          <t>5.55%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.08</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.97</v>
+        <v>15.29</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.28</v>
+        <v>0.32</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>2.14%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>49.70%</t>
+          <t>52.90%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.28</t>
+          <t>33.36</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H265"/>
+  <dimension ref="A1:H276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9993,10 +9993,8 @@
           <t>1.73%</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>37.94</t>
-        </is>
+      <c r="H255" t="n">
+        <v>37.94</v>
       </c>
     </row>
     <row r="256">
@@ -10031,11 +10029,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -10069,10 +10063,8 @@
           <t>11.60%</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>47.34</t>
-        </is>
+      <c r="H257" t="n">
+        <v>47.34</v>
       </c>
     </row>
     <row r="258">
@@ -10107,10 +10099,8 @@
           <t>3.39%</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>16.72</t>
-        </is>
+      <c r="H258" t="n">
+        <v>16.72</v>
       </c>
     </row>
     <row r="259">
@@ -10145,10 +10135,8 @@
           <t>7.54%</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>16.11</t>
-        </is>
+      <c r="H259" t="n">
+        <v>16.11</v>
       </c>
     </row>
     <row r="260">
@@ -10183,10 +10171,8 @@
           <t>3.40%</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>19.81</t>
-        </is>
+      <c r="H260" t="n">
+        <v>19.81</v>
       </c>
     </row>
     <row r="261">
@@ -10221,11 +10207,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -10259,10 +10241,8 @@
           <t>1.30%</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>30.96</t>
-        </is>
+      <c r="H262" t="n">
+        <v>30.96</v>
       </c>
     </row>
     <row r="263">
@@ -10297,10 +10277,8 @@
           <t>3.35%</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>31.54</t>
-        </is>
+      <c r="H263" t="n">
+        <v>31.54</v>
       </c>
     </row>
     <row r="264">
@@ -10335,10 +10313,8 @@
           <t>5.73%</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>36.85</t>
-        </is>
+      <c r="H264" t="n">
+        <v>36.85</v>
       </c>
     </row>
     <row r="265">
@@ -10373,9 +10349,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>33.28</t>
+      <c r="H265" t="n">
+        <v>33.28</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>166</v>
+      </c>
+      <c r="D266" t="n">
+        <v>15</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>9.93%</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>287.69%</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>1.57%</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>42.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="D267" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>-2.08%</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>36.13%</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D268" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>2.94%</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>5.76%</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>11.27%</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>49.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="D269" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>107.33%</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>3.32%</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>17.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="D270" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>-0.14%</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>6.52%</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>7.55%</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>16.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>46</v>
+      </c>
+      <c r="D271" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>-2.13%</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>13.76%</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>3.48%</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>19.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>156.52%</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="D273" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>1.82%</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>117.12%</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>1.28%</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>31.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="D274" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>2.22%</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>109.78%</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>3.28%</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>31.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>41.29</v>
+      </c>
+      <c r="D275" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>3.23%</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>158.56%</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>5.55%</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>37.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="D276" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>2.14%</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>52.90%</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>33.36</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>-6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9.93%</t>
+          <t>-3.61%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>287.69%</t>
+          <t>274.54%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>42.13</t>
+          <t>40.71</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23.55</v>
+        <v>22.5</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.5</v>
+        <v>-1.05</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.08%</t>
+          <t>-4.46%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>36.13%</t>
+          <t>30.43%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31.5</v>
+        <v>31.35</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9</v>
+        <v>-0.15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5.76%</t>
+          <t>5.45%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.27%</t>
+          <t>11.32%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>49.22</t>
+          <t>48.98</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.15</v>
+        <v>30.55</v>
       </c>
       <c r="D5" t="n">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>107.33%</t>
+          <t>107.35%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.32%</t>
+          <t>3.27%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.56</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.45</v>
+        <v>34.9</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.05</v>
+        <v>0.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>6.52%</t>
+          <t>8.06%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.55%</t>
+          <t>7.45%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>16.46</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46</v>
+        <v>46.6</v>
       </c>
       <c r="D7" t="n">
-        <v>-1</v>
+        <v>0.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-2.13%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>13.76%</t>
+          <t>14.69%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.75</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -714,16 +714,16 @@
         <v>17.7</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2</v>
+        <v>-0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>156.52%</t>
+          <t>159.15%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>106.3</v>
+        <v>106.4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>0.09%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>117.12%</t>
+          <t>115.60%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -771,14 +771,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.04</t>
+          <t>31.07</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>89.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="D10" t="n">
-        <v>1.95</v>
+        <v>-0.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>109.78%</t>
+          <t>107.56%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.61</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>41.29</v>
+        <v>38.7</v>
       </c>
       <c r="D11" t="n">
-        <v>1.29</v>
+        <v>-2.59</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>-6.27%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>158.56%</t>
+          <t>138.89%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.55%</t>
+          <t>5.35%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>37.08</t>
+          <t>34.76</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -866,11 +866,11 @@
         <v>15.29</v>
       </c>
       <c r="D12" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H276"/>
+  <dimension ref="A1:H287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10385,10 +10385,8 @@
           <t>1.57%</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>42.13</t>
-        </is>
+      <c r="H266" t="n">
+        <v>42.13</v>
       </c>
     </row>
     <row r="267">
@@ -10423,11 +10421,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -10461,10 +10455,8 @@
           <t>11.27%</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>49.22</t>
-        </is>
+      <c r="H268" t="n">
+        <v>49.22</v>
       </c>
     </row>
     <row r="269">
@@ -10499,10 +10491,8 @@
           <t>3.32%</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>17.33</t>
-        </is>
+      <c r="H269" t="n">
+        <v>17.33</v>
       </c>
     </row>
     <row r="270">
@@ -10537,10 +10527,8 @@
           <t>7.55%</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>16.25</t>
-        </is>
+      <c r="H270" t="n">
+        <v>16.25</v>
       </c>
     </row>
     <row r="271">
@@ -10575,10 +10563,8 @@
           <t>3.48%</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>19.49</t>
-        </is>
+      <c r="H271" t="n">
+        <v>19.49</v>
       </c>
     </row>
     <row r="272">
@@ -10613,11 +10599,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -10651,10 +10633,8 @@
           <t>1.28%</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>31.04</t>
-        </is>
+      <c r="H273" t="n">
+        <v>31.04</v>
       </c>
     </row>
     <row r="274">
@@ -10689,10 +10669,8 @@
           <t>3.28%</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
+      <c r="H274" t="n">
+        <v>31.65</v>
       </c>
     </row>
     <row r="275">
@@ -10727,10 +10705,8 @@
           <t>5.55%</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>37.08</t>
-        </is>
+      <c r="H275" t="n">
+        <v>37.08</v>
       </c>
     </row>
     <row r="276">
@@ -10765,7 +10741,423 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr">
+      <c r="H276" t="n">
+        <v>33.36</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>160</v>
+      </c>
+      <c r="D277" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>-3.61%</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>274.54%</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>1.63%</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>40.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D278" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>-4.46%</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>30.43%</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="D279" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>-0.48%</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>5.45%</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>11.32%</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>48.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="D280" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>107.35%</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>3.27%</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>17.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>1.31%</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>8.06%</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>7.45%</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>16.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>14.69%</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="D283" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>-0.0%</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>159.15%</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="D284" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>0.09%</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>115.60%</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>1.28%</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>31.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="D285" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>-0.11%</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>107.56%</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>3.29%</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>31.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="D286" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>-6.27%</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>138.89%</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>5.35%</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>34.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="D287" t="n">
+        <v>0</v>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>52.90%</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
         <is>
           <t>33.36</t>
         </is>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="D2" t="n">
-        <v>-6</v>
+        <v>-16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-3.61%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>274.54%</t>
+          <t>236.31%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>36.55</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.05</v>
+        <v>-2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-4.46%</t>
+          <t>-8.89%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30.43%</t>
+          <t>17.14%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31.35</v>
+        <v>30.4</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.15</v>
+        <v>-0.95</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-3.03%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5.45%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.32%</t>
+          <t>11.67%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>47.50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.55</v>
+        <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4</v>
+        <v>-0.55</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>107.35%</t>
+          <t>102.96%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>17.24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.9</v>
+        <v>35.1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.45</v>
+        <v>0.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>8.06%</t>
+          <t>8.68%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.45%</t>
+          <t>7.41%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.46</t>
+          <t>16.56</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.6</v>
+        <v>47.6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14.69%</t>
+          <t>17.57%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.36%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.17</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.7</v>
+        <v>17.85</v>
       </c>
       <c r="D8" t="n">
-        <v>-0</v>
+        <v>0.15</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>159.15%</t>
+          <t>149.30%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>106.4</v>
+        <v>100.15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1</v>
+        <v>-6.25</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>-5.87%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>115.60%</t>
+          <t>101.73%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>29.25</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>89.8</v>
+        <v>84.05</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1</v>
+        <v>-5.75</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>107.56%</t>
+          <t>94.15%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.51%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.61</t>
+          <t>29.59</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38.7</v>
+        <v>35.68</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.59</v>
+        <v>-3.02</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-6.27%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>138.89%</t>
+          <t>128.16%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.35%</t>
+          <t>11.07%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>32.05</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.29</v>
+        <v>14.28</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-1.01</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-6.61%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>52.90%</t>
+          <t>42.80%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.36</t>
+          <t>31.16</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H287"/>
+  <dimension ref="A1:H298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10777,10 +10777,8 @@
           <t>1.63%</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>40.71</t>
-        </is>
+      <c r="H277" t="n">
+        <v>40.71</v>
       </c>
     </row>
     <row r="278">
@@ -10815,11 +10813,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -10853,10 +10847,8 @@
           <t>11.32%</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>48.98</t>
-        </is>
+      <c r="H279" t="n">
+        <v>48.98</v>
       </c>
     </row>
     <row r="280">
@@ -10891,10 +10883,8 @@
           <t>3.27%</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>17.56</t>
-        </is>
+      <c r="H280" t="n">
+        <v>17.56</v>
       </c>
     </row>
     <row r="281">
@@ -10929,10 +10919,8 @@
           <t>7.45%</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>16.46</t>
-        </is>
+      <c r="H281" t="n">
+        <v>16.46</v>
       </c>
     </row>
     <row r="282">
@@ -10967,10 +10955,8 @@
           <t>3.43%</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>19.75</t>
-        </is>
+      <c r="H282" t="n">
+        <v>19.75</v>
       </c>
     </row>
     <row r="283">
@@ -10988,7 +10974,7 @@
         <v>17.7</v>
       </c>
       <c r="D283" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -11005,11 +10991,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -11043,10 +11025,8 @@
           <t>1.28%</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>31.07</t>
-        </is>
+      <c r="H284" t="n">
+        <v>31.07</v>
       </c>
     </row>
     <row r="285">
@@ -11081,10 +11061,8 @@
           <t>3.29%</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>31.61</t>
-        </is>
+      <c r="H285" t="n">
+        <v>31.61</v>
       </c>
     </row>
     <row r="286">
@@ -11119,10 +11097,8 @@
           <t>5.35%</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>34.76</t>
-        </is>
+      <c r="H286" t="n">
+        <v>34.76</v>
       </c>
     </row>
     <row r="287">
@@ -11157,9 +11133,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>33.36</t>
+      <c r="H287" t="n">
+        <v>33.36</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>144</v>
+      </c>
+      <c r="D288" t="n">
+        <v>-16</v>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>-10.0%</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>236.31%</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>1.81%</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>36.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D289" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>-8.89%</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>17.14%</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="D290" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>-3.03%</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>11.67%</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>47.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>30</v>
+      </c>
+      <c r="D291" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>-1.8%</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>102.96%</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>3.33%</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>17.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="D292" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>0.57%</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>8.68%</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>7.41%</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>16.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="D293" t="n">
+        <v>1</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>2.15%</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>17.57%</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>3.36%</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>20.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="D294" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>0.85%</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>149.30%</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>100.15</v>
+      </c>
+      <c r="D295" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>-5.87%</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>101.73%</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>1.36%</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>29.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>84.05</v>
+      </c>
+      <c r="D296" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>-6.4%</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>94.15%</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>3.51%</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>29.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>35.68</v>
+      </c>
+      <c r="D297" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>-7.8%</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>128.16%</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>11.07%</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>32.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>14.28</v>
+      </c>
+      <c r="D298" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>-6.61%</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>42.80%</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>31.16</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="D2" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>-9.72%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>236.31%</t>
+          <t>203.97%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>32.91</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.5</v>
+        <v>20.65</v>
       </c>
       <c r="D3" t="n">
-        <v>-2</v>
+        <v>0.15</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-8.89%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.14%</t>
+          <t>16.34%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30.4</v>
+        <v>29.85</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.95</v>
+        <v>-0.55</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-3.03%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.67%</t>
+          <t>11.89%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>47.50</t>
+          <t>46.64</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>29.55</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.55</v>
+        <v>-0.45</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>102.96%</t>
+          <t>101.22%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>16.98</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35.1</v>
+        <v>35.85</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>2.14%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>8.68%</t>
+          <t>14.41%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.41%</t>
+          <t>7.25%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>16.91</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>47.6</v>
+        <v>48.2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.57%</t>
+          <t>18.49%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.36%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>20.42</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.85</v>
+        <v>18.45</v>
       </c>
       <c r="D8" t="n">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>3.36%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>149.30%</t>
+          <t>163.57%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>100.15</v>
+        <v>99.2</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.25</v>
+        <v>-0.95</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-5.87%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>101.73%</t>
+          <t>97.64%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>28.97</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>84.05</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.75</v>
+        <v>-0.65</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>94.15%</t>
+          <t>91.17%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.51%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.36</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35.68</v>
+        <v>34.5</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.02</v>
+        <v>-1.18</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-3.31%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>128.16%</t>
+          <t>120.12%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.07%</t>
+          <t>11.45%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>30.99</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.28</v>
+        <v>14.14</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.01</v>
+        <v>-0.14</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-6.61%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>42.80%</t>
+          <t>41.40%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>31.16</t>
+          <t>30.86</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H298"/>
+  <dimension ref="A1:H309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11169,10 +11169,8 @@
           <t>1.81%</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>36.55</t>
-        </is>
+      <c r="H288" t="n">
+        <v>36.55</v>
       </c>
     </row>
     <row r="289">
@@ -11207,11 +11205,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -11245,10 +11239,8 @@
           <t>11.67%</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>47.50</t>
-        </is>
+      <c r="H290" t="n">
+        <v>47.5</v>
       </c>
     </row>
     <row r="291">
@@ -11283,10 +11275,8 @@
           <t>3.33%</t>
         </is>
       </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t>17.24</t>
-        </is>
+      <c r="H291" t="n">
+        <v>17.24</v>
       </c>
     </row>
     <row r="292">
@@ -11321,10 +11311,8 @@
           <t>7.41%</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>16.56</t>
-        </is>
+      <c r="H292" t="n">
+        <v>16.56</v>
       </c>
     </row>
     <row r="293">
@@ -11359,10 +11347,8 @@
           <t>3.36%</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>20.17</t>
-        </is>
+      <c r="H293" t="n">
+        <v>20.17</v>
       </c>
     </row>
     <row r="294">
@@ -11397,11 +11383,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -11435,10 +11417,8 @@
           <t>1.36%</t>
         </is>
       </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>29.25</t>
-        </is>
+      <c r="H295" t="n">
+        <v>29.25</v>
       </c>
     </row>
     <row r="296">
@@ -11473,10 +11453,8 @@
           <t>3.51%</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>29.59</t>
-        </is>
+      <c r="H296" t="n">
+        <v>29.59</v>
       </c>
     </row>
     <row r="297">
@@ -11511,10 +11489,8 @@
           <t>11.07%</t>
         </is>
       </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>32.05</t>
-        </is>
+      <c r="H297" t="n">
+        <v>32.05</v>
       </c>
     </row>
     <row r="298">
@@ -11549,9 +11525,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>31.16</t>
+      <c r="H298" t="n">
+        <v>31.16</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>130</v>
+      </c>
+      <c r="D299" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>-9.72%</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>203.97%</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>2.01%</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>32.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="D300" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>0.73%</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>16.34%</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>29.85</v>
+      </c>
+      <c r="D301" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>-1.81%</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>11.89%</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>46.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>29.55</v>
+      </c>
+      <c r="D302" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>-1.5%</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>101.22%</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>3.38%</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>16.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>35.85</v>
+      </c>
+      <c r="D303" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>2.14%</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>14.41%</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>7.25%</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>16.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="D304" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>18.49%</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>3.32%</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>20.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="D305" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>3.36%</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>163.57%</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="D306" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>-0.95%</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>97.64%</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>1.37%</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>28.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="D307" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>-0.77%</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>91.17%</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>3.54%</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>29.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="D308" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>-3.31%</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>120.12%</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>11.45%</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>30.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="D309" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>-0.98%</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>41.40%</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>30.86</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>130</v>
+        <v>134.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-14</v>
+        <v>4.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-9.72%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>203.97%</t>
+          <t>214.49%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>32.91</t>
+          <t>34.14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.65</v>
+        <v>22.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0.15</v>
+        <v>1.65</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>7.99%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.34%</t>
+          <t>25.63%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.85</v>
+        <v>30.65</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.55</v>
+        <v>0.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>2.68%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>3.10%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.89%</t>
+          <t>11.58%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>47.89</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29.55</v>
+        <v>29.7</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.45</v>
+        <v>0.15</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>101.22%</t>
+          <t>102.24%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.37%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>17.07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35.85</v>
+        <v>36.95</v>
       </c>
       <c r="D6" t="n">
-        <v>0.75</v>
+        <v>1.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14.41%</t>
+          <t>17.92%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.25%</t>
+          <t>7.04%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>17.43</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>48.2</v>
+        <v>48.6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.49%</t>
+          <t>19.48%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.32%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.59</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18.45</v>
+        <v>19.1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.36%</t>
+          <t>3.52%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>163.57%</t>
+          <t>172.86%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>99.2</v>
+        <v>102.5</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.95</v>
+        <v>3.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>97.64%</t>
+          <t>104.22%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>28.97</t>
+          <t>29.93</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>83.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.65</v>
+        <v>3.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>3.96%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>91.17%</t>
+          <t>98.74%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>3.40%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>30.52</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>34.5</v>
+        <v>36.11</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.18</v>
+        <v>1.61</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-3.31%</t>
+          <t>4.67%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>120.12%</t>
+          <t>130.39%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.45%</t>
+          <t>10.94%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>32.43</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.14</v>
+        <v>14.76</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.14</v>
+        <v>0.62</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.98%</t>
+          <t>4.38%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>41.40%</t>
+          <t>47.60%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>32.21</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H309"/>
+  <dimension ref="A1:H320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11561,10 +11561,8 @@
           <t>2.01%</t>
         </is>
       </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>32.91</t>
-        </is>
+      <c r="H299" t="n">
+        <v>32.91</v>
       </c>
     </row>
     <row r="300">
@@ -11599,11 +11597,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -11637,10 +11631,8 @@
           <t>11.89%</t>
         </is>
       </c>
-      <c r="H301" t="inlineStr">
-        <is>
-          <t>46.64</t>
-        </is>
+      <c r="H301" t="n">
+        <v>46.64</v>
       </c>
     </row>
     <row r="302">
@@ -11675,10 +11667,8 @@
           <t>3.38%</t>
         </is>
       </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>16.98</t>
-        </is>
+      <c r="H302" t="n">
+        <v>16.98</v>
       </c>
     </row>
     <row r="303">
@@ -11713,10 +11703,8 @@
           <t>7.25%</t>
         </is>
       </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t>16.91</t>
-        </is>
+      <c r="H303" t="n">
+        <v>16.91</v>
       </c>
     </row>
     <row r="304">
@@ -11751,10 +11739,8 @@
           <t>3.32%</t>
         </is>
       </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>20.42</t>
-        </is>
+      <c r="H304" t="n">
+        <v>20.42</v>
       </c>
     </row>
     <row r="305">
@@ -11789,11 +11775,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -11827,10 +11809,8 @@
           <t>1.37%</t>
         </is>
       </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>28.97</t>
-        </is>
+      <c r="H306" t="n">
+        <v>28.97</v>
       </c>
     </row>
     <row r="307">
@@ -11865,10 +11845,8 @@
           <t>3.54%</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>29.36</t>
-        </is>
+      <c r="H307" t="n">
+        <v>29.36</v>
       </c>
     </row>
     <row r="308">
@@ -11903,10 +11881,8 @@
           <t>11.45%</t>
         </is>
       </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>30.99</t>
-        </is>
+      <c r="H308" t="n">
+        <v>30.99</v>
       </c>
     </row>
     <row r="309">
@@ -11941,9 +11917,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>30.86</t>
+      <c r="H309" t="n">
+        <v>30.86</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="D310" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>3.46%</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>214.49%</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>1.94%</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>34.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D311" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>7.99%</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>25.63%</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="D312" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>2.68%</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>3.10%</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>11.58%</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>47.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="D313" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>102.24%</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>17.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="D314" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>17.92%</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>7.04%</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>17.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="D315" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>0.83%</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>19.48%</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>3.29%</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>20.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="D316" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>3.52%</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>172.86%</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="D317" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>3.33%</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>104.22%</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>0.98%</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>29.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="D318" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>3.96%</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>98.74%</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>3.40%</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>30.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>36.11</v>
+      </c>
+      <c r="D319" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>4.67%</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>130.39%</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>10.94%</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>32.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>14.76</v>
+      </c>
+      <c r="D320" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>4.38%</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>47.60%</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>32.21</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>134.5</v>
+        <v>139</v>
       </c>
       <c r="D2" t="n">
         <v>4.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>214.49%</t>
+          <t>228.79%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.88%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>34.14</t>
+          <t>35.28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.3</v>
+        <v>23.9</v>
       </c>
       <c r="D3" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.99%</t>
+          <t>7.17%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.63%</t>
+          <t>39.36%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30.65</v>
+        <v>30.4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8</v>
+        <v>-0.25</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>-0.82%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>5.17%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.58%</t>
+          <t>11.67%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>47.89</t>
+          <t>51.53</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29.7</v>
+        <v>30.45</v>
       </c>
       <c r="D5" t="n">
-        <v>0.15</v>
+        <v>0.75</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>2.53%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>102.24%</t>
+          <t>109.39%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.37%</t>
+          <t>3.28%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>17.50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36.95</v>
+        <v>36.05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1</v>
+        <v>-0.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>-2.44%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.92%</t>
+          <t>13.18%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>3.88%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>48.6</v>
+        <v>48.2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4</v>
+        <v>-0.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>-0.82%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.48%</t>
+          <t>17.24%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>20.42</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.1</v>
+        <v>19.45</v>
       </c>
       <c r="D8" t="n">
-        <v>0.65</v>
+        <v>0.35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>172.86%</t>
+          <t>182.29%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>102.5</v>
+        <v>103.85</v>
       </c>
       <c r="D9" t="n">
-        <v>3.3</v>
+        <v>1.35</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>104.22%</t>
+          <t>109.61%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>29.93</t>
+          <t>30.33</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>86.7</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.96%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>98.74%</t>
+          <t>104.19%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.34%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>31.12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.11</v>
+        <v>37.2</v>
       </c>
       <c r="D11" t="n">
-        <v>1.61</v>
+        <v>1.09</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4.67%</t>
+          <t>3.02%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>130.39%</t>
+          <t>140.45%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.94%</t>
+          <t>10.62%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>33.41</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.76</v>
+        <v>15.04</v>
       </c>
       <c r="D12" t="n">
-        <v>0.62</v>
+        <v>0.28</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4.38%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>47.60%</t>
+          <t>50.40%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>32.82</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H320"/>
+  <dimension ref="A1:H331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11953,10 +11953,8 @@
           <t>1.94%</t>
         </is>
       </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>34.14</t>
-        </is>
+      <c r="H310" t="n">
+        <v>34.14</v>
       </c>
     </row>
     <row r="311">
@@ -11991,11 +11989,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -12029,10 +12023,8 @@
           <t>11.58%</t>
         </is>
       </c>
-      <c r="H312" t="inlineStr">
-        <is>
-          <t>47.89</t>
-        </is>
+      <c r="H312" t="n">
+        <v>47.89</v>
       </c>
     </row>
     <row r="313">
@@ -12067,10 +12059,8 @@
           <t>3.37%</t>
         </is>
       </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>17.07</t>
-        </is>
+      <c r="H313" t="n">
+        <v>17.07</v>
       </c>
     </row>
     <row r="314">
@@ -12105,10 +12095,8 @@
           <t>7.04%</t>
         </is>
       </c>
-      <c r="H314" t="inlineStr">
-        <is>
-          <t>17.43</t>
-        </is>
+      <c r="H314" t="n">
+        <v>17.43</v>
       </c>
     </row>
     <row r="315">
@@ -12143,10 +12131,8 @@
           <t>3.29%</t>
         </is>
       </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>20.59</t>
-        </is>
+      <c r="H315" t="n">
+        <v>20.59</v>
       </c>
     </row>
     <row r="316">
@@ -12181,11 +12167,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -12219,10 +12201,8 @@
           <t>0.98%</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t>29.93</t>
-        </is>
+      <c r="H317" t="n">
+        <v>29.93</v>
       </c>
     </row>
     <row r="318">
@@ -12257,10 +12237,8 @@
           <t>3.40%</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>30.52</t>
-        </is>
+      <c r="H318" t="n">
+        <v>30.52</v>
       </c>
     </row>
     <row r="319">
@@ -12295,10 +12273,8 @@
           <t>10.94%</t>
         </is>
       </c>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t>32.43</t>
-        </is>
+      <c r="H319" t="n">
+        <v>32.43</v>
       </c>
     </row>
     <row r="320">
@@ -12333,9 +12309,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t>32.21</t>
+      <c r="H320" t="n">
+        <v>32.21</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>139</v>
+      </c>
+      <c r="D321" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>3.35%</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>228.79%</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>1.88%</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>35.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D322" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>7.17%</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>39.36%</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="D323" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>-0.82%</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>5.17%</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>11.67%</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>51.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>30.45</v>
+      </c>
+      <c r="D324" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>2.53%</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>109.39%</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>3.28%</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>17.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>36.05</v>
+      </c>
+      <c r="D325" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-2.44%</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>13.18%</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>3.88%</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="D326" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>-0.82%</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>17.24%</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>3.32%</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>20.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="D327" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>1.83%</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>182.29%</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="D328" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>1.32%</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>109.61%</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>1.54%</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>30.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="D329" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>1.96%</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>104.19%</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>3.34%</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>31.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="D330" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>3.02%</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>140.45%</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>10.62%</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>33.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="D331" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>50.40%</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>32.82</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,19 +483,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>139</v>
+        <v>138.5</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5</v>
+        <v>-0.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>228.79%</t>
+          <t>220.89%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -505,14 +505,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>35.28</t>
+          <t>35.24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23.9</v>
+        <v>22.4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6</v>
+        <v>-1.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.17%</t>
+          <t>-6.28%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39.36%</t>
+          <t>29.48%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.25</v>
+        <v>0.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.82%</t>
+          <t>2.38%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5.17%</t>
+          <t>6.06%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.67%</t>
+          <t>15.11%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>51.53</t>
+          <t>51.02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,14 +597,14 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.45</v>
+        <v>30.85</v>
       </c>
       <c r="D5" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -614,19 +614,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>3.24%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.50</t>
+          <t>17.73</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36.05</v>
+        <v>35.65</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-2.44%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13.18%</t>
+          <t>12.44%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.88%</t>
+          <t>3.93%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>16.82</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>48.2</v>
+        <v>48.15</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4</v>
+        <v>-0.05</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.82%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.24%</t>
+          <t>16.58%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -695,14 +695,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.40</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.45</v>
+        <v>18.35</v>
       </c>
       <c r="D8" t="n">
-        <v>0.35</v>
+        <v>-1.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>-5.66%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>182.29%</t>
+          <t>159.18%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>103.85</v>
+        <v>103.9</v>
       </c>
       <c r="D9" t="n">
-        <v>1.35</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>109.61%</t>
+          <t>109.09%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -771,14 +771,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>30.34</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>88.40000000000001</v>
+        <v>88.55</v>
       </c>
       <c r="D10" t="n">
-        <v>1.7</v>
+        <v>0.15</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>104.19%</t>
+          <t>102.98%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.12</t>
+          <t>31.17</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37.2</v>
+        <v>36.94</v>
       </c>
       <c r="D11" t="n">
-        <v>1.09</v>
+        <v>-0.26</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>140.45%</t>
+          <t>136.08%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.62%</t>
+          <t>10.69%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.18</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.04</v>
+        <v>15.08</v>
       </c>
       <c r="D12" t="n">
-        <v>0.28</v>
+        <v>0.04</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50.40%</t>
+          <t>50.80%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32.82</t>
+          <t>32.91</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H331"/>
+  <dimension ref="A1:H342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12345,10 +12345,8 @@
           <t>1.88%</t>
         </is>
       </c>
-      <c r="H321" t="inlineStr">
-        <is>
-          <t>35.28</t>
-        </is>
+      <c r="H321" t="n">
+        <v>35.28</v>
       </c>
     </row>
     <row r="322">
@@ -12383,11 +12381,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H322" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -12421,10 +12415,8 @@
           <t>11.67%</t>
         </is>
       </c>
-      <c r="H323" t="inlineStr">
-        <is>
-          <t>51.53</t>
-        </is>
+      <c r="H323" t="n">
+        <v>51.53</v>
       </c>
     </row>
     <row r="324">
@@ -12459,10 +12451,8 @@
           <t>3.28%</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>17.50</t>
-        </is>
+      <c r="H324" t="n">
+        <v>17.5</v>
       </c>
     </row>
     <row r="325">
@@ -12497,10 +12487,8 @@
           <t>3.88%</t>
         </is>
       </c>
-      <c r="H325" t="inlineStr">
-        <is>
-          <t>17.00</t>
-        </is>
+      <c r="H325" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="326">
@@ -12535,10 +12523,8 @@
           <t>3.32%</t>
         </is>
       </c>
-      <c r="H326" t="inlineStr">
-        <is>
-          <t>20.42</t>
-        </is>
+      <c r="H326" t="n">
+        <v>20.42</v>
       </c>
     </row>
     <row r="327">
@@ -12573,11 +12559,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H327" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -12611,10 +12593,8 @@
           <t>1.54%</t>
         </is>
       </c>
-      <c r="H328" t="inlineStr">
-        <is>
-          <t>30.33</t>
-        </is>
+      <c r="H328" t="n">
+        <v>30.33</v>
       </c>
     </row>
     <row r="329">
@@ -12649,10 +12629,8 @@
           <t>3.34%</t>
         </is>
       </c>
-      <c r="H329" t="inlineStr">
-        <is>
-          <t>31.12</t>
-        </is>
+      <c r="H329" t="n">
+        <v>31.12</v>
       </c>
     </row>
     <row r="330">
@@ -12687,10 +12665,8 @@
           <t>10.62%</t>
         </is>
       </c>
-      <c r="H330" t="inlineStr">
-        <is>
-          <t>33.41</t>
-        </is>
+      <c r="H330" t="n">
+        <v>33.41</v>
       </c>
     </row>
     <row r="331">
@@ -12725,9 +12701,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>32.82</t>
+      <c r="H331" t="n">
+        <v>32.82</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="D332" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>-0.36%</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>220.89%</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>1.88%</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>35.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="D333" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>-6.28%</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>29.48%</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>2.38%</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>6.06%</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>15.11%</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>51.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="D335" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>1.31%</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>109.39%</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>3.24%</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>17.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="D336" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>-1.11%</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>12.44%</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>3.93%</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>16.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="D337" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>16.58%</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>3.32%</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>20.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="D338" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>-5.66%</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>159.18%</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="D339" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>109.09%</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>1.54%</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>30.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>88.55</v>
+      </c>
+      <c r="D340" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>102.98%</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>3.33%</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>31.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="D341" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>136.08%</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>10.69%</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>33.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="D342" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>50.80%</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>32.91</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>138.5</v>
+        <v>128</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5</v>
+        <v>-10.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>-7.58%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>220.89%</t>
+          <t>199.29%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>32.57</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.4</v>
+        <v>22.1</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.5</v>
+        <v>-0.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-6.28%</t>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.48%</t>
+          <t>27.01%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30.1</v>
+        <v>29.2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7</v>
+        <v>-0.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>6.06%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>15.11%</t>
+          <t>10.94%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>49.49</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.85</v>
+        <v>30.65</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>109.39%</t>
+          <t>108.71%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>3.26%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>17.61</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35.65</v>
+        <v>35.95</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-1.11%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>12.44%</t>
+          <t>14.07%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.93%</t>
+          <t>3.89%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.96</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>48.15</v>
+        <v>48.45</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05</v>
+        <v>0.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16.58%</t>
+          <t>17.44%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.32%</t>
+          <t>3.30%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.40</t>
+          <t>20.53</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18.35</v>
+        <v>18.3</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-5.66%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>159.18%</t>
+          <t>161.80%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>103.9</v>
+        <v>101.7</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>-2.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>-2.12%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>109.09%</t>
+          <t>103.46%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>30.83</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>88.55</v>
+        <v>86.7</v>
       </c>
       <c r="D10" t="n">
-        <v>0.15</v>
+        <v>-1.85</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>102.98%</t>
+          <t>97.83%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.40%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>30.52</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.94</v>
+        <v>35.9</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.26</v>
+        <v>-1.04</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-2.82%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>136.08%</t>
+          <t>128.41%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.69%</t>
+          <t>11.00%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>32.24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.08</v>
+        <v>14.72</v>
       </c>
       <c r="D12" t="n">
-        <v>0.04</v>
+        <v>-0.36</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>-2.39%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50.80%</t>
+          <t>47.20%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32.91</t>
+          <t>32.12</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H342"/>
+  <dimension ref="A1:H353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12737,10 +12737,8 @@
           <t>1.88%</t>
         </is>
       </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>35.24</t>
-        </is>
+      <c r="H332" t="n">
+        <v>35.24</v>
       </c>
     </row>
     <row r="333">
@@ -12775,11 +12773,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -12813,10 +12807,8 @@
           <t>15.11%</t>
         </is>
       </c>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t>51.02</t>
-        </is>
+      <c r="H334" t="n">
+        <v>51.02</v>
       </c>
     </row>
     <row r="335">
@@ -12851,10 +12843,8 @@
           <t>3.24%</t>
         </is>
       </c>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>17.73</t>
-        </is>
+      <c r="H335" t="n">
+        <v>17.73</v>
       </c>
     </row>
     <row r="336">
@@ -12889,10 +12879,8 @@
           <t>3.93%</t>
         </is>
       </c>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>16.82</t>
-        </is>
+      <c r="H336" t="n">
+        <v>16.82</v>
       </c>
     </row>
     <row r="337">
@@ -12927,10 +12915,8 @@
           <t>3.32%</t>
         </is>
       </c>
-      <c r="H337" t="inlineStr">
-        <is>
-          <t>20.40</t>
-        </is>
+      <c r="H337" t="n">
+        <v>20.4</v>
       </c>
     </row>
     <row r="338">
@@ -12965,11 +12951,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -13003,10 +12985,8 @@
           <t>1.54%</t>
         </is>
       </c>
-      <c r="H339" t="inlineStr">
-        <is>
-          <t>30.34</t>
-        </is>
+      <c r="H339" t="n">
+        <v>30.34</v>
       </c>
     </row>
     <row r="340">
@@ -13041,10 +13021,8 @@
           <t>3.33%</t>
         </is>
       </c>
-      <c r="H340" t="inlineStr">
-        <is>
-          <t>31.17</t>
-        </is>
+      <c r="H340" t="n">
+        <v>31.17</v>
       </c>
     </row>
     <row r="341">
@@ -13079,10 +13057,8 @@
           <t>10.69%</t>
         </is>
       </c>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t>33.18</t>
-        </is>
+      <c r="H341" t="n">
+        <v>33.18</v>
       </c>
     </row>
     <row r="342">
@@ -13117,9 +13093,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H342" t="inlineStr">
-        <is>
-          <t>32.91</t>
+      <c r="H342" t="n">
+        <v>32.91</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>128</v>
+      </c>
+      <c r="D343" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>-7.58%</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>199.29%</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>2.04%</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>32.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="D344" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>-1.34%</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>27.01%</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="D345" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>-2.99%</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>0.31%</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>10.94%</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>49.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="D346" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>-0.65%</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>108.71%</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>3.26%</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>17.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>35.95</v>
+      </c>
+      <c r="D347" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>0.84%</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>14.07%</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>3.89%</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>16.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>48.45</v>
+      </c>
+      <c r="D348" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>17.44%</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>3.30%</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>20.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D349" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-0.27%</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>161.80%</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="D350" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>-2.12%</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>103.46%</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>1.57%</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>30.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="D351" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-2.09%</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>97.83%</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>3.40%</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>30.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="D352" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-2.82%</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>128.41%</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>11.00%</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>32.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="D353" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-2.39%</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>47.20%</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>32.12</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D2" t="n">
-        <v>-10.5</v>
+        <v>-2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-7.58%</t>
+          <t>-1.56%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>199.29%</t>
+          <t>194.61%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>32.57</t>
+          <t>31.98</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3</v>
+        <v>2.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.34%</t>
+          <t>9.95%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>27.01%</t>
+          <t>39.66%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.2</v>
+        <v>28.75</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.9</v>
+        <v>-0.45</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-2.99%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.94%</t>
+          <t>11.11%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>49.49</t>
+          <t>48.73</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.65</v>
+        <v>30.7</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2</v>
+        <v>0.05</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>108.71%</t>
+          <t>111.11%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -619,14 +619,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>17.64</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35.95</v>
+        <v>36.4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14.07%</t>
+          <t>17.83%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>3.85%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>17.17</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>48.45</v>
+        <v>49.4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3</v>
+        <v>0.95</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.44%</t>
+          <t>20.02%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.24%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.93</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18.3</v>
+        <v>17.85</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>-0.45</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>-2.46%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>161.80%</t>
+          <t>155.73%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>101.7</v>
+        <v>101.45</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2</v>
+        <v>-0.25</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-2.12%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>103.46%</t>
+          <t>102.76%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30.83</t>
+          <t>30.76</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -790,16 +790,16 @@
         <v>86.7</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.85</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-2.09%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>97.83%</t>
+          <t>97.40%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -809,14 +809,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>29.04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35.9</v>
+        <v>35.83</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>128.41%</t>
+          <t>129.12%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.00%</t>
+          <t>11.02%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>32.24</t>
+          <t>28.95</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.72</v>
+        <v>14.68</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.36</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-2.39%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>47.20%</t>
+          <t>46.80%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>31.03</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H353"/>
+  <dimension ref="A1:H364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13129,10 +13129,8 @@
           <t>2.04%</t>
         </is>
       </c>
-      <c r="H343" t="inlineStr">
-        <is>
-          <t>32.57</t>
-        </is>
+      <c r="H343" t="n">
+        <v>32.57</v>
       </c>
     </row>
     <row r="344">
@@ -13167,11 +13165,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H344" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -13205,10 +13199,8 @@
           <t>10.94%</t>
         </is>
       </c>
-      <c r="H345" t="inlineStr">
-        <is>
-          <t>49.49</t>
-        </is>
+      <c r="H345" t="n">
+        <v>49.49</v>
       </c>
     </row>
     <row r="346">
@@ -13243,10 +13235,8 @@
           <t>3.26%</t>
         </is>
       </c>
-      <c r="H346" t="inlineStr">
-        <is>
-          <t>17.61</t>
-        </is>
+      <c r="H346" t="n">
+        <v>17.61</v>
       </c>
     </row>
     <row r="347">
@@ -13281,10 +13271,8 @@
           <t>3.89%</t>
         </is>
       </c>
-      <c r="H347" t="inlineStr">
-        <is>
-          <t>16.96</t>
-        </is>
+      <c r="H347" t="n">
+        <v>16.96</v>
       </c>
     </row>
     <row r="348">
@@ -13319,10 +13307,8 @@
           <t>3.30%</t>
         </is>
       </c>
-      <c r="H348" t="inlineStr">
-        <is>
-          <t>20.53</t>
-        </is>
+      <c r="H348" t="n">
+        <v>20.53</v>
       </c>
     </row>
     <row r="349">
@@ -13357,11 +13343,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H349" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -13395,10 +13377,8 @@
           <t>1.57%</t>
         </is>
       </c>
-      <c r="H350" t="inlineStr">
-        <is>
-          <t>30.83</t>
-        </is>
+      <c r="H350" t="n">
+        <v>30.83</v>
       </c>
     </row>
     <row r="351">
@@ -13433,10 +13413,8 @@
           <t>3.40%</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t>30.52</t>
-        </is>
+      <c r="H351" t="n">
+        <v>30.52</v>
       </c>
     </row>
     <row r="352">
@@ -13471,10 +13449,8 @@
           <t>11.00%</t>
         </is>
       </c>
-      <c r="H352" t="inlineStr">
-        <is>
-          <t>32.24</t>
-        </is>
+      <c r="H352" t="n">
+        <v>32.24</v>
       </c>
     </row>
     <row r="353">
@@ -13509,9 +13485,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H353" t="inlineStr">
-        <is>
-          <t>32.12</t>
+      <c r="H353" t="n">
+        <v>32.12</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>126</v>
+      </c>
+      <c r="D354" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-1.56%</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>194.61%</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>2.07%</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>31.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="D355" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>9.95%</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>39.66%</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="D356" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-1.54%</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>-1.80%</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>11.11%</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>48.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="D357" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>111.11%</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>3.26%</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>17.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="D358" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>1.25%</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>17.83%</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>17.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="D359" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>1.96%</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>20.02%</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>3.24%</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>20.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="D360" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-2.46%</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>155.73%</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D361" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-0.25%</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>102.76%</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>1.58%</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>30.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="D362" t="n">
+        <v>0</v>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>97.40%</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>3.40%</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>29.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>35.83</v>
+      </c>
+      <c r="D363" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>-0.19%</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>129.12%</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>11.02%</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>28.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="D364" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>-0.27%</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>46.80%</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>31.03</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>126</v>
+        <v>113.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-2</v>
+        <v>-12.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>-9.92%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>194.61%</t>
+          <t>165.38%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>28.81</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24.3</v>
+        <v>23.6</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2</v>
+        <v>-0.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.95%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39.66%</t>
+          <t>35.63%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.75</v>
+        <v>27.7</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.45</v>
+        <v>-1.05</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>-3.65%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>-5.39%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.11%</t>
+          <t>11.53%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>48.73</t>
+          <t>46.95</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.7</v>
+        <v>29.6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05</v>
+        <v>-1.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>-3.58%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>111.11%</t>
+          <t>103.55%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.64</t>
+          <t>17.01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36.4</v>
+        <v>36.25</v>
       </c>
       <c r="D6" t="n">
-        <v>0.45</v>
+        <v>-0.15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.83%</t>
+          <t>17.35%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.85%</t>
+          <t>3.86%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>17.10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49.4</v>
+        <v>49.45</v>
       </c>
       <c r="D7" t="n">
-        <v>0.95</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.02%</t>
+          <t>20.14%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -695,14 +695,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>20.95</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.85</v>
+        <v>16.85</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.45</v>
+        <v>-1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-2.46%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>155.73%</t>
+          <t>141.40%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>101.45</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.25</v>
+        <v>-4.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-4.24%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>102.76%</t>
+          <t>94.16%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>29.45</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>86.7</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-4.35</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-5.02%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>97.40%</t>
+          <t>87.50%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.58%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>29.04</t>
+          <t>27.59</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35.83</v>
+        <v>33.41</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-2.42</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-6.75%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>129.12%</t>
+          <t>113.64%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.02%</t>
+          <t>11.82%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>27.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.68</v>
+        <v>13.94</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.04</v>
+        <v>-0.74</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>-5.04%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>46.80%</t>
+          <t>39.40%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>29.47</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H364"/>
+  <dimension ref="A1:H375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13521,10 +13521,8 @@
           <t>2.07%</t>
         </is>
       </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t>31.98</t>
-        </is>
+      <c r="H354" t="n">
+        <v>31.98</v>
       </c>
     </row>
     <row r="355">
@@ -13559,11 +13557,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -13597,10 +13591,8 @@
           <t>11.11%</t>
         </is>
       </c>
-      <c r="H356" t="inlineStr">
-        <is>
-          <t>48.73</t>
-        </is>
+      <c r="H356" t="n">
+        <v>48.73</v>
       </c>
     </row>
     <row r="357">
@@ -13635,10 +13627,8 @@
           <t>3.26%</t>
         </is>
       </c>
-      <c r="H357" t="inlineStr">
-        <is>
-          <t>17.64</t>
-        </is>
+      <c r="H357" t="n">
+        <v>17.64</v>
       </c>
     </row>
     <row r="358">
@@ -13673,10 +13663,8 @@
           <t>3.85%</t>
         </is>
       </c>
-      <c r="H358" t="inlineStr">
-        <is>
-          <t>17.17</t>
-        </is>
+      <c r="H358" t="n">
+        <v>17.17</v>
       </c>
     </row>
     <row r="359">
@@ -13711,10 +13699,8 @@
           <t>3.24%</t>
         </is>
       </c>
-      <c r="H359" t="inlineStr">
-        <is>
-          <t>20.93</t>
-        </is>
+      <c r="H359" t="n">
+        <v>20.93</v>
       </c>
     </row>
     <row r="360">
@@ -13749,11 +13735,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H360" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -13787,10 +13769,8 @@
           <t>1.58%</t>
         </is>
       </c>
-      <c r="H361" t="inlineStr">
-        <is>
-          <t>30.76</t>
-        </is>
+      <c r="H361" t="n">
+        <v>30.76</v>
       </c>
     </row>
     <row r="362">
@@ -13825,10 +13805,8 @@
           <t>3.40%</t>
         </is>
       </c>
-      <c r="H362" t="inlineStr">
-        <is>
-          <t>29.04</t>
-        </is>
+      <c r="H362" t="n">
+        <v>29.04</v>
       </c>
     </row>
     <row r="363">
@@ -13863,10 +13841,8 @@
           <t>11.02%</t>
         </is>
       </c>
-      <c r="H363" t="inlineStr">
-        <is>
-          <t>28.95</t>
-        </is>
+      <c r="H363" t="n">
+        <v>28.95</v>
       </c>
     </row>
     <row r="364">
@@ -13901,9 +13877,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H364" t="inlineStr">
-        <is>
-          <t>31.03</t>
+      <c r="H364" t="n">
+        <v>31.03</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="D365" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>-9.92%</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>165.38%</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>2.30%</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>28.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="D366" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>-2.88%</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>35.63%</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="D367" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>-3.65%</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>-5.39%</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>11.53%</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>46.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="D368" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>-3.58%</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>103.55%</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>3.38%</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>17.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="D369" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>17.35%</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>3.86%</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>17.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="D370" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>20.14%</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>3.24%</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>20.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="D371" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>-5.6%</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>141.40%</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>97.15000000000001</v>
+      </c>
+      <c r="D372" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>-4.24%</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>94.16%</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>1.65%</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>82.34999999999999</v>
+      </c>
+      <c r="D373" t="n">
+        <v>-4.35</v>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>-5.02%</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>87.50%</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>3.58%</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>27.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>33.41</v>
+      </c>
+      <c r="D374" t="n">
+        <v>-2.42</v>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>-6.75%</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>113.64%</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>11.82%</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>27.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="D375" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>-5.04%</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>39.40%</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>29.47</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>113.5</v>
+        <v>102.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-12.5</v>
+        <v>-11</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-9.92%</t>
+          <t>-9.69%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>165.38%</t>
+          <t>143.58%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.54%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>26.02</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23.6</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>35.63%</t>
+          <t>39.53%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>27.7</v>
+        <v>26.95</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.05</v>
+        <v>-0.75</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-3.65%</t>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-5.39%</t>
+          <t>-7.25%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.53%</t>
+          <t>11.86%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>45.68</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29.6</v>
+        <v>29.15</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1</v>
+        <v>-0.45</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-3.58%</t>
+          <t>-1.52%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>103.55%</t>
+          <t>101.78%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>16.75</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36.25</v>
+        <v>36.5</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.15</v>
+        <v>0.25</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.35%</t>
+          <t>19.08%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.86%</t>
+          <t>3.84%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17.10</t>
+          <t>17.22</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49.45</v>
+        <v>49.9</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>0.45</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.14%</t>
+          <t>21.52%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>21.14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.85</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>-1</v>
+        <v>-0.85</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.04%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>141.40%</t>
+          <t>132.90%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>97.15000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.3</v>
+        <v>-3.45</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-4.24%</t>
+          <t>-3.55%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>94.16%</t>
+          <t>89.50%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>28.41</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>82.34999999999999</v>
+        <v>78.75</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.35</v>
+        <v>-3.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-5.02%</t>
+          <t>-4.37%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>87.50%</t>
+          <t>81.26%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>26.38</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>33.41</v>
+        <v>31.59</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.42</v>
+        <v>-1.82</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-6.75%</t>
+          <t>-5.45%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>113.64%</t>
+          <t>103.96%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.82%</t>
+          <t>12.50%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>27.00</t>
+          <t>25.53</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13.94</v>
+        <v>13.35</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.74</v>
+        <v>-0.59</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-5.04%</t>
+          <t>-4.23%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>39.40%</t>
+          <t>33.50%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>28.22</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H375"/>
+  <dimension ref="A1:H386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13913,10 +13913,8 @@
           <t>2.30%</t>
         </is>
       </c>
-      <c r="H365" t="inlineStr">
-        <is>
-          <t>28.81</t>
-        </is>
+      <c r="H365" t="n">
+        <v>28.81</v>
       </c>
     </row>
     <row r="366">
@@ -13951,11 +13949,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H366" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -13989,10 +13983,8 @@
           <t>11.53%</t>
         </is>
       </c>
-      <c r="H367" t="inlineStr">
-        <is>
-          <t>46.95</t>
-        </is>
+      <c r="H367" t="n">
+        <v>46.95</v>
       </c>
     </row>
     <row r="368">
@@ -14027,10 +14019,8 @@
           <t>3.38%</t>
         </is>
       </c>
-      <c r="H368" t="inlineStr">
-        <is>
-          <t>17.01</t>
-        </is>
+      <c r="H368" t="n">
+        <v>17.01</v>
       </c>
     </row>
     <row r="369">
@@ -14065,10 +14055,8 @@
           <t>3.86%</t>
         </is>
       </c>
-      <c r="H369" t="inlineStr">
-        <is>
-          <t>17.10</t>
-        </is>
+      <c r="H369" t="n">
+        <v>17.1</v>
       </c>
     </row>
     <row r="370">
@@ -14103,10 +14091,8 @@
           <t>3.24%</t>
         </is>
       </c>
-      <c r="H370" t="inlineStr">
-        <is>
-          <t>20.95</t>
-        </is>
+      <c r="H370" t="n">
+        <v>20.95</v>
       </c>
     </row>
     <row r="371">
@@ -14141,11 +14127,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H371" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -14179,10 +14161,8 @@
           <t>1.65%</t>
         </is>
       </c>
-      <c r="H372" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
+      <c r="H372" t="n">
+        <v>29.45</v>
       </c>
     </row>
     <row r="373">
@@ -14217,10 +14197,8 @@
           <t>3.58%</t>
         </is>
       </c>
-      <c r="H373" t="inlineStr">
-        <is>
-          <t>27.59</t>
-        </is>
+      <c r="H373" t="n">
+        <v>27.59</v>
       </c>
     </row>
     <row r="374">
@@ -14255,10 +14233,8 @@
           <t>11.82%</t>
         </is>
       </c>
-      <c r="H374" t="inlineStr">
-        <is>
-          <t>27.00</t>
-        </is>
+      <c r="H374" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="375">
@@ -14293,9 +14269,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H375" t="inlineStr">
-        <is>
-          <t>29.47</t>
+      <c r="H375" t="n">
+        <v>29.47</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="D376" t="n">
+        <v>-11</v>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>-9.69%</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>143.58%</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>2.54%</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>26.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>24</v>
+      </c>
+      <c r="D377" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>39.53%</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="D378" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>-2.71%</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>-7.25%</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>11.86%</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>45.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="D379" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>-1.52%</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>101.78%</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>16.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="D380" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>19.08%</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>3.84%</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>17.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="D381" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>0.91%</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>21.52%</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>3.21%</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>21.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>16</v>
+      </c>
+      <c r="D382" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>-5.04%</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>132.90%</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="D383" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>-3.55%</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>89.50%</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>1.71%</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="D384" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>-4.37%</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>81.26%</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>26.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="D385" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>-5.45%</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>103.96%</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>12.50%</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>25.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="D386" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>-4.23%</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>33.50%</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>28.22</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>102.5</v>
+        <v>110</v>
       </c>
       <c r="D2" t="n">
-        <v>-11</v>
+        <v>7.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-9.69%</t>
+          <t>7.32%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>143.58%</t>
+          <t>162.94%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.37%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>16.69</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>21.6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4</v>
+        <v>-2.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39.53%</t>
+          <t>25.95%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26.95</v>
+        <v>26.45</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.75</v>
+        <v>-0.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-2.71%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-7.25%</t>
+          <t>-9.83%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.86%</t>
+          <t>12.08%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>45.68</t>
+          <t>44.83</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29.15</v>
+        <v>28.95</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.45</v>
+        <v>-0.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.52%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>101.78%</t>
+          <t>97.13%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.45%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>16.64</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36.5</v>
+        <v>37.7</v>
       </c>
       <c r="D6" t="n">
-        <v>0.25</v>
+        <v>1.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.08%</t>
+          <t>22.23%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.84%</t>
+          <t>3.71%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17.22</t>
+          <t>17.78</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49.9</v>
+        <v>51.5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.45</v>
+        <v>1.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.52%</t>
+          <t>24.83%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.11%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.82</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>15.65</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.85</v>
+        <v>-0.35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-5.04%</t>
+          <t>-2.19%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>132.90%</t>
+          <t>123.57%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>93.7</v>
+        <v>93.5</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.45</v>
+        <v>-0.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-3.55%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>89.50%</t>
+          <t>87.05%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -771,14 +771,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>28.35</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>78.75</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6</v>
+        <v>0.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-4.37%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>81.26%</t>
+          <t>79.96%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>3.74%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>26.41</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>31.59</v>
+        <v>31.43</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.82</v>
+        <v>-0.16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-5.45%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>103.96%</t>
+          <t>102.92%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>12.50%</t>
+          <t>12.57%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>25.40</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13.35</v>
+        <v>13.41</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.59</v>
+        <v>0.06</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-4.23%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>33.50%</t>
+          <t>34.10%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>28.22</t>
+          <t>28.34</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H386"/>
+  <dimension ref="A1:H397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14305,10 +14305,8 @@
           <t>2.54%</t>
         </is>
       </c>
-      <c r="H376" t="inlineStr">
-        <is>
-          <t>26.02</t>
-        </is>
+      <c r="H376" t="n">
+        <v>26.02</v>
       </c>
     </row>
     <row r="377">
@@ -14343,11 +14341,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -14381,10 +14375,8 @@
           <t>11.86%</t>
         </is>
       </c>
-      <c r="H378" t="inlineStr">
-        <is>
-          <t>45.68</t>
-        </is>
+      <c r="H378" t="n">
+        <v>45.68</v>
       </c>
     </row>
     <row r="379">
@@ -14419,10 +14411,8 @@
           <t>3.43%</t>
         </is>
       </c>
-      <c r="H379" t="inlineStr">
-        <is>
-          <t>16.75</t>
-        </is>
+      <c r="H379" t="n">
+        <v>16.75</v>
       </c>
     </row>
     <row r="380">
@@ -14457,10 +14447,8 @@
           <t>3.84%</t>
         </is>
       </c>
-      <c r="H380" t="inlineStr">
-        <is>
-          <t>17.22</t>
-        </is>
+      <c r="H380" t="n">
+        <v>17.22</v>
       </c>
     </row>
     <row r="381">
@@ -14495,10 +14483,8 @@
           <t>3.21%</t>
         </is>
       </c>
-      <c r="H381" t="inlineStr">
-        <is>
-          <t>21.14</t>
-        </is>
+      <c r="H381" t="n">
+        <v>21.14</v>
       </c>
     </row>
     <row r="382">
@@ -14533,11 +14519,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H382" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -14571,10 +14553,8 @@
           <t>1.71%</t>
         </is>
       </c>
-      <c r="H383" t="inlineStr">
-        <is>
-          <t>28.41</t>
-        </is>
+      <c r="H383" t="n">
+        <v>28.41</v>
       </c>
     </row>
     <row r="384">
@@ -14609,10 +14589,8 @@
           <t>3.75%</t>
         </is>
       </c>
-      <c r="H384" t="inlineStr">
-        <is>
-          <t>26.38</t>
-        </is>
+      <c r="H384" t="n">
+        <v>26.38</v>
       </c>
     </row>
     <row r="385">
@@ -14647,10 +14625,8 @@
           <t>12.50%</t>
         </is>
       </c>
-      <c r="H385" t="inlineStr">
-        <is>
-          <t>25.53</t>
-        </is>
+      <c r="H385" t="n">
+        <v>25.53</v>
       </c>
     </row>
     <row r="386">
@@ -14685,9 +14661,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H386" t="inlineStr">
-        <is>
-          <t>28.22</t>
+      <c r="H386" t="n">
+        <v>28.22</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>110</v>
+      </c>
+      <c r="D387" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>7.32%</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>162.94%</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>2.37%</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>16.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="D388" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>-10.0%</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>25.95%</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>26.45</v>
+      </c>
+      <c r="D389" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>-1.86%</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>-9.83%</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>12.08%</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>44.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>28.95</v>
+      </c>
+      <c r="D390" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>-0.69%</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>97.13%</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>16.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="D391" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>3.29%</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>22.23%</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>3.71%</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>17.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="D392" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>3.21%</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>24.83%</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>3.11%</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>21.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="D393" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>-2.19%</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>123.57%</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="D394" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>87.05%</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>1.71%</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>28.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>78.84999999999999</v>
+      </c>
+      <c r="D395" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>0.13%</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>79.96%</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>3.74%</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>26.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="D396" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>-0.51%</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>102.92%</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>12.57%</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>25.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="D397" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>34.10%</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>28.34</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7.32%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>162.94%</t>
+          <t>196.20%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.16%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>18.36</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.6</v>
+        <v>21.25</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.4</v>
+        <v>-0.35</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>-1.62%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.95%</t>
+          <t>28.79%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26.45</v>
+        <v>27.35</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5</v>
+        <v>0.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.86%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-9.83%</t>
+          <t>-4.96%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>12.08%</t>
+          <t>11.68%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>44.83</t>
+          <t>46.36</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.95</v>
+        <v>30.85</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2</v>
+        <v>1.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>6.56%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>97.13%</t>
+          <t>112.15%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.24%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>16.64</t>
+          <t>17.73</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37.7</v>
+        <v>38.65</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2</v>
+        <v>0.95</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>2.52%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.23%</t>
+          <t>25.70%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.71%</t>
+          <t>3.62%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>18.23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>51.5</v>
+        <v>53.1</v>
       </c>
       <c r="D7" t="n">
         <v>1.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.11%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.83%</t>
+          <t>29.47%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.01%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.50</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15.65</v>
+        <v>16.3</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.35</v>
+        <v>0.65</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>4.15%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>123.57%</t>
+          <t>129.58%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>93.5</v>
+        <v>102.85</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2</v>
+        <v>9.35</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>87.05%</t>
+          <t>103.56%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>31.18</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>78.84999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1</v>
+        <v>7.05</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>8.94%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>79.96%</t>
+          <t>94.19%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>28.78</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>31.43</v>
+        <v>34.49</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.16</v>
+        <v>3.06</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>9.74%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>102.92%</t>
+          <t>121.92%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>12.57%</t>
+          <t>11.45%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>25.40</t>
+          <t>27.87</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13.41</v>
+        <v>14.65</v>
       </c>
       <c r="D12" t="n">
-        <v>0.06</v>
+        <v>1.24</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>9.25%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>34.10%</t>
+          <t>46.50%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>28.34</t>
+          <t>30.97</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H397"/>
+  <dimension ref="A1:H408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14697,10 +14697,8 @@
           <t>2.37%</t>
         </is>
       </c>
-      <c r="H387" t="inlineStr">
-        <is>
-          <t>16.69</t>
-        </is>
+      <c r="H387" t="n">
+        <v>16.69</v>
       </c>
     </row>
     <row r="388">
@@ -14735,11 +14733,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H388" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -14773,10 +14767,8 @@
           <t>12.08%</t>
         </is>
       </c>
-      <c r="H389" t="inlineStr">
-        <is>
-          <t>44.83</t>
-        </is>
+      <c r="H389" t="n">
+        <v>44.83</v>
       </c>
     </row>
     <row r="390">
@@ -14811,10 +14803,8 @@
           <t>3.45%</t>
         </is>
       </c>
-      <c r="H390" t="inlineStr">
-        <is>
-          <t>16.64</t>
-        </is>
+      <c r="H390" t="n">
+        <v>16.64</v>
       </c>
     </row>
     <row r="391">
@@ -14849,10 +14839,8 @@
           <t>3.71%</t>
         </is>
       </c>
-      <c r="H391" t="inlineStr">
-        <is>
-          <t>17.78</t>
-        </is>
+      <c r="H391" t="n">
+        <v>17.78</v>
       </c>
     </row>
     <row r="392">
@@ -14887,10 +14875,8 @@
           <t>3.11%</t>
         </is>
       </c>
-      <c r="H392" t="inlineStr">
-        <is>
-          <t>21.82</t>
-        </is>
+      <c r="H392" t="n">
+        <v>21.82</v>
       </c>
     </row>
     <row r="393">
@@ -14925,11 +14911,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H393" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -14963,10 +14945,8 @@
           <t>1.71%</t>
         </is>
       </c>
-      <c r="H394" t="inlineStr">
-        <is>
-          <t>28.35</t>
-        </is>
+      <c r="H394" t="n">
+        <v>28.35</v>
       </c>
     </row>
     <row r="395">
@@ -15001,10 +14981,8 @@
           <t>3.74%</t>
         </is>
       </c>
-      <c r="H395" t="inlineStr">
-        <is>
-          <t>26.41</t>
-        </is>
+      <c r="H395" t="n">
+        <v>26.41</v>
       </c>
     </row>
     <row r="396">
@@ -15039,10 +15017,8 @@
           <t>12.57%</t>
         </is>
       </c>
-      <c r="H396" t="inlineStr">
-        <is>
-          <t>25.40</t>
-        </is>
+      <c r="H396" t="n">
+        <v>25.4</v>
       </c>
     </row>
     <row r="397">
@@ -15077,9 +15053,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H397" t="inlineStr">
-        <is>
-          <t>28.34</t>
+      <c r="H397" t="n">
+        <v>28.34</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>121</v>
+      </c>
+      <c r="D398" t="n">
+        <v>11</v>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>196.20%</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>2.16%</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>18.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="D399" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>-1.62%</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>28.79%</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="D400" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>-4.96%</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>11.68%</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>46.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="D401" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>6.56%</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>112.15%</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>3.24%</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>17.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="D402" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>2.52%</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>25.70%</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>3.62%</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>18.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="D403" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>3.11%</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>29.47%</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>3.01%</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>22.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="D404" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>129.58%</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="D405" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>103.56%</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>1.56%</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>31.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="D406" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>8.94%</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>94.19%</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>28.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="D407" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>9.74%</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>121.92%</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>11.45%</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>27.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="D408" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>9.25%</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>46.50%</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>30.97</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>-3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>-2.48%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>196.20%</t>
+          <t>191.31%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>17.91</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.25</v>
+        <v>22.2</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.35</v>
+        <v>0.95</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.62%</t>
+          <t>4.47%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28.79%</t>
+          <t>29.45%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>27.35</v>
+        <v>28.45</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>4.02%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-4.96%</t>
+          <t>-3.37%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.68%</t>
+          <t>11.23%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>46.36</t>
+          <t>48.22</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.85</v>
+        <v>30.4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9</v>
+        <v>-0.45</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.56%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>112.15%</t>
+          <t>107.01%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>17.47</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38.65</v>
+        <v>38.45</v>
       </c>
       <c r="D6" t="n">
-        <v>0.95</v>
+        <v>-0.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.70%</t>
+          <t>22.94%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>3.64%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>18.23</t>
+          <t>18.14</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>53.1</v>
+        <v>51.6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6</v>
+        <v>-1.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>-2.82%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.47%</t>
+          <t>24.78%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>3.10%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>22.50</t>
+          <t>21.86</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.3</v>
+        <v>16.65</v>
       </c>
       <c r="D8" t="n">
-        <v>0.65</v>
+        <v>0.35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4.15%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>129.58%</t>
+          <t>136.51%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>102.85</v>
+        <v>102</v>
       </c>
       <c r="D9" t="n">
-        <v>9.35</v>
+        <v>-0.85</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>103.56%</t>
+          <t>104.86%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>30.93</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>85.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>7.05</v>
+        <v>0.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8.94%</t>
+          <t>0.58%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>94.19%</t>
+          <t>96.76%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.41%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>28.78</t>
+          <t>28.94</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>34.49</v>
+        <v>34.8</v>
       </c>
       <c r="D11" t="n">
-        <v>3.06</v>
+        <v>0.31</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9.74%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>121.92%</t>
+          <t>127.39%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.45%</t>
+          <t>11.35%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>28.12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.65</v>
+        <v>14.61</v>
       </c>
       <c r="D12" t="n">
-        <v>1.24</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>9.25%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>46.50%</t>
+          <t>46.10%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30.97</t>
+          <t>30.88</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H408"/>
+  <dimension ref="A1:H419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15089,10 +15089,8 @@
           <t>2.16%</t>
         </is>
       </c>
-      <c r="H398" t="inlineStr">
-        <is>
-          <t>18.36</t>
-        </is>
+      <c r="H398" t="n">
+        <v>18.36</v>
       </c>
     </row>
     <row r="399">
@@ -15127,11 +15125,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H399" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -15165,10 +15159,8 @@
           <t>11.68%</t>
         </is>
       </c>
-      <c r="H400" t="inlineStr">
-        <is>
-          <t>46.36</t>
-        </is>
+      <c r="H400" t="n">
+        <v>46.36</v>
       </c>
     </row>
     <row r="401">
@@ -15203,10 +15195,8 @@
           <t>3.24%</t>
         </is>
       </c>
-      <c r="H401" t="inlineStr">
-        <is>
-          <t>17.73</t>
-        </is>
+      <c r="H401" t="n">
+        <v>17.73</v>
       </c>
     </row>
     <row r="402">
@@ -15241,10 +15231,8 @@
           <t>3.62%</t>
         </is>
       </c>
-      <c r="H402" t="inlineStr">
-        <is>
-          <t>18.23</t>
-        </is>
+      <c r="H402" t="n">
+        <v>18.23</v>
       </c>
     </row>
     <row r="403">
@@ -15279,10 +15267,8 @@
           <t>3.01%</t>
         </is>
       </c>
-      <c r="H403" t="inlineStr">
-        <is>
-          <t>22.50</t>
-        </is>
+      <c r="H403" t="n">
+        <v>22.5</v>
       </c>
     </row>
     <row r="404">
@@ -15317,11 +15303,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H404" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -15355,10 +15337,8 @@
           <t>1.56%</t>
         </is>
       </c>
-      <c r="H405" t="inlineStr">
-        <is>
-          <t>31.18</t>
-        </is>
+      <c r="H405" t="n">
+        <v>31.18</v>
       </c>
     </row>
     <row r="406">
@@ -15393,10 +15373,8 @@
           <t>3.43%</t>
         </is>
       </c>
-      <c r="H406" t="inlineStr">
-        <is>
-          <t>28.78</t>
-        </is>
+      <c r="H406" t="n">
+        <v>28.78</v>
       </c>
     </row>
     <row r="407">
@@ -15431,10 +15409,8 @@
           <t>11.45%</t>
         </is>
       </c>
-      <c r="H407" t="inlineStr">
-        <is>
-          <t>27.87</t>
-        </is>
+      <c r="H407" t="n">
+        <v>27.87</v>
       </c>
     </row>
     <row r="408">
@@ -15469,9 +15445,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H408" t="inlineStr">
-        <is>
-          <t>30.97</t>
+      <c r="H408" t="n">
+        <v>30.97</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>118</v>
+      </c>
+      <c r="D409" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>-2.48%</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>191.31%</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>2.21%</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>17.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D410" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>4.47%</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>29.45%</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="D411" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>4.02%</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>-3.37%</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>11.23%</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>48.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="D412" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>-1.46%</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>107.01%</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>3.29%</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>17.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="D413" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>-0.52%</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>22.94%</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>3.64%</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>18.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="D414" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>-2.82%</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>24.78%</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>3.10%</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>21.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="D415" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>2.15%</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>136.51%</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>102</v>
+      </c>
+      <c r="D416" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>-0.83%</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>104.86%</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>1.57%</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>30.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="D417" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>96.76%</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>3.41%</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>28.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="D418" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>127.39%</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>11.35%</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>28.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="D419" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>-0.27%</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>46.10%</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>30.88</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>118</v>
+        <v>118.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-3</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-2.48%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>191.31%</t>
+          <t>192.54%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>17.91</t>
+          <t>18.43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.2</v>
+        <v>23.85</v>
       </c>
       <c r="D3" t="n">
-        <v>0.95</v>
+        <v>1.65</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.47%</t>
+          <t>7.43%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.45%</t>
+          <t>39.07%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.45</v>
+        <v>28.9</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1</v>
+        <v>0.45</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4.02%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-3.37%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.23%</t>
+          <t>11.06%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>48.22</t>
+          <t>47.38</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.4</v>
+        <v>30.55</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.45</v>
+        <v>0.15</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>107.01%</t>
+          <t>108.03%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.27%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>17.87</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38.45</v>
+        <v>38</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2</v>
+        <v>-0.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.94%</t>
+          <t>21.50%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.64%</t>
+          <t>3.68%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>18.01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>51.6</v>
+        <v>50.7</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5</v>
+        <v>-0.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>-1.74%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.78%</t>
+          <t>22.61%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.16%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>22.14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.65</v>
+        <v>16.6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.35</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>136.51%</t>
+          <t>135.80%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>39.52</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>102</v>
+        <v>100.65</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.85</v>
+        <v>-1.35</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.83%</t>
+          <t>-1.32%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>104.86%</t>
+          <t>102.15%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>30.52</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>86.40000000000001</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>96.76%</t>
+          <t>96.19%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.42%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>28.86</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>34.8</v>
+        <v>35.02</v>
       </c>
       <c r="D11" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>127.39%</t>
+          <t>128.83%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.35%</t>
+          <t>11.28%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28.12</t>
+          <t>28.30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.61</v>
+        <v>14.56</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>46.10%</t>
+          <t>45.60%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30.88</t>
+          <t>30.78</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H419"/>
+  <dimension ref="A1:H430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15481,10 +15481,8 @@
           <t>2.21%</t>
         </is>
       </c>
-      <c r="H409" t="inlineStr">
-        <is>
-          <t>17.91</t>
-        </is>
+      <c r="H409" t="n">
+        <v>17.91</v>
       </c>
     </row>
     <row r="410">
@@ -15519,11 +15517,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H410" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -15557,10 +15551,8 @@
           <t>11.23%</t>
         </is>
       </c>
-      <c r="H411" t="inlineStr">
-        <is>
-          <t>48.22</t>
-        </is>
+      <c r="H411" t="n">
+        <v>48.22</v>
       </c>
     </row>
     <row r="412">
@@ -15595,10 +15587,8 @@
           <t>3.29%</t>
         </is>
       </c>
-      <c r="H412" t="inlineStr">
-        <is>
-          <t>17.47</t>
-        </is>
+      <c r="H412" t="n">
+        <v>17.47</v>
       </c>
     </row>
     <row r="413">
@@ -15633,10 +15623,8 @@
           <t>3.64%</t>
         </is>
       </c>
-      <c r="H413" t="inlineStr">
-        <is>
-          <t>18.14</t>
-        </is>
+      <c r="H413" t="n">
+        <v>18.14</v>
       </c>
     </row>
     <row r="414">
@@ -15671,10 +15659,8 @@
           <t>3.10%</t>
         </is>
       </c>
-      <c r="H414" t="inlineStr">
-        <is>
-          <t>21.86</t>
-        </is>
+      <c r="H414" t="n">
+        <v>21.86</v>
       </c>
     </row>
     <row r="415">
@@ -15709,11 +15695,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H415" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -15747,10 +15729,8 @@
           <t>1.57%</t>
         </is>
       </c>
-      <c r="H416" t="inlineStr">
-        <is>
-          <t>30.93</t>
-        </is>
+      <c r="H416" t="n">
+        <v>30.93</v>
       </c>
     </row>
     <row r="417">
@@ -15785,10 +15765,8 @@
           <t>3.41%</t>
         </is>
       </c>
-      <c r="H417" t="inlineStr">
-        <is>
-          <t>28.94</t>
-        </is>
+      <c r="H417" t="n">
+        <v>28.94</v>
       </c>
     </row>
     <row r="418">
@@ -15823,10 +15801,8 @@
           <t>11.35%</t>
         </is>
       </c>
-      <c r="H418" t="inlineStr">
-        <is>
-          <t>28.12</t>
-        </is>
+      <c r="H418" t="n">
+        <v>28.12</v>
       </c>
     </row>
     <row r="419">
@@ -15861,9 +15837,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H419" t="inlineStr">
-        <is>
-          <t>30.88</t>
+      <c r="H419" t="n">
+        <v>30.88</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="D420" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>192.54%</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>2.20%</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>18.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="D421" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>7.43%</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>39.07%</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="D422" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>1.58%</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>-1.85%</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>11.06%</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>47.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="D423" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>108.03%</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>3.27%</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>17.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>38</v>
+      </c>
+      <c r="D424" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>-1.17%</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>21.50%</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>3.68%</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>18.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="D425" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>-1.74%</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>22.61%</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>3.16%</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>22.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="D426" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>135.80%</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>39.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="D427" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>-1.32%</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>102.15%</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>1.59%</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>30.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>86.15000000000001</v>
+      </c>
+      <c r="D428" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>-0.29%</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>96.19%</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>3.42%</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>28.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="D429" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>128.83%</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>11.28%</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>28.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="D430" t="n">
+        <v>0</v>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>45.60%</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>30.78</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>118.5</v>
+        <v>122</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>2.95%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>192.54%</t>
+          <t>199.73%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.14%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18.43</t>
+          <t>18.46</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23.85</v>
+        <v>22.9</v>
       </c>
       <c r="D3" t="n">
-        <v>1.65</v>
+        <v>-0.95</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.43%</t>
+          <t>-3.98%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39.07%</t>
+          <t>31.61%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.9</v>
+        <v>28.45</v>
       </c>
       <c r="D4" t="n">
-        <v>0.45</v>
+        <v>-0.45</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>-1.56%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>-5.16%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.06%</t>
+          <t>11.23%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>47.38</t>
+          <t>47.42</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.55</v>
+        <v>31.6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.15</v>
+        <v>1.05</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>3.44%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>108.03%</t>
+          <t>114.48%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>3.16%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.87</t>
+          <t>18.06</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.45</v>
+        <v>0.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.50%</t>
+          <t>21.64%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>18.23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50.7</v>
+        <v>51.2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9</v>
+        <v>0.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.74%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.61%</t>
+          <t>24.10%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.12%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>22.07</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.6</v>
+        <v>18.25</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>1.65</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>9.94%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>135.80%</t>
+          <t>161.46%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>39.52</t>
+          <t>44.51</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>100.65</v>
+        <v>103.8</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>102.15%</t>
+          <t>105.84%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>31.47</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>86.15000000000001</v>
+        <v>88.55</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>96.19%</t>
+          <t>99.06%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>28.86</t>
+          <t>29.66</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35.02</v>
+        <v>36.01</v>
       </c>
       <c r="D11" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>128.83%</t>
+          <t>133.02%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.28%</t>
+          <t>10.97%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28.30</t>
+          <t>29.10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.56</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>45.60%</t>
+          <t>50.00%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30.78</t>
+          <t>31.71</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H430"/>
+  <dimension ref="A1:H441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15873,10 +15873,8 @@
           <t>2.20%</t>
         </is>
       </c>
-      <c r="H420" t="inlineStr">
-        <is>
-          <t>18.43</t>
-        </is>
+      <c r="H420" t="n">
+        <v>18.43</v>
       </c>
     </row>
     <row r="421">
@@ -15911,11 +15909,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H421" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -15949,10 +15943,8 @@
           <t>11.06%</t>
         </is>
       </c>
-      <c r="H422" t="inlineStr">
-        <is>
-          <t>47.38</t>
-        </is>
+      <c r="H422" t="n">
+        <v>47.38</v>
       </c>
     </row>
     <row r="423">
@@ -15987,10 +15979,8 @@
           <t>3.27%</t>
         </is>
       </c>
-      <c r="H423" t="inlineStr">
-        <is>
-          <t>17.87</t>
-        </is>
+      <c r="H423" t="n">
+        <v>17.87</v>
       </c>
     </row>
     <row r="424">
@@ -16025,10 +16015,8 @@
           <t>3.68%</t>
         </is>
       </c>
-      <c r="H424" t="inlineStr">
-        <is>
-          <t>18.01</t>
-        </is>
+      <c r="H424" t="n">
+        <v>18.01</v>
       </c>
     </row>
     <row r="425">
@@ -16063,10 +16051,8 @@
           <t>3.16%</t>
         </is>
       </c>
-      <c r="H425" t="inlineStr">
-        <is>
-          <t>22.14</t>
-        </is>
+      <c r="H425" t="n">
+        <v>22.14</v>
       </c>
     </row>
     <row r="426">
@@ -16101,10 +16087,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H426" t="inlineStr">
-        <is>
-          <t>39.52</t>
-        </is>
+      <c r="H426" t="n">
+        <v>39.52</v>
       </c>
     </row>
     <row r="427">
@@ -16139,10 +16123,8 @@
           <t>1.59%</t>
         </is>
       </c>
-      <c r="H427" t="inlineStr">
-        <is>
-          <t>30.52</t>
-        </is>
+      <c r="H427" t="n">
+        <v>30.52</v>
       </c>
     </row>
     <row r="428">
@@ -16177,10 +16159,8 @@
           <t>3.42%</t>
         </is>
       </c>
-      <c r="H428" t="inlineStr">
-        <is>
-          <t>28.86</t>
-        </is>
+      <c r="H428" t="n">
+        <v>28.86</v>
       </c>
     </row>
     <row r="429">
@@ -16215,10 +16195,8 @@
           <t>11.28%</t>
         </is>
       </c>
-      <c r="H429" t="inlineStr">
-        <is>
-          <t>28.30</t>
-        </is>
+      <c r="H429" t="n">
+        <v>28.3</v>
       </c>
     </row>
     <row r="430">
@@ -16253,9 +16231,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H430" t="inlineStr">
-        <is>
-          <t>30.78</t>
+      <c r="H430" t="n">
+        <v>30.78</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>122</v>
+      </c>
+      <c r="D431" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>2.95%</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>199.73%</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>2.14%</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>18.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="D432" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>-3.98%</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>31.61%</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="D433" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>-1.56%</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>-5.16%</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>11.23%</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>47.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="D434" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>3.44%</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>114.48%</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>3.16%</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>18.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="D435" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>0.26%</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>21.64%</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>3.67%</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>18.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="D436" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>0.99%</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>24.10%</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>3.12%</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>22.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="D437" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>9.94%</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>161.46%</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>44.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="D438" t="n">
+        <v>0</v>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>105.84%</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>1.54%</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>31.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>88.55</v>
+      </c>
+      <c r="D439" t="n">
+        <v>0</v>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>99.06%</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>3.33%</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>29.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>36.01</v>
+      </c>
+      <c r="D440" t="n">
+        <v>0</v>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>133.02%</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>10.97%</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>29.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>15</v>
+      </c>
+      <c r="D441" t="n">
+        <v>0</v>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>50.00%</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>31.71</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>122</v>
+        <v>121.5</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5</v>
+        <v>-0.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>199.73%</t>
+          <t>203.63%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>18.44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.95</v>
+        <v>-0.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-3.98%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31.61%</t>
+          <t>31.59%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.45</v>
+        <v>28.8</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.45</v>
+        <v>0.35</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-5.16%</t>
+          <t>-4.87%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.23%</t>
+          <t>11.09%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>47.42</t>
+          <t>48.81</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31.6</v>
+        <v>30.6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.05</v>
+        <v>-1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>-3.16%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>114.48%</t>
+          <t>106.35%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.27%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>18.06</t>
+          <t>17.59</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38.1</v>
+        <v>37.95</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1</v>
+        <v>-0.15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.64%</t>
+          <t>20.24%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>3.69%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>18.23</t>
+          <t>17.90</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>51.2</v>
+        <v>50.3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.10%</t>
+          <t>21.50%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.18%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>21.31</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18.25</v>
+        <v>17.4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.65</v>
+        <v>-0.85</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9.94%</t>
+          <t>-4.66%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>161.46%</t>
+          <t>149.64%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>42.44</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>103.8</v>
+        <v>103.3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>105.84%</t>
+          <t>106.66%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.47</t>
+          <t>31.32</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,19 +787,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>88.55</v>
+        <v>88.5</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>99.06%</t>
+          <t>99.68%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -809,14 +809,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>29.65</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.01</v>
+        <v>35.98</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>133.02%</t>
+          <t>135.78%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.97%</t>
+          <t>10.98%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>29.10</t>
+          <t>29.08</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>14.96</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50.00%</t>
+          <t>49.60%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>31.71</t>
+          <t>31.62</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H441"/>
+  <dimension ref="A1:H452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16267,10 +16267,8 @@
           <t>2.14%</t>
         </is>
       </c>
-      <c r="H431" t="inlineStr">
-        <is>
-          <t>18.46</t>
-        </is>
+      <c r="H431" t="n">
+        <v>18.46</v>
       </c>
     </row>
     <row r="432">
@@ -16305,11 +16303,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H432" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -16343,10 +16337,8 @@
           <t>11.23%</t>
         </is>
       </c>
-      <c r="H433" t="inlineStr">
-        <is>
-          <t>47.42</t>
-        </is>
+      <c r="H433" t="n">
+        <v>47.42</v>
       </c>
     </row>
     <row r="434">
@@ -16381,10 +16373,8 @@
           <t>3.16%</t>
         </is>
       </c>
-      <c r="H434" t="inlineStr">
-        <is>
-          <t>18.06</t>
-        </is>
+      <c r="H434" t="n">
+        <v>18.06</v>
       </c>
     </row>
     <row r="435">
@@ -16419,10 +16409,8 @@
           <t>3.67%</t>
         </is>
       </c>
-      <c r="H435" t="inlineStr">
-        <is>
-          <t>18.23</t>
-        </is>
+      <c r="H435" t="n">
+        <v>18.23</v>
       </c>
     </row>
     <row r="436">
@@ -16457,10 +16445,8 @@
           <t>3.12%</t>
         </is>
       </c>
-      <c r="H436" t="inlineStr">
-        <is>
-          <t>22.07</t>
-        </is>
+      <c r="H436" t="n">
+        <v>22.07</v>
       </c>
     </row>
     <row r="437">
@@ -16495,10 +16481,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H437" t="inlineStr">
-        <is>
-          <t>44.51</t>
-        </is>
+      <c r="H437" t="n">
+        <v>44.51</v>
       </c>
     </row>
     <row r="438">
@@ -16533,10 +16517,8 @@
           <t>1.54%</t>
         </is>
       </c>
-      <c r="H438" t="inlineStr">
-        <is>
-          <t>31.47</t>
-        </is>
+      <c r="H438" t="n">
+        <v>31.47</v>
       </c>
     </row>
     <row r="439">
@@ -16571,10 +16553,8 @@
           <t>3.33%</t>
         </is>
       </c>
-      <c r="H439" t="inlineStr">
-        <is>
-          <t>29.66</t>
-        </is>
+      <c r="H439" t="n">
+        <v>29.66</v>
       </c>
     </row>
     <row r="440">
@@ -16609,10 +16589,8 @@
           <t>10.97%</t>
         </is>
       </c>
-      <c r="H440" t="inlineStr">
-        <is>
-          <t>29.10</t>
-        </is>
+      <c r="H440" t="n">
+        <v>29.1</v>
       </c>
     </row>
     <row r="441">
@@ -16647,9 +16625,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H441" t="inlineStr">
-        <is>
-          <t>31.71</t>
+      <c r="H441" t="n">
+        <v>31.71</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="D442" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>203.63%</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>2.15%</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>18.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="D443" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>-0.87%</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>31.59%</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D444" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>1.23%</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>-4.87%</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>11.09%</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>48.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="D445" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>-3.16%</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>106.35%</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>3.27%</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>17.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>37.95</v>
+      </c>
+      <c r="D446" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>-0.39%</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>20.24%</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>3.69%</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>17.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="D447" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>-1.76%</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>21.50%</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>3.18%</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>21.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D448" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>-4.66%</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>149.64%</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>42.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="D449" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>-0.48%</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>106.66%</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>1.55%</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>31.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="D450" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>-0.06%</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>99.68%</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>3.33%</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>29.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>35.98</v>
+      </c>
+      <c r="D451" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>-0.08%</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>135.78%</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>10.98%</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>29.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="D452" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>-0.27%</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>49.60%</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>31.62</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>121.5</v>
+        <v>116</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5</v>
+        <v>-5.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-4.53%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>203.63%</t>
+          <t>192.04%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.25%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>17.60</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.7</v>
+        <v>22.15</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2</v>
+        <v>-0.55</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.87%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31.59%</t>
+          <t>28.41%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.8</v>
+        <v>28.3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.35</v>
+        <v>-0.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>-1.74%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-4.87%</t>
+          <t>-6.01%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.09%</t>
+          <t>11.29%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>48.81</t>
+          <t>47.97</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.6</v>
+        <v>30.85</v>
       </c>
       <c r="D5" t="n">
-        <v>-1</v>
+        <v>0.25</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-3.16%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>106.35%</t>
+          <t>108.04%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>3.24%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.59</t>
+          <t>17.73</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37.95</v>
+        <v>38.15</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.15</v>
+        <v>0.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.24%</t>
+          <t>19.96%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17.90</t>
+          <t>18.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50.3</v>
+        <v>50.9</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9</v>
+        <v>0.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.50%</t>
+          <t>25.37%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>21.57</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.4</v>
+        <v>16.95</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.85</v>
+        <v>-0.45</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-4.66%</t>
+          <t>-2.59%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>149.64%</t>
+          <t>141.45%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>42.44</t>
+          <t>41.34</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>103.3</v>
+        <v>102.85</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5</v>
+        <v>-0.45</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>106.66%</t>
+          <t>100.07%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.18</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>88.5</v>
+        <v>88</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.05</v>
+        <v>-0.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>99.68%</t>
+          <t>94.66%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.48</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35.98</v>
+        <v>35.54</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.03</v>
+        <v>-0.44</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>135.78%</t>
+          <t>129.59%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.98%</t>
+          <t>11.11%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>28.72</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.96</v>
+        <v>14.88</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>49.60%</t>
+          <t>48.80%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>31.45</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H452"/>
+  <dimension ref="A1:H463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16661,10 +16661,8 @@
           <t>2.15%</t>
         </is>
       </c>
-      <c r="H442" t="inlineStr">
-        <is>
-          <t>18.44</t>
-        </is>
+      <c r="H442" t="n">
+        <v>18.44</v>
       </c>
     </row>
     <row r="443">
@@ -16699,11 +16697,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H443" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -16737,10 +16731,8 @@
           <t>11.09%</t>
         </is>
       </c>
-      <c r="H444" t="inlineStr">
-        <is>
-          <t>48.81</t>
-        </is>
+      <c r="H444" t="n">
+        <v>48.81</v>
       </c>
     </row>
     <row r="445">
@@ -16775,10 +16767,8 @@
           <t>3.27%</t>
         </is>
       </c>
-      <c r="H445" t="inlineStr">
-        <is>
-          <t>17.59</t>
-        </is>
+      <c r="H445" t="n">
+        <v>17.59</v>
       </c>
     </row>
     <row r="446">
@@ -16813,10 +16803,8 @@
           <t>3.69%</t>
         </is>
       </c>
-      <c r="H446" t="inlineStr">
-        <is>
-          <t>17.90</t>
-        </is>
+      <c r="H446" t="n">
+        <v>17.9</v>
       </c>
     </row>
     <row r="447">
@@ -16851,10 +16839,8 @@
           <t>3.18%</t>
         </is>
       </c>
-      <c r="H447" t="inlineStr">
-        <is>
-          <t>21.31</t>
-        </is>
+      <c r="H447" t="n">
+        <v>21.31</v>
       </c>
     </row>
     <row r="448">
@@ -16889,10 +16875,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H448" t="inlineStr">
-        <is>
-          <t>42.44</t>
-        </is>
+      <c r="H448" t="n">
+        <v>42.44</v>
       </c>
     </row>
     <row r="449">
@@ -16927,10 +16911,8 @@
           <t>1.55%</t>
         </is>
       </c>
-      <c r="H449" t="inlineStr">
-        <is>
-          <t>31.32</t>
-        </is>
+      <c r="H449" t="n">
+        <v>31.32</v>
       </c>
     </row>
     <row r="450">
@@ -16965,10 +16947,8 @@
           <t>3.33%</t>
         </is>
       </c>
-      <c r="H450" t="inlineStr">
-        <is>
-          <t>29.65</t>
-        </is>
+      <c r="H450" t="n">
+        <v>29.65</v>
       </c>
     </row>
     <row r="451">
@@ -17003,10 +16983,8 @@
           <t>10.98%</t>
         </is>
       </c>
-      <c r="H451" t="inlineStr">
-        <is>
-          <t>29.08</t>
-        </is>
+      <c r="H451" t="n">
+        <v>29.08</v>
       </c>
     </row>
     <row r="452">
@@ -17041,9 +17019,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H452" t="inlineStr">
-        <is>
-          <t>31.62</t>
+      <c r="H452" t="n">
+        <v>31.62</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>116</v>
+      </c>
+      <c r="D453" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>-4.53%</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>192.04%</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>2.25%</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>17.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="D454" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>-2.42%</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>28.41%</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="D455" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>-1.74%</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>-6.01%</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>11.29%</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>47.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="D456" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>0.82%</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>108.04%</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>3.24%</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>17.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="D457" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>0.53%</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>19.96%</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>3.67%</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="D458" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>1.19%</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>25.37%</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>21.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="D459" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>-2.59%</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>141.45%</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>41.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="D460" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>-0.44%</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>100.07%</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>1.56%</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>31.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>88</v>
+      </c>
+      <c r="D461" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>94.66%</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>3.35%</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>29.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>35.54</v>
+      </c>
+      <c r="D462" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>-1.22%</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>129.59%</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>11.11%</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>28.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="D463" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>-0.53%</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>48.80%</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>31.45</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D2" t="n">
-        <v>-5.5</v>
+        <v>7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-4.53%</t>
+          <t>6.03%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>192.04%</t>
+          <t>209.67%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.12%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>17.60</t>
+          <t>18.66</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.15</v>
+        <v>23.6</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.55</v>
+        <v>1.45</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>6.55%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28.41%</t>
+          <t>38.82%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.3</v>
+        <v>29.6</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5</v>
+        <v>1.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.74%</t>
+          <t>4.59%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-6.01%</t>
+          <t>-4.16%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.29%</t>
+          <t>10.79%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>50.17</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.85</v>
+        <v>31.05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>108.04%</t>
+          <t>108.71%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>3.22%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>17.84</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38.15</v>
+        <v>37.8</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2</v>
+        <v>-0.35</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.96%</t>
+          <t>18.86%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>17.83</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.37%</t>
+          <t>24.85%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -695,14 +695,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.57</t>
+          <t>21.61</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.95</v>
+        <v>17.15</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.45</v>
+        <v>0.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-2.59%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>141.45%</t>
+          <t>149.27%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>41.34</t>
+          <t>41.83</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>102.85</v>
+        <v>104.25</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.45</v>
+        <v>1.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>100.07%</t>
+          <t>101.26%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>31.61</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>88</v>
+        <v>89.55</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5</v>
+        <v>1.55</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>94.66%</t>
+          <t>96.64%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>30.00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35.54</v>
+        <v>36.4</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.44</v>
+        <v>0.86</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>129.59%</t>
+          <t>135.01%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.11%</t>
+          <t>10.85%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28.72</t>
+          <t>29.41</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.88</v>
+        <v>15.12</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.08</v>
+        <v>0.24</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>48.80%</t>
+          <t>51.20%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>31.96</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H463"/>
+  <dimension ref="A1:H474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17055,10 +17055,8 @@
           <t>2.25%</t>
         </is>
       </c>
-      <c r="H453" t="inlineStr">
-        <is>
-          <t>17.60</t>
-        </is>
+      <c r="H453" t="n">
+        <v>17.6</v>
       </c>
     </row>
     <row r="454">
@@ -17093,11 +17091,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H454" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -17131,10 +17125,8 @@
           <t>11.29%</t>
         </is>
       </c>
-      <c r="H455" t="inlineStr">
-        <is>
-          <t>47.97</t>
-        </is>
+      <c r="H455" t="n">
+        <v>47.97</v>
       </c>
     </row>
     <row r="456">
@@ -17169,10 +17161,8 @@
           <t>3.24%</t>
         </is>
       </c>
-      <c r="H456" t="inlineStr">
-        <is>
-          <t>17.73</t>
-        </is>
+      <c r="H456" t="n">
+        <v>17.73</v>
       </c>
     </row>
     <row r="457">
@@ -17207,10 +17197,8 @@
           <t>3.67%</t>
         </is>
       </c>
-      <c r="H457" t="inlineStr">
-        <is>
-          <t>18.00</t>
-        </is>
+      <c r="H457" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="458">
@@ -17245,10 +17233,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H458" t="inlineStr">
-        <is>
-          <t>21.57</t>
-        </is>
+      <c r="H458" t="n">
+        <v>21.57</v>
       </c>
     </row>
     <row r="459">
@@ -17283,10 +17269,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H459" t="inlineStr">
-        <is>
-          <t>41.34</t>
-        </is>
+      <c r="H459" t="n">
+        <v>41.34</v>
       </c>
     </row>
     <row r="460">
@@ -17321,10 +17305,8 @@
           <t>1.56%</t>
         </is>
       </c>
-      <c r="H460" t="inlineStr">
-        <is>
-          <t>31.18</t>
-        </is>
+      <c r="H460" t="n">
+        <v>31.18</v>
       </c>
     </row>
     <row r="461">
@@ -17359,10 +17341,8 @@
           <t>3.35%</t>
         </is>
       </c>
-      <c r="H461" t="inlineStr">
-        <is>
-          <t>29.48</t>
-        </is>
+      <c r="H461" t="n">
+        <v>29.48</v>
       </c>
     </row>
     <row r="462">
@@ -17397,10 +17377,8 @@
           <t>11.11%</t>
         </is>
       </c>
-      <c r="H462" t="inlineStr">
-        <is>
-          <t>28.72</t>
-        </is>
+      <c r="H462" t="n">
+        <v>28.72</v>
       </c>
     </row>
     <row r="463">
@@ -17435,9 +17413,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H463" t="inlineStr">
-        <is>
-          <t>31.45</t>
+      <c r="H463" t="n">
+        <v>31.45</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>123</v>
+      </c>
+      <c r="D464" t="n">
+        <v>7</v>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>6.03%</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>209.67%</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>2.12%</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>18.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="D465" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>6.55%</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>38.82%</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="D466" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>4.59%</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>-4.16%</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>10.79%</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>50.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>31.05</v>
+      </c>
+      <c r="D467" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>0.65%</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>108.71%</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>3.22%</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>17.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="D468" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>-0.92%</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>18.86%</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>3.70%</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>17.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>51</v>
+      </c>
+      <c r="D469" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>24.85%</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>21.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="D470" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>1.18%</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>149.27%</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>41.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="D471" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>1.36%</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>101.26%</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>1.53%</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>31.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>89.55</v>
+      </c>
+      <c r="D472" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>1.76%</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>96.64%</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>3.29%</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="D473" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>2.42%</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>135.01%</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>10.85%</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>29.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="D474" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>51.20%</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>31.96</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,11 +486,11 @@
         <v>123</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6.03%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23.6</v>
+        <v>22.6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.45</v>
+        <v>-1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6.55%</t>
+          <t>-4.24%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>38.82%</t>
+          <t>32.94%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.6</v>
+        <v>28.9</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3</v>
+        <v>-0.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4.59%</t>
+          <t>-2.36%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-4.16%</t>
+          <t>-6.43%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.79%</t>
+          <t>11.06%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>50.17</t>
+          <t>48.98</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -600,11 +600,11 @@
         <v>31.05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -626,7 +626,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37.8</v>
+        <v>36.9</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.35</v>
+        <v>-0.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>-2.38%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.86%</t>
+          <t>16.03%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.79%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17.83</t>
+          <t>17.41</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>51</v>
+        <v>49.4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>-1.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-3.14%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.85%</t>
+          <t>20.93%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -695,14 +695,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>20.93</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.15</v>
+        <v>17.3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>149.27%</t>
+          <t>151.45%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>42.20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>104.25</v>
+        <v>104.6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4</v>
+        <v>0.35</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>101.26%</t>
+          <t>101.93%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -771,14 +771,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.61</t>
+          <t>31.71</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>89.55</v>
+        <v>89.95</v>
       </c>
       <c r="D10" t="n">
-        <v>1.55</v>
+        <v>0.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>96.64%</t>
+          <t>97.52%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.28%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>30.13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.4</v>
+        <v>36.43</v>
       </c>
       <c r="D11" t="n">
-        <v>0.86</v>
+        <v>0.03</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>135.01%</t>
+          <t>135.21%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.85%</t>
+          <t>10.84%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>29.44</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.12</v>
+        <v>15.16</v>
       </c>
       <c r="D12" t="n">
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>51.20%</t>
+          <t>51.60%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>32.04</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H474"/>
+  <dimension ref="A1:H485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17449,10 +17449,8 @@
           <t>2.12%</t>
         </is>
       </c>
-      <c r="H464" t="inlineStr">
-        <is>
-          <t>18.66</t>
-        </is>
+      <c r="H464" t="n">
+        <v>18.66</v>
       </c>
     </row>
     <row r="465">
@@ -17487,11 +17485,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H465" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -17525,10 +17519,8 @@
           <t>10.79%</t>
         </is>
       </c>
-      <c r="H466" t="inlineStr">
-        <is>
-          <t>50.17</t>
-        </is>
+      <c r="H466" t="n">
+        <v>50.17</v>
       </c>
     </row>
     <row r="467">
@@ -17563,10 +17555,8 @@
           <t>3.22%</t>
         </is>
       </c>
-      <c r="H467" t="inlineStr">
-        <is>
-          <t>17.84</t>
-        </is>
+      <c r="H467" t="n">
+        <v>17.84</v>
       </c>
     </row>
     <row r="468">
@@ -17601,10 +17591,8 @@
           <t>3.70%</t>
         </is>
       </c>
-      <c r="H468" t="inlineStr">
-        <is>
-          <t>17.83</t>
-        </is>
+      <c r="H468" t="n">
+        <v>17.83</v>
       </c>
     </row>
     <row r="469">
@@ -17639,10 +17627,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H469" t="inlineStr">
-        <is>
-          <t>21.61</t>
-        </is>
+      <c r="H469" t="n">
+        <v>21.61</v>
       </c>
     </row>
     <row r="470">
@@ -17677,10 +17663,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H470" t="inlineStr">
-        <is>
-          <t>41.83</t>
-        </is>
+      <c r="H470" t="n">
+        <v>41.83</v>
       </c>
     </row>
     <row r="471">
@@ -17715,10 +17699,8 @@
           <t>1.53%</t>
         </is>
       </c>
-      <c r="H471" t="inlineStr">
-        <is>
-          <t>31.61</t>
-        </is>
+      <c r="H471" t="n">
+        <v>31.61</v>
       </c>
     </row>
     <row r="472">
@@ -17753,10 +17735,8 @@
           <t>3.29%</t>
         </is>
       </c>
-      <c r="H472" t="inlineStr">
-        <is>
-          <t>30.00</t>
-        </is>
+      <c r="H472" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="473">
@@ -17791,10 +17771,8 @@
           <t>10.85%</t>
         </is>
       </c>
-      <c r="H473" t="inlineStr">
-        <is>
-          <t>29.41</t>
-        </is>
+      <c r="H473" t="n">
+        <v>29.41</v>
       </c>
     </row>
     <row r="474">
@@ -17829,9 +17807,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H474" t="inlineStr">
-        <is>
-          <t>31.96</t>
+      <c r="H474" t="n">
+        <v>31.96</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>123</v>
+      </c>
+      <c r="D475" t="n">
+        <v>0</v>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>209.67%</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>2.12%</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>18.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="D476" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>-4.24%</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>32.94%</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="D477" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>-2.36%</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>-6.43%</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>11.06%</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>48.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>31.05</v>
+      </c>
+      <c r="D478" t="n">
+        <v>0</v>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>108.71%</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>3.22%</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>17.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="D479" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>-2.38%</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>16.03%</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>3.79%</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>17.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="D480" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>-3.14%</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>20.93%</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>20.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="D481" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>151.45%</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>42.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="D482" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>0.34%</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>101.93%</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>1.53%</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>31.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="D483" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>97.52%</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>3.28%</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>30.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>36.43</v>
+      </c>
+      <c r="D484" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>135.21%</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>10.84%</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>29.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="D485" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>0.26%</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>51.60%</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>32.04</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>209.67%</t>
+          <t>207.76%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.6</v>
+        <v>22.3</v>
       </c>
       <c r="D3" t="n">
-        <v>-1</v>
+        <v>-0.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-4.24%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>32.94%</t>
+          <t>28.90%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -562,16 +562,16 @@
         <v>28.9</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-2.36%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-6.43%</t>
+          <t>-5.92%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31.05</v>
+        <v>31.2</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>108.71%</t>
+          <t>108.38%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>17.93</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36.9</v>
+        <v>36.75</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9</v>
+        <v>-0.15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16.03%</t>
+          <t>15.38%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>3.81%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>17.33</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49.4</v>
+        <v>48.7</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6</v>
+        <v>-0.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-3.14%</t>
+          <t>-1.42%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.93%</t>
+          <t>17.35%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -695,14 +695,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>20.64</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -714,11 +714,11 @@
         <v>17.3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>104.6</v>
+        <v>105.2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>101.93%</t>
+          <t>102.90%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.71</t>
+          <t>31.90</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>89.95</v>
+        <v>90.5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>97.52%</t>
+          <t>98.56%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>3.26%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>30.32</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.43</v>
+        <v>36.69</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>135.21%</t>
+          <t>135.81%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.84%</t>
+          <t>10.77%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.16</v>
+        <v>15.26</v>
       </c>
       <c r="D12" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>51.60%</t>
+          <t>52.60%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>32.26</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H485"/>
+  <dimension ref="A1:H496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17843,10 +17843,8 @@
           <t>2.12%</t>
         </is>
       </c>
-      <c r="H475" t="inlineStr">
-        <is>
-          <t>18.66</t>
-        </is>
+      <c r="H475" t="n">
+        <v>18.66</v>
       </c>
     </row>
     <row r="476">
@@ -17881,11 +17879,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H476" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -17919,10 +17913,8 @@
           <t>11.06%</t>
         </is>
       </c>
-      <c r="H477" t="inlineStr">
-        <is>
-          <t>48.98</t>
-        </is>
+      <c r="H477" t="n">
+        <v>48.98</v>
       </c>
     </row>
     <row r="478">
@@ -17957,10 +17949,8 @@
           <t>3.22%</t>
         </is>
       </c>
-      <c r="H478" t="inlineStr">
-        <is>
-          <t>17.84</t>
-        </is>
+      <c r="H478" t="n">
+        <v>17.84</v>
       </c>
     </row>
     <row r="479">
@@ -17995,10 +17985,8 @@
           <t>3.79%</t>
         </is>
       </c>
-      <c r="H479" t="inlineStr">
-        <is>
-          <t>17.41</t>
-        </is>
+      <c r="H479" t="n">
+        <v>17.41</v>
       </c>
     </row>
     <row r="480">
@@ -18033,10 +18021,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H480" t="inlineStr">
-        <is>
-          <t>20.93</t>
-        </is>
+      <c r="H480" t="n">
+        <v>20.93</v>
       </c>
     </row>
     <row r="481">
@@ -18071,10 +18057,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H481" t="inlineStr">
-        <is>
-          <t>42.20</t>
-        </is>
+      <c r="H481" t="n">
+        <v>42.2</v>
       </c>
     </row>
     <row r="482">
@@ -18109,10 +18093,8 @@
           <t>1.53%</t>
         </is>
       </c>
-      <c r="H482" t="inlineStr">
-        <is>
-          <t>31.71</t>
-        </is>
+      <c r="H482" t="n">
+        <v>31.71</v>
       </c>
     </row>
     <row r="483">
@@ -18147,10 +18129,8 @@
           <t>3.28%</t>
         </is>
       </c>
-      <c r="H483" t="inlineStr">
-        <is>
-          <t>30.13</t>
-        </is>
+      <c r="H483" t="n">
+        <v>30.13</v>
       </c>
     </row>
     <row r="484">
@@ -18185,10 +18165,8 @@
           <t>10.84%</t>
         </is>
       </c>
-      <c r="H484" t="inlineStr">
-        <is>
-          <t>29.44</t>
-        </is>
+      <c r="H484" t="n">
+        <v>29.44</v>
       </c>
     </row>
     <row r="485">
@@ -18223,9 +18201,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H485" t="inlineStr">
-        <is>
-          <t>32.04</t>
+      <c r="H485" t="n">
+        <v>32.04</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>123</v>
+      </c>
+      <c r="D486" t="n">
+        <v>0</v>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>207.76%</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>2.12%</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>18.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D487" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>-1.33%</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>28.90%</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="D488" t="n">
+        <v>0</v>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>-5.92%</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>11.06%</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>48.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D489" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>108.38%</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>3.21%</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>17.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="D490" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>15.38%</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>3.81%</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>17.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="D491" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>-1.42%</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>17.35%</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>20.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="D492" t="n">
+        <v>0</v>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>151.45%</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>42.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="D493" t="n">
+        <v>0</v>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>102.90%</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>1.52%</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>31.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="D494" t="n">
+        <v>0</v>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>98.56%</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>3.26%</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>30.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="D495" t="n">
+        <v>0</v>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>135.81%</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>10.77%</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>29.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="D496" t="n">
+        <v>0</v>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>52.60%</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>32.26</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>123</v>
+        <v>124.5</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>207.76%</t>
+          <t>210.75%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>18.89</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.3</v>
+        <v>22.65</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3</v>
+        <v>0.35</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28.90%</t>
+          <t>29.80%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.9</v>
+        <v>28.7</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-5.92%</t>
+          <t>-5.20%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.06%</t>
+          <t>11.13%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>48.64</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31.2</v>
+        <v>31.5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>108.38%</t>
+          <t>109.05%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>18.10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36.75</v>
+        <v>37.3</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.15</v>
+        <v>0.55</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>15.38%</t>
+          <t>14.19%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.81%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.59</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>48.7</v>
+        <v>45.85</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7</v>
+        <v>-1.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.42%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.35%</t>
+          <t>13.37%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>3.82%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>19.43</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.3</v>
+        <v>17.9</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.47%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>151.45%</t>
+          <t>160.93%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>42.20</t>
+          <t>43.66</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>105.2</v>
+        <v>106.7</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -761,24 +761,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>102.90%</t>
+          <t>104.06%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>32.35</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>90.5</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -799,24 +799,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>98.56%</t>
+          <t>100.35%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.77</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.69</v>
+        <v>37.34</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -837,24 +837,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>135.81%</t>
+          <t>138.11%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.77%</t>
+          <t>10.58%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>30.17</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.26</v>
+        <v>15.52</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>52.60%</t>
+          <t>55.20%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>32.80</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H496"/>
+  <dimension ref="A1:H507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18237,10 +18237,8 @@
           <t>2.12%</t>
         </is>
       </c>
-      <c r="H486" t="inlineStr">
-        <is>
-          <t>18.66</t>
-        </is>
+      <c r="H486" t="n">
+        <v>18.66</v>
       </c>
     </row>
     <row r="487">
@@ -18275,11 +18273,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H487" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -18313,10 +18307,8 @@
           <t>11.06%</t>
         </is>
       </c>
-      <c r="H488" t="inlineStr">
-        <is>
-          <t>48.98</t>
-        </is>
+      <c r="H488" t="n">
+        <v>48.98</v>
       </c>
     </row>
     <row r="489">
@@ -18351,10 +18343,8 @@
           <t>3.21%</t>
         </is>
       </c>
-      <c r="H489" t="inlineStr">
-        <is>
-          <t>17.93</t>
-        </is>
+      <c r="H489" t="n">
+        <v>17.93</v>
       </c>
     </row>
     <row r="490">
@@ -18389,10 +18379,8 @@
           <t>3.81%</t>
         </is>
       </c>
-      <c r="H490" t="inlineStr">
-        <is>
-          <t>17.33</t>
-        </is>
+      <c r="H490" t="n">
+        <v>17.33</v>
       </c>
     </row>
     <row r="491">
@@ -18427,10 +18415,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H491" t="inlineStr">
-        <is>
-          <t>20.64</t>
-        </is>
+      <c r="H491" t="n">
+        <v>20.64</v>
       </c>
     </row>
     <row r="492">
@@ -18465,10 +18451,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H492" t="inlineStr">
-        <is>
-          <t>42.20</t>
-        </is>
+      <c r="H492" t="n">
+        <v>42.2</v>
       </c>
     </row>
     <row r="493">
@@ -18503,10 +18487,8 @@
           <t>1.52%</t>
         </is>
       </c>
-      <c r="H493" t="inlineStr">
-        <is>
-          <t>31.90</t>
-        </is>
+      <c r="H493" t="n">
+        <v>31.9</v>
       </c>
     </row>
     <row r="494">
@@ -18541,10 +18523,8 @@
           <t>3.26%</t>
         </is>
       </c>
-      <c r="H494" t="inlineStr">
-        <is>
-          <t>30.32</t>
-        </is>
+      <c r="H494" t="n">
+        <v>30.32</v>
       </c>
     </row>
     <row r="495">
@@ -18579,10 +18559,8 @@
           <t>10.77%</t>
         </is>
       </c>
-      <c r="H495" t="inlineStr">
-        <is>
-          <t>29.65</t>
-        </is>
+      <c r="H495" t="n">
+        <v>29.65</v>
       </c>
     </row>
     <row r="496">
@@ -18617,9 +18595,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H496" t="inlineStr">
-        <is>
-          <t>32.26</t>
+      <c r="H496" t="n">
+        <v>32.26</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="D497" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>210.75%</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>2.09%</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>18.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="D498" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>1.57%</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>29.80%</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="D499" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>-0.69%</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>-5.20%</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>11.13%</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>48.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D500" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>109.05%</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>18.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D501" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>14.19%</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>17.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="D502" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>-2.34%</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>13.37%</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>3.82%</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>19.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="D503" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>3.47%</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>160.93%</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>43.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="D504" t="n">
+        <v>0</v>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>104.06%</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>1.50%</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>32.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>91.84999999999999</v>
+      </c>
+      <c r="D505" t="n">
+        <v>0</v>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>100.35%</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>3.21%</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>30.77</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>37.34</v>
+      </c>
+      <c r="D506" t="n">
+        <v>0</v>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>138.11%</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>10.58%</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>30.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="D507" t="n">
+        <v>0</v>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>55.20%</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>32.80</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="今日總覽" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="歷史紀錄" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日總覽" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="歷史紀錄" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>124.5</v>
+        <v>121</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>-3.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>-2.81%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>210.75%</t>
+          <t>201.64%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.16%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>18.36</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.65</v>
+        <v>22.6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.35</v>
+        <v>-0.05</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.80%</t>
+          <t>31.40%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.7</v>
+        <v>29.5</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>2.79%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-5.20%</t>
+          <t>-1.30%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.13%</t>
+          <t>10.83%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>48.64</t>
+          <t>50.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31.5</v>
+        <v>31.65</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>109.05%</t>
+          <t>108.72%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.16%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>18.10</t>
+          <t>18.19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37.3</v>
+        <v>37.65</v>
       </c>
       <c r="D6" t="n">
-        <v>0.55</v>
+        <v>0.35</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14.19%</t>
+          <t>13.75%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>3.72%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17.59</t>
+          <t>17.76</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>45.85</v>
+        <v>47.35</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1</v>
+        <v>1.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>3.27%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>13.37%</t>
+          <t>14.75%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.82%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>20.06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.9</v>
+        <v>17.75</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6</v>
+        <v>-0.15</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>160.93%</t>
+          <t>156.13%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>43.66</t>
+          <t>43.29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>106.7</v>
+        <v>106.4</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>104.06%</t>
+          <t>104.25%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -771,14 +771,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>91.84999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -799,7 +799,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>100.35%</t>
+          <t>100.40%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -809,14 +809,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.75</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37.34</v>
+        <v>36.65</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -837,24 +837,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>138.11%</t>
+          <t>132.53%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.58%</t>
+          <t>10.78%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>29.62</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.52</v>
+        <v>15.49</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>55.20%</t>
+          <t>54.90%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>32.74</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H507"/>
+  <dimension ref="A1:H518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18631,10 +18631,8 @@
           <t>2.09%</t>
         </is>
       </c>
-      <c r="H497" t="inlineStr">
-        <is>
-          <t>18.89</t>
-        </is>
+      <c r="H497" t="n">
+        <v>18.89</v>
       </c>
     </row>
     <row r="498">
@@ -18669,11 +18667,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H498" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -18707,10 +18701,8 @@
           <t>11.13%</t>
         </is>
       </c>
-      <c r="H499" t="inlineStr">
-        <is>
-          <t>48.64</t>
-        </is>
+      <c r="H499" t="n">
+        <v>48.64</v>
       </c>
     </row>
     <row r="500">
@@ -18745,10 +18737,8 @@
           <t>3.17%</t>
         </is>
       </c>
-      <c r="H500" t="inlineStr">
-        <is>
-          <t>18.10</t>
-        </is>
+      <c r="H500" t="n">
+        <v>18.1</v>
       </c>
     </row>
     <row r="501">
@@ -18783,10 +18773,8 @@
           <t>3.75%</t>
         </is>
       </c>
-      <c r="H501" t="inlineStr">
-        <is>
-          <t>17.59</t>
-        </is>
+      <c r="H501" t="n">
+        <v>17.59</v>
       </c>
     </row>
     <row r="502">
@@ -18821,10 +18809,8 @@
           <t>3.82%</t>
         </is>
       </c>
-      <c r="H502" t="inlineStr">
-        <is>
-          <t>19.43</t>
-        </is>
+      <c r="H502" t="n">
+        <v>19.43</v>
       </c>
     </row>
     <row r="503">
@@ -18859,10 +18845,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H503" t="inlineStr">
-        <is>
-          <t>43.66</t>
-        </is>
+      <c r="H503" t="n">
+        <v>43.66</v>
       </c>
     </row>
     <row r="504">
@@ -18897,10 +18881,8 @@
           <t>1.50%</t>
         </is>
       </c>
-      <c r="H504" t="inlineStr">
-        <is>
-          <t>32.35</t>
-        </is>
+      <c r="H504" t="n">
+        <v>32.35</v>
       </c>
     </row>
     <row r="505">
@@ -18935,10 +18917,8 @@
           <t>3.21%</t>
         </is>
       </c>
-      <c r="H505" t="inlineStr">
-        <is>
-          <t>30.77</t>
-        </is>
+      <c r="H505" t="n">
+        <v>30.77</v>
       </c>
     </row>
     <row r="506">
@@ -18973,10 +18953,8 @@
           <t>10.58%</t>
         </is>
       </c>
-      <c r="H506" t="inlineStr">
-        <is>
-          <t>30.17</t>
-        </is>
+      <c r="H506" t="n">
+        <v>30.17</v>
       </c>
     </row>
     <row r="507">
@@ -19011,9 +18989,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H507" t="inlineStr">
-        <is>
-          <t>32.80</t>
+      <c r="H507" t="n">
+        <v>32.8</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>121</v>
+      </c>
+      <c r="D508" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>-2.81%</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>201.64%</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>2.16%</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>18.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="D509" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>-0.22%</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>31.40%</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="D510" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>2.79%</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>-1.30%</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>10.83%</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="D511" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>108.72%</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>3.16%</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>18.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>37.65</v>
+      </c>
+      <c r="D512" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>0.94%</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>13.75%</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>3.72%</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>17.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>47.35</v>
+      </c>
+      <c r="D513" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>3.27%</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>14.75%</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>3.70%</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>20.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="D514" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>-0.84%</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>156.13%</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>43.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="D515" t="n">
+        <v>0</v>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>104.25%</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>1.50%</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>32.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="D516" t="n">
+        <v>0</v>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>100.40%</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>3.21%</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>30.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>36.65</v>
+      </c>
+      <c r="D517" t="n">
+        <v>0</v>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>132.53%</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>10.78%</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>29.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="D518" t="n">
+        <v>0</v>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>54.90%</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>32.74</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>121</v>
+        <v>121.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.5</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-2.81%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>201.64%</t>
+          <t>205.89%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>18.44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.6</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.05</v>
+        <v>-0.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-2.65%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31.40%</t>
+          <t>25.00%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.5</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>-1.69%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.30%</t>
+          <t>-1.32%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.83%</t>
+          <t>11.02%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>49.15</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31.65</v>
+        <v>31.4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.15</v>
+        <v>-0.25</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>108.72%</t>
+          <t>105.77%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.18%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>18.19</t>
+          <t>18.05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37.65</v>
+        <v>37.75</v>
       </c>
       <c r="D6" t="n">
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13.75%</t>
+          <t>14.55%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.71%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17.76</t>
+          <t>17.81</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>47.35</v>
+        <v>46.6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5</v>
+        <v>-0.75</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>-1.58%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14.75%</t>
+          <t>13.07%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.76%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>19.75</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.75</v>
+        <v>17.85</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.15</v>
+        <v>0.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>156.13%</t>
+          <t>147.92%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>43.29</t>
+          <t>43.54</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>106.4</v>
+        <v>106.45</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>104.25%</t>
+          <t>103.77%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -771,14 +771,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>32.27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,19 +787,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>91.8</v>
+        <v>92</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>100.40%</t>
+          <t>99.06%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -809,14 +809,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.82</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.65</v>
+        <v>36.4</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>132.53%</t>
+          <t>133.29%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.78%</t>
+          <t>10.85%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>29.41</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.49</v>
+        <v>15.52</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>54.90%</t>
+          <t>55.20%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>32.80</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H518"/>
+  <dimension ref="A1:H529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19025,10 +19025,8 @@
           <t>2.16%</t>
         </is>
       </c>
-      <c r="H508" t="inlineStr">
-        <is>
-          <t>18.36</t>
-        </is>
+      <c r="H508" t="n">
+        <v>18.36</v>
       </c>
     </row>
     <row r="509">
@@ -19063,11 +19061,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H509" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -19101,10 +19095,8 @@
           <t>10.83%</t>
         </is>
       </c>
-      <c r="H510" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="H510" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="511">
@@ -19139,10 +19131,8 @@
           <t>3.16%</t>
         </is>
       </c>
-      <c r="H511" t="inlineStr">
-        <is>
-          <t>18.19</t>
-        </is>
+      <c r="H511" t="n">
+        <v>18.19</v>
       </c>
     </row>
     <row r="512">
@@ -19177,10 +19167,8 @@
           <t>3.72%</t>
         </is>
       </c>
-      <c r="H512" t="inlineStr">
-        <is>
-          <t>17.76</t>
-        </is>
+      <c r="H512" t="n">
+        <v>17.76</v>
       </c>
     </row>
     <row r="513">
@@ -19215,10 +19203,8 @@
           <t>3.70%</t>
         </is>
       </c>
-      <c r="H513" t="inlineStr">
-        <is>
-          <t>20.06</t>
-        </is>
+      <c r="H513" t="n">
+        <v>20.06</v>
       </c>
     </row>
     <row r="514">
@@ -19253,10 +19239,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H514" t="inlineStr">
-        <is>
-          <t>43.29</t>
-        </is>
+      <c r="H514" t="n">
+        <v>43.29</v>
       </c>
     </row>
     <row r="515">
@@ -19291,10 +19275,8 @@
           <t>1.50%</t>
         </is>
       </c>
-      <c r="H515" t="inlineStr">
-        <is>
-          <t>32.26</t>
-        </is>
+      <c r="H515" t="n">
+        <v>32.26</v>
       </c>
     </row>
     <row r="516">
@@ -19329,10 +19311,8 @@
           <t>3.21%</t>
         </is>
       </c>
-      <c r="H516" t="inlineStr">
-        <is>
-          <t>30.75</t>
-        </is>
+      <c r="H516" t="n">
+        <v>30.75</v>
       </c>
     </row>
     <row r="517">
@@ -19367,10 +19347,8 @@
           <t>10.78%</t>
         </is>
       </c>
-      <c r="H517" t="inlineStr">
-        <is>
-          <t>29.62</t>
-        </is>
+      <c r="H517" t="n">
+        <v>29.62</v>
       </c>
     </row>
     <row r="518">
@@ -19405,9 +19383,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H518" t="inlineStr">
-        <is>
-          <t>32.74</t>
+      <c r="H518" t="n">
+        <v>32.74</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="D519" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>205.89%</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>2.15%</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>18.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>22</v>
+      </c>
+      <c r="D520" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>-2.65%</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>25.00%</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>29</v>
+      </c>
+      <c r="D521" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>-1.69%</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>-1.32%</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>11.02%</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="D522" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>-0.79%</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>105.77%</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>3.18%</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>18.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="D523" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>14.55%</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>3.71%</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>17.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="D524" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>-1.58%</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>13.07%</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>3.76%</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="D525" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>0.56%</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>147.92%</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>43.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C526" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="D526" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>103.77%</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>1.50%</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>32.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C527" t="n">
+        <v>92</v>
+      </c>
+      <c r="D527" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>0.22%</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>99.06%</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>3.21%</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>30.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C528" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="D528" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>133.29%</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>10.85%</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>29.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C529" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="D529" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>55.20%</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>32.80</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>121.5</v>
+        <v>119</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>-2.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>-2.06%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>205.89%</t>
+          <t>199.60%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.19%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>18.06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.65%</t>
+          <t>-4.55%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.00%</t>
+          <t>19.32%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>28.35</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5</v>
+        <v>-0.65</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.69%</t>
+          <t>-2.24%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>-3.53%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.02%</t>
+          <t>11.27%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>36.35</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31.4</v>
+        <v>30.95</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.25</v>
+        <v>-0.45</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>105.77%</t>
+          <t>102.83%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.79</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37.75</v>
+        <v>38.1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14.55%</t>
+          <t>15.62%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.71%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17.81</t>
+          <t>17.97</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.6</v>
+        <v>46.9</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.75</v>
+        <v>0.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.58%</t>
+          <t>0.64%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>13.07%</t>
+          <t>13.80%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>3.73%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.87</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.85</v>
+        <v>17.05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>-4.48%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>147.92%</t>
+          <t>136.81%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>41.59</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>106.45</v>
+        <v>104.9</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>-1.55</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>103.77%</t>
+          <t>100.80%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>31.80</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>92</v>
+        <v>90.45</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2</v>
+        <v>-1.55</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>99.06%</t>
+          <t>95.71%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.26%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.82</t>
+          <t>30.30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.4</v>
+        <v>35.65</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.25</v>
+        <v>-0.75</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.06%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>133.29%</t>
+          <t>128.48%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.85%</t>
+          <t>11.08%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>28.81</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.52</v>
+        <v>15.31</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>55.20%</t>
+          <t>53.10%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>32.36</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H529"/>
+  <dimension ref="A1:H540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19419,10 +19419,8 @@
           <t>2.15%</t>
         </is>
       </c>
-      <c r="H519" t="inlineStr">
-        <is>
-          <t>18.44</t>
-        </is>
+      <c r="H519" t="n">
+        <v>18.44</v>
       </c>
     </row>
     <row r="520">
@@ -19457,11 +19455,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H520" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -19495,10 +19489,8 @@
           <t>11.02%</t>
         </is>
       </c>
-      <c r="H521" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
+      <c r="H521" t="n">
+        <v>49.15</v>
       </c>
     </row>
     <row r="522">
@@ -19533,10 +19525,8 @@
           <t>3.18%</t>
         </is>
       </c>
-      <c r="H522" t="inlineStr">
-        <is>
-          <t>18.05</t>
-        </is>
+      <c r="H522" t="n">
+        <v>18.05</v>
       </c>
     </row>
     <row r="523">
@@ -19571,10 +19561,8 @@
           <t>3.71%</t>
         </is>
       </c>
-      <c r="H523" t="inlineStr">
-        <is>
-          <t>17.81</t>
-        </is>
+      <c r="H523" t="n">
+        <v>17.81</v>
       </c>
     </row>
     <row r="524">
@@ -19609,10 +19597,8 @@
           <t>3.76%</t>
         </is>
       </c>
-      <c r="H524" t="inlineStr">
-        <is>
-          <t>19.75</t>
-        </is>
+      <c r="H524" t="n">
+        <v>19.75</v>
       </c>
     </row>
     <row r="525">
@@ -19647,10 +19633,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H525" t="inlineStr">
-        <is>
-          <t>43.54</t>
-        </is>
+      <c r="H525" t="n">
+        <v>43.54</v>
       </c>
     </row>
     <row r="526">
@@ -19685,10 +19669,8 @@
           <t>1.50%</t>
         </is>
       </c>
-      <c r="H526" t="inlineStr">
-        <is>
-          <t>32.27</t>
-        </is>
+      <c r="H526" t="n">
+        <v>32.27</v>
       </c>
     </row>
     <row r="527">
@@ -19723,10 +19705,8 @@
           <t>3.21%</t>
         </is>
       </c>
-      <c r="H527" t="inlineStr">
-        <is>
-          <t>30.82</t>
-        </is>
+      <c r="H527" t="n">
+        <v>30.82</v>
       </c>
     </row>
     <row r="528">
@@ -19761,10 +19741,8 @@
           <t>10.85%</t>
         </is>
       </c>
-      <c r="H528" t="inlineStr">
-        <is>
-          <t>29.41</t>
-        </is>
+      <c r="H528" t="n">
+        <v>29.41</v>
       </c>
     </row>
     <row r="529">
@@ -19799,9 +19777,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H529" t="inlineStr">
-        <is>
-          <t>32.80</t>
+      <c r="H529" t="n">
+        <v>32.8</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C530" t="n">
+        <v>119</v>
+      </c>
+      <c r="D530" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>-2.06%</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>199.60%</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>2.19%</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>18.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C531" t="n">
+        <v>21</v>
+      </c>
+      <c r="D531" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>-4.55%</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>19.32%</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C532" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="D532" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>-2.24%</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>-3.53%</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>11.27%</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>36.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C533" t="n">
+        <v>30.95</v>
+      </c>
+      <c r="D533" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>-1.43%</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>102.83%</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>3.23%</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>17.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C534" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="D534" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>0.93%</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>15.62%</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>3.67%</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>17.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C535" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="D535" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>0.64%</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>13.80%</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>3.73%</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>19.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C536" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="D536" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>-4.48%</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>136.81%</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>41.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="D537" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>-1.46%</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>100.80%</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>1.53%</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>31.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C538" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="D538" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>-1.68%</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>95.71%</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>3.26%</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>30.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C539" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="D539" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>-2.06%</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>128.48%</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>11.08%</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>28.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C540" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="D540" t="n">
+        <v>0</v>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>53.10%</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>32.36</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>119</v>
+        <v>115.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.5</v>
+        <v>-3.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-2.06%</t>
+          <t>-2.94%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>199.60%</t>
+          <t>186.18%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18.06</t>
+          <t>17.53</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="D3" t="n">
-        <v>-1</v>
+        <v>-0.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-4.55%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.32%</t>
+          <t>16.29%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.35</v>
+        <v>28.75</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.65</v>
+        <v>0.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-2.24%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-3.53%</t>
+          <t>-4.16%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.27%</t>
+          <t>11.11%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>36.86</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.95</v>
+        <v>30.4</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.45</v>
+        <v>-0.55</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-1.78%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>102.83%</t>
+          <t>99.85%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.79</t>
+          <t>17.47</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="D6" t="n">
-        <v>0.35</v>
+        <v>-0.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>15.62%</t>
+          <t>15.21%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>17.83</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.9</v>
+        <v>47.05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>13.80%</t>
+          <t>15.51%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.73%</t>
+          <t>3.72%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.87</t>
+          <t>19.94</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.05</v>
+        <v>16.75</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8</v>
+        <v>-0.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-4.48%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>136.81%</t>
+          <t>131.03%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>40.85</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>104.9</v>
+        <v>103.1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.55</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>100.80%</t>
+          <t>97.73%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.80</t>
+          <t>31.26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>90.45</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.55</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>95.71%</t>
+          <t>93.90%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.31%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.30</t>
+          <t>29.85</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35.65</v>
+        <v>35.36</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.75</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-2.06%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>128.48%</t>
+          <t>128.17%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.08%</t>
+          <t>11.17%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>28.57</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.31</v>
+        <v>15.11</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53.10%</t>
+          <t>51.10%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>31.94</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H540"/>
+  <dimension ref="A1:H551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19813,10 +19813,8 @@
           <t>2.19%</t>
         </is>
       </c>
-      <c r="H530" t="inlineStr">
-        <is>
-          <t>18.06</t>
-        </is>
+      <c r="H530" t="n">
+        <v>18.06</v>
       </c>
     </row>
     <row r="531">
@@ -19851,11 +19849,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H531" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -19889,10 +19883,8 @@
           <t>11.27%</t>
         </is>
       </c>
-      <c r="H532" t="inlineStr">
-        <is>
-          <t>36.35</t>
-        </is>
+      <c r="H532" t="n">
+        <v>36.35</v>
       </c>
     </row>
     <row r="533">
@@ -19927,10 +19919,8 @@
           <t>3.23%</t>
         </is>
       </c>
-      <c r="H533" t="inlineStr">
-        <is>
-          <t>17.79</t>
-        </is>
+      <c r="H533" t="n">
+        <v>17.79</v>
       </c>
     </row>
     <row r="534">
@@ -19965,10 +19955,8 @@
           <t>3.67%</t>
         </is>
       </c>
-      <c r="H534" t="inlineStr">
-        <is>
-          <t>17.97</t>
-        </is>
+      <c r="H534" t="n">
+        <v>17.97</v>
       </c>
     </row>
     <row r="535">
@@ -20003,10 +19991,8 @@
           <t>3.73%</t>
         </is>
       </c>
-      <c r="H535" t="inlineStr">
-        <is>
-          <t>19.87</t>
-        </is>
+      <c r="H535" t="n">
+        <v>19.87</v>
       </c>
     </row>
     <row r="536">
@@ -20041,10 +20027,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H536" t="inlineStr">
-        <is>
-          <t>41.59</t>
-        </is>
+      <c r="H536" t="n">
+        <v>41.59</v>
       </c>
     </row>
     <row r="537">
@@ -20079,10 +20063,8 @@
           <t>1.53%</t>
         </is>
       </c>
-      <c r="H537" t="inlineStr">
-        <is>
-          <t>31.80</t>
-        </is>
+      <c r="H537" t="n">
+        <v>31.8</v>
       </c>
     </row>
     <row r="538">
@@ -20117,10 +20099,8 @@
           <t>3.26%</t>
         </is>
       </c>
-      <c r="H538" t="inlineStr">
-        <is>
-          <t>30.30</t>
-        </is>
+      <c r="H538" t="n">
+        <v>30.3</v>
       </c>
     </row>
     <row r="539">
@@ -20155,10 +20135,8 @@
           <t>11.08%</t>
         </is>
       </c>
-      <c r="H539" t="inlineStr">
-        <is>
-          <t>28.81</t>
-        </is>
+      <c r="H539" t="n">
+        <v>28.81</v>
       </c>
     </row>
     <row r="540">
@@ -20193,9 +20171,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H540" t="inlineStr">
-        <is>
-          <t>32.36</t>
+      <c r="H540" t="n">
+        <v>32.36</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C541" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="D541" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>-2.94%</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>186.18%</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>2.26%</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>17.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C542" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="D542" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>-1.43%</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>16.29%</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C543" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="D543" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>1.41%</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>-4.16%</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>11.11%</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>36.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C544" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="D544" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>-1.78%</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>99.85%</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>3.29%</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>17.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C545" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="D545" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>-0.79%</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>15.21%</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>3.70%</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>17.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C546" t="n">
+        <v>47.05</v>
+      </c>
+      <c r="D546" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>15.51%</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>3.72%</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>19.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C547" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="D547" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>-1.76%</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>131.03%</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>40.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C548" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="D548" t="n">
+        <v>0</v>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>97.73%</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>1.55%</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>31.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C549" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="D549" t="n">
+        <v>0</v>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>93.90%</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>3.31%</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>29.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C550" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="D550" t="n">
+        <v>0</v>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>128.17%</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>11.17%</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>28.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="D551" t="n">
+        <v>0</v>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>51.10%</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>31.94</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,16 +486,16 @@
         <v>115.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.5</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-2.94%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>186.18%</t>
+          <t>180.37%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -505,14 +505,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.29%</t>
+          <t>17.82%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.75</v>
+        <v>29.25</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-4.16%</t>
+          <t>-2.49%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.11%</t>
+          <t>10.92%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36.86</t>
+          <t>37.50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -600,16 +600,16 @@
         <v>30.4</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.55</v>
+        <v>0</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>99.85%</t>
+          <t>101.75%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -626,7 +626,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37.8</v>
+        <v>37.35</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3</v>
+        <v>-0.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>15.21%</t>
+          <t>14.84%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17.83</t>
+          <t>17.62</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>47.05</v>
+        <v>46.4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.15</v>
+        <v>-0.65</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>15.51%</t>
+          <t>15.14%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.77%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>19.66</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.75</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>131.03%</t>
+          <t>140.79%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.46</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>103.1</v>
+        <v>103.8</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -761,24 +761,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>97.73%</t>
+          <t>104.85%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.26</t>
+          <t>31.47</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>89.09999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -799,7 +799,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>93.90%</t>
+          <t>99.24%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -809,14 +809,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>29.88</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35.36</v>
+        <v>35.3</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -837,24 +837,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>128.17%</t>
+          <t>133.61%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.17%</t>
+          <t>11.19%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>28.53</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.11</v>
+        <v>15.13</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>51.10%</t>
+          <t>51.30%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>31.98</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H551"/>
+  <dimension ref="A1:H562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20207,10 +20207,8 @@
           <t>2.26%</t>
         </is>
       </c>
-      <c r="H541" t="inlineStr">
-        <is>
-          <t>17.53</t>
-        </is>
+      <c r="H541" t="n">
+        <v>17.53</v>
       </c>
     </row>
     <row r="542">
@@ -20245,11 +20243,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H542" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -20283,10 +20277,8 @@
           <t>11.11%</t>
         </is>
       </c>
-      <c r="H543" t="inlineStr">
-        <is>
-          <t>36.86</t>
-        </is>
+      <c r="H543" t="n">
+        <v>36.86</v>
       </c>
     </row>
     <row r="544">
@@ -20321,10 +20313,8 @@
           <t>3.29%</t>
         </is>
       </c>
-      <c r="H544" t="inlineStr">
-        <is>
-          <t>17.47</t>
-        </is>
+      <c r="H544" t="n">
+        <v>17.47</v>
       </c>
     </row>
     <row r="545">
@@ -20359,10 +20349,8 @@
           <t>3.70%</t>
         </is>
       </c>
-      <c r="H545" t="inlineStr">
-        <is>
-          <t>17.83</t>
-        </is>
+      <c r="H545" t="n">
+        <v>17.83</v>
       </c>
     </row>
     <row r="546">
@@ -20397,10 +20385,8 @@
           <t>3.72%</t>
         </is>
       </c>
-      <c r="H546" t="inlineStr">
-        <is>
-          <t>19.94</t>
-        </is>
+      <c r="H546" t="n">
+        <v>19.94</v>
       </c>
     </row>
     <row r="547">
@@ -20435,10 +20421,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H547" t="inlineStr">
-        <is>
-          <t>40.85</t>
-        </is>
+      <c r="H547" t="n">
+        <v>40.85</v>
       </c>
     </row>
     <row r="548">
@@ -20473,10 +20457,8 @@
           <t>1.55%</t>
         </is>
       </c>
-      <c r="H548" t="inlineStr">
-        <is>
-          <t>31.26</t>
-        </is>
+      <c r="H548" t="n">
+        <v>31.26</v>
       </c>
     </row>
     <row r="549">
@@ -20511,10 +20493,8 @@
           <t>3.31%</t>
         </is>
       </c>
-      <c r="H549" t="inlineStr">
-        <is>
-          <t>29.85</t>
-        </is>
+      <c r="H549" t="n">
+        <v>29.85</v>
       </c>
     </row>
     <row r="550">
@@ -20549,10 +20529,8 @@
           <t>11.17%</t>
         </is>
       </c>
-      <c r="H550" t="inlineStr">
-        <is>
-          <t>28.57</t>
-        </is>
+      <c r="H550" t="n">
+        <v>28.57</v>
       </c>
     </row>
     <row r="551">
@@ -20587,9 +20565,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H551" t="inlineStr">
-        <is>
-          <t>31.94</t>
+      <c r="H551" t="n">
+        <v>31.94</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="D552" t="n">
+        <v>0</v>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>180.37%</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>2.26%</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>17.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D553" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>-0.97%</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>17.82%</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="D554" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>1.74%</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>-2.49%</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>10.92%</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>37.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="D555" t="n">
+        <v>0</v>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>101.75%</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>3.29%</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>17.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="D556" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>-1.19%</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>14.84%</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>17.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="D557" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>-1.38%</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>15.14%</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>3.77%</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>19.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>17</v>
+      </c>
+      <c r="D558" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>1.49%</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>140.79%</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>41.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="D559" t="n">
+        <v>0</v>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>104.85%</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>1.54%</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>31.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="D560" t="n">
+        <v>0</v>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>99.24%</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>3.31%</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>29.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="D561" t="n">
+        <v>0</v>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>133.61%</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>11.19%</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>28.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="D562" t="n">
+        <v>0</v>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>51.30%</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>31.98</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>115.5</v>
+        <v>116.5</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>180.37%</t>
+          <t>186.22%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.24%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>17.50</t>
+          <t>17.65</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.82%</t>
+          <t>17.78%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.25</v>
+        <v>28.8</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>-0.45</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>-5.91%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.92%</t>
+          <t>11.09%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.50</t>
+          <t>36.92</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.4</v>
+        <v>31.55</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.78%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>101.75%</t>
+          <t>106.11%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>18.13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37.35</v>
+        <v>38</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.45</v>
+        <v>0.65</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14.84%</t>
+          <t>17.36%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>3.68%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17.62</t>
+          <t>17.92</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.4</v>
+        <v>46.95</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.65</v>
+        <v>0.55</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>15.14%</t>
+          <t>17.21%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.77%</t>
+          <t>3.73%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>19.89</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>140.79%</t>
+          <t>143.66%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>42.20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>103.8</v>
+        <v>104.65</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -761,24 +761,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>104.85%</t>
+          <t>105.33%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.47</t>
+          <t>31.73</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>89.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -799,24 +799,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>99.24%</t>
+          <t>95.96%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>2.65%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>29.68</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35.3</v>
+        <v>35.45</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -837,24 +837,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>133.61%</t>
+          <t>131.77%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.19%</t>
+          <t>11.14%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28.65</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.13</v>
+        <v>15.25</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>51.30%</t>
+          <t>52.50%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>32.23</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H562"/>
+  <dimension ref="A1:H573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20601,10 +20601,8 @@
           <t>2.26%</t>
         </is>
       </c>
-      <c r="H552" t="inlineStr">
-        <is>
-          <t>17.50</t>
-        </is>
+      <c r="H552" t="n">
+        <v>17.5</v>
       </c>
     </row>
     <row r="553">
@@ -20639,11 +20637,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H553" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -20677,10 +20671,8 @@
           <t>10.92%</t>
         </is>
       </c>
-      <c r="H554" t="inlineStr">
-        <is>
-          <t>37.50</t>
-        </is>
+      <c r="H554" t="n">
+        <v>37.5</v>
       </c>
     </row>
     <row r="555">
@@ -20715,10 +20707,8 @@
           <t>3.29%</t>
         </is>
       </c>
-      <c r="H555" t="inlineStr">
-        <is>
-          <t>17.47</t>
-        </is>
+      <c r="H555" t="n">
+        <v>17.47</v>
       </c>
     </row>
     <row r="556">
@@ -20753,10 +20743,8 @@
           <t>3.75%</t>
         </is>
       </c>
-      <c r="H556" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="H556" t="n">
+        <v>17.62</v>
       </c>
     </row>
     <row r="557">
@@ -20791,10 +20779,8 @@
           <t>3.77%</t>
         </is>
       </c>
-      <c r="H557" t="inlineStr">
-        <is>
-          <t>19.66</t>
-        </is>
+      <c r="H557" t="n">
+        <v>19.66</v>
       </c>
     </row>
     <row r="558">
@@ -20829,10 +20815,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H558" t="inlineStr">
-        <is>
-          <t>41.46</t>
-        </is>
+      <c r="H558" t="n">
+        <v>41.46</v>
       </c>
     </row>
     <row r="559">
@@ -20867,10 +20851,8 @@
           <t>1.54%</t>
         </is>
       </c>
-      <c r="H559" t="inlineStr">
-        <is>
-          <t>31.47</t>
-        </is>
+      <c r="H559" t="n">
+        <v>31.47</v>
       </c>
     </row>
     <row r="560">
@@ -20905,10 +20887,8 @@
           <t>3.31%</t>
         </is>
       </c>
-      <c r="H560" t="inlineStr">
-        <is>
-          <t>29.88</t>
-        </is>
+      <c r="H560" t="n">
+        <v>29.88</v>
       </c>
     </row>
     <row r="561">
@@ -20943,10 +20923,8 @@
           <t>11.19%</t>
         </is>
       </c>
-      <c r="H561" t="inlineStr">
-        <is>
-          <t>28.53</t>
-        </is>
+      <c r="H561" t="n">
+        <v>28.53</v>
       </c>
     </row>
     <row r="562">
@@ -20981,9 +20959,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H562" t="inlineStr">
-        <is>
-          <t>31.98</t>
+      <c r="H562" t="n">
+        <v>31.98</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="D563" t="n">
+        <v>1</v>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>186.22%</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>2.24%</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>17.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="D564" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>-1.46%</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>17.78%</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C565" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D565" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>-1.54%</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>-5.91%</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>11.09%</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>36.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C566" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="D566" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>3.78%</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>106.11%</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>18.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
+        <v>38</v>
+      </c>
+      <c r="D567" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>1.74%</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>17.36%</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>3.68%</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>17.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C568" t="n">
+        <v>46.95</v>
+      </c>
+      <c r="D568" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>1.19%</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>17.21%</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>3.73%</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>19.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C569" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="D569" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>1.76%</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>143.66%</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>42.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C570" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="D570" t="n">
+        <v>0</v>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>105.33%</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>1.53%</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>31.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C571" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="D571" t="n">
+        <v>0</v>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>95.96%</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>2.65%</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>29.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="D572" t="n">
+        <v>0</v>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>131.77%</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>11.14%</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>28.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="D573" t="n">
+        <v>0</v>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>52.50%</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>32.23</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>116.5</v>
+        <v>123.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>6.01%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>186.22%</t>
+          <t>209.77%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>18.74</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.2</v>
+        <v>20.35</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3</v>
+        <v>0.15</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>0.74%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.78%</t>
+          <t>16.62%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.8</v>
+        <v>28.65</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.45</v>
+        <v>-0.15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-5.91%</t>
+          <t>-22.54%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.09%</t>
+          <t>11.15%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>36.73</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31.55</v>
+        <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>1.15</v>
+        <v>-0.55</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.78%</t>
+          <t>-1.74%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>106.11%</t>
+          <t>102.52%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>17.82</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38</v>
+        <v>38.15</v>
       </c>
       <c r="D6" t="n">
-        <v>0.65</v>
+        <v>0.15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.36%</t>
+          <t>19.06%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17.92</t>
+          <t>18.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.95</v>
+        <v>46.85</v>
       </c>
       <c r="D7" t="n">
-        <v>0.55</v>
+        <v>-0.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.21%</t>
+          <t>18.53%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.73%</t>
+          <t>3.74%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.89</t>
+          <t>19.85</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.3</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>143.66%</t>
+          <t>152.98%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>42.20</t>
+          <t>41.46</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>104.65</v>
+        <v>103.8</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.85</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>105.33%</t>
+          <t>100.96%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.73</t>
+          <t>31.47</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>88.59999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>95.96%</t>
+          <t>93.99%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>3.62%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>29.68</t>
+          <t>29.58</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35.45</v>
+        <v>35.83</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>131.77%</t>
+          <t>131.33%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.14%</t>
+          <t>11.02%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.95</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.25</v>
+        <v>15.12</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.85%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>52.50%</t>
+          <t>51.20%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>31.96</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H573"/>
+  <dimension ref="A1:H584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20995,10 +20995,8 @@
           <t>2.24%</t>
         </is>
       </c>
-      <c r="H563" t="inlineStr">
-        <is>
-          <t>17.65</t>
-        </is>
+      <c r="H563" t="n">
+        <v>17.65</v>
       </c>
     </row>
     <row r="564">
@@ -21033,11 +21031,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H564" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -21071,10 +21065,8 @@
           <t>11.09%</t>
         </is>
       </c>
-      <c r="H565" t="inlineStr">
-        <is>
-          <t>36.92</t>
-        </is>
+      <c r="H565" t="n">
+        <v>36.92</v>
       </c>
     </row>
     <row r="566">
@@ -21109,10 +21101,8 @@
           <t>3.17%</t>
         </is>
       </c>
-      <c r="H566" t="inlineStr">
-        <is>
-          <t>18.13</t>
-        </is>
+      <c r="H566" t="n">
+        <v>18.13</v>
       </c>
     </row>
     <row r="567">
@@ -21147,10 +21137,8 @@
           <t>3.68%</t>
         </is>
       </c>
-      <c r="H567" t="inlineStr">
-        <is>
-          <t>17.92</t>
-        </is>
+      <c r="H567" t="n">
+        <v>17.92</v>
       </c>
     </row>
     <row r="568">
@@ -21185,10 +21173,8 @@
           <t>3.73%</t>
         </is>
       </c>
-      <c r="H568" t="inlineStr">
-        <is>
-          <t>19.89</t>
-        </is>
+      <c r="H568" t="n">
+        <v>19.89</v>
       </c>
     </row>
     <row r="569">
@@ -21223,10 +21209,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H569" t="inlineStr">
-        <is>
-          <t>42.20</t>
-        </is>
+      <c r="H569" t="n">
+        <v>42.2</v>
       </c>
     </row>
     <row r="570">
@@ -21261,10 +21245,8 @@
           <t>1.53%</t>
         </is>
       </c>
-      <c r="H570" t="inlineStr">
-        <is>
-          <t>31.73</t>
-        </is>
+      <c r="H570" t="n">
+        <v>31.73</v>
       </c>
     </row>
     <row r="571">
@@ -21299,10 +21281,8 @@
           <t>2.65%</t>
         </is>
       </c>
-      <c r="H571" t="inlineStr">
-        <is>
-          <t>29.68</t>
-        </is>
+      <c r="H571" t="n">
+        <v>29.68</v>
       </c>
     </row>
     <row r="572">
@@ -21337,10 +21317,8 @@
           <t>11.14%</t>
         </is>
       </c>
-      <c r="H572" t="inlineStr">
-        <is>
-          <t>28.65</t>
-        </is>
+      <c r="H572" t="n">
+        <v>28.65</v>
       </c>
     </row>
     <row r="573">
@@ -21375,9 +21353,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H573" t="inlineStr">
-        <is>
-          <t>32.23</t>
+      <c r="H573" t="n">
+        <v>32.23</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="D574" t="n">
+        <v>7</v>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>6.01%</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>209.77%</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>2.11%</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>18.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="D575" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>0.74%</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>16.62%</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="D576" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>-0.52%</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>-22.54%</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>11.15%</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>36.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>31</v>
+      </c>
+      <c r="D577" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>-1.74%</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>102.52%</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>3.23%</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>17.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="D578" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>19.06%</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>3.67%</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C579" t="n">
+        <v>46.85</v>
+      </c>
+      <c r="D579" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>18.53%</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>3.74%</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>19.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
+        <v>17</v>
+      </c>
+      <c r="D580" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>-1.73%</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>152.98%</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>41.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="D581" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>-0.81%</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>100.96%</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>1.54%</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>31.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="D582" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>-0.34%</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>93.99%</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>3.62%</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>29.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C583" t="n">
+        <v>35.83</v>
+      </c>
+      <c r="D583" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>1.07%</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>131.33%</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>11.02%</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>28.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C584" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="D584" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>51.20%</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>31.96</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>123.5</v>
+        <v>125</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6.01%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>209.77%</t>
+          <t>213.54%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.97</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.35</v>
+        <v>20.1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.15</v>
+        <v>-0.25</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.62%</t>
+          <t>15.19%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.65</v>
+        <v>28.15</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-22.54%</t>
+          <t>-23.89%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.15%</t>
+          <t>11.35%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>36.09</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31</v>
+        <v>31.7</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.55</v>
+        <v>0.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.74%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>102.52%</t>
+          <t>107.09%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.82</t>
+          <t>18.22</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38.15</v>
+        <v>39</v>
       </c>
       <c r="D6" t="n">
-        <v>0.15</v>
+        <v>0.85</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.06%</t>
+          <t>21.71%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>3.59%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>18.40</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.85</v>
+        <v>47</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1</v>
+        <v>0.15</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.53%</t>
+          <t>18.91%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>3.72%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.92</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>152.98%</t>
+          <t>154.46%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>32.26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>103.8</v>
+        <v>104.4</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.85</v>
+        <v>0.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>0.58%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>100.96%</t>
+          <t>102.12%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.47</t>
+          <t>31.65</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>88.3</v>
+        <v>88.8</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>93.99%</t>
+          <t>95.09%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>3.60%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>29.58</t>
+          <t>29.75</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -828,11 +828,11 @@
         <v>35.83</v>
       </c>
       <c r="D11" t="n">
-        <v>0.38</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -854,7 +854,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.12</v>
+        <v>15.21</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.13</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>51.20%</t>
+          <t>52.10%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>32.15</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H584"/>
+  <dimension ref="A1:H595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21389,10 +21389,8 @@
           <t>2.11%</t>
         </is>
       </c>
-      <c r="H574" t="inlineStr">
-        <is>
-          <t>18.74</t>
-        </is>
+      <c r="H574" t="n">
+        <v>18.74</v>
       </c>
     </row>
     <row r="575">
@@ -21427,11 +21425,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H575" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -21465,10 +21459,8 @@
           <t>11.15%</t>
         </is>
       </c>
-      <c r="H576" t="inlineStr">
-        <is>
-          <t>36.73</t>
-        </is>
+      <c r="H576" t="n">
+        <v>36.73</v>
       </c>
     </row>
     <row r="577">
@@ -21503,10 +21495,8 @@
           <t>3.23%</t>
         </is>
       </c>
-      <c r="H577" t="inlineStr">
-        <is>
-          <t>17.82</t>
-        </is>
+      <c r="H577" t="n">
+        <v>17.82</v>
       </c>
     </row>
     <row r="578">
@@ -21541,10 +21531,8 @@
           <t>3.67%</t>
         </is>
       </c>
-      <c r="H578" t="inlineStr">
-        <is>
-          <t>18.00</t>
-        </is>
+      <c r="H578" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="579">
@@ -21579,10 +21567,8 @@
           <t>3.74%</t>
         </is>
       </c>
-      <c r="H579" t="inlineStr">
-        <is>
-          <t>19.85</t>
-        </is>
+      <c r="H579" t="n">
+        <v>19.85</v>
       </c>
     </row>
     <row r="580">
@@ -21617,10 +21603,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H580" t="inlineStr">
-        <is>
-          <t>41.46</t>
-        </is>
+      <c r="H580" t="n">
+        <v>41.46</v>
       </c>
     </row>
     <row r="581">
@@ -21655,10 +21639,8 @@
           <t>1.54%</t>
         </is>
       </c>
-      <c r="H581" t="inlineStr">
-        <is>
-          <t>31.47</t>
-        </is>
+      <c r="H581" t="n">
+        <v>31.47</v>
       </c>
     </row>
     <row r="582">
@@ -21693,10 +21675,8 @@
           <t>3.62%</t>
         </is>
       </c>
-      <c r="H582" t="inlineStr">
-        <is>
-          <t>29.58</t>
-        </is>
+      <c r="H582" t="n">
+        <v>29.58</v>
       </c>
     </row>
     <row r="583">
@@ -21731,10 +21711,8 @@
           <t>11.02%</t>
         </is>
       </c>
-      <c r="H583" t="inlineStr">
-        <is>
-          <t>28.95</t>
-        </is>
+      <c r="H583" t="n">
+        <v>28.95</v>
       </c>
     </row>
     <row r="584">
@@ -21769,9 +21747,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H584" t="inlineStr">
-        <is>
-          <t>31.96</t>
+      <c r="H584" t="n">
+        <v>31.96</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C585" t="n">
+        <v>125</v>
+      </c>
+      <c r="D585" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>1.21%</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>213.54%</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>2.09%</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>18.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C586" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="D586" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>-1.23%</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>15.19%</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="D587" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>-1.75%</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>-23.89%</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>11.35%</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>36.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C588" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="D588" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>2.26%</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>107.09%</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>3.15%</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>18.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C589" t="n">
+        <v>39</v>
+      </c>
+      <c r="D589" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>21.71%</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>3.59%</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>18.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C590" t="n">
+        <v>47</v>
+      </c>
+      <c r="D590" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>18.91%</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>3.72%</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>19.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C591" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="D591" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>0.59%</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>154.46%</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>32.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C592" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="D592" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>102.12%</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>1.53%</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>31.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C593" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="D593" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>0.57%</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>95.09%</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>3.60%</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>35.83</v>
+      </c>
+      <c r="D594" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>-0.0%</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>131.33%</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>11.02%</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>28.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C595" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="D595" t="n">
+        <v>0</v>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>52.10%</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>32.15</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>125</v>
+        <v>123.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>213.54%</t>
+          <t>200.51%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.74</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.25</v>
+        <v>-0.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>15.19%</t>
+          <t>12.68%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.15</v>
+        <v>28.1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-23.89%</t>
+          <t>-19.05%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.35%</t>
+          <t>11.37%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36.09</t>
+          <t>36.03</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31.7</v>
+        <v>32.25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>107.09%</t>
+          <t>114.03%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>3.10%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>18.53</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>39</v>
+        <v>38.7</v>
       </c>
       <c r="D6" t="n">
-        <v>0.85</v>
+        <v>-0.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.71%</t>
+          <t>19.70%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>3.62%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>18.40</t>
+          <t>18.25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>47</v>
+        <v>46.6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.15</v>
+        <v>-0.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>-0.85%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.91%</t>
+          <t>20.69%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.76%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>19.75</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.1</v>
+        <v>17.05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>154.46%</t>
+          <t>160.31%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>32.17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>104.4</v>
+        <v>105.9</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>102.12%</t>
+          <t>104.83%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>32.11</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>88.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>95.09%</t>
+          <t>98.69%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.60%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>30.28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35.83</v>
+        <v>36.36</v>
       </c>
       <c r="D11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>131.33%</t>
+          <t>133.16%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.02%</t>
+          <t>10.86%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.38</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.21</v>
+        <v>15.43</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>52.10%</t>
+          <t>54.30%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>32.61</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H595"/>
+  <dimension ref="A1:H606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21783,10 +21783,8 @@
           <t>2.09%</t>
         </is>
       </c>
-      <c r="H585" t="inlineStr">
-        <is>
-          <t>18.97</t>
-        </is>
+      <c r="H585" t="n">
+        <v>18.97</v>
       </c>
     </row>
     <row r="586">
@@ -21821,11 +21819,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H586" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -21859,10 +21853,8 @@
           <t>11.35%</t>
         </is>
       </c>
-      <c r="H587" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
+      <c r="H587" t="n">
+        <v>36.09</v>
       </c>
     </row>
     <row r="588">
@@ -21897,10 +21889,8 @@
           <t>3.15%</t>
         </is>
       </c>
-      <c r="H588" t="inlineStr">
-        <is>
-          <t>18.22</t>
-        </is>
+      <c r="H588" t="n">
+        <v>18.22</v>
       </c>
     </row>
     <row r="589">
@@ -21935,10 +21925,8 @@
           <t>3.59%</t>
         </is>
       </c>
-      <c r="H589" t="inlineStr">
-        <is>
-          <t>18.40</t>
-        </is>
+      <c r="H589" t="n">
+        <v>18.4</v>
       </c>
     </row>
     <row r="590">
@@ -21973,10 +21961,8 @@
           <t>3.72%</t>
         </is>
       </c>
-      <c r="H590" t="inlineStr">
-        <is>
-          <t>19.92</t>
-        </is>
+      <c r="H590" t="n">
+        <v>19.92</v>
       </c>
     </row>
     <row r="591">
@@ -22011,10 +21997,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H591" t="inlineStr">
-        <is>
-          <t>32.26</t>
-        </is>
+      <c r="H591" t="n">
+        <v>32.26</v>
       </c>
     </row>
     <row r="592">
@@ -22049,10 +22033,8 @@
           <t>1.53%</t>
         </is>
       </c>
-      <c r="H592" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
+      <c r="H592" t="n">
+        <v>31.65</v>
       </c>
     </row>
     <row r="593">
@@ -22087,10 +22069,8 @@
           <t>3.60%</t>
         </is>
       </c>
-      <c r="H593" t="inlineStr">
-        <is>
-          <t>29.75</t>
-        </is>
+      <c r="H593" t="n">
+        <v>29.75</v>
       </c>
     </row>
     <row r="594">
@@ -22108,7 +22088,7 @@
         <v>35.83</v>
       </c>
       <c r="D594" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E594" t="inlineStr">
         <is>
@@ -22125,10 +22105,8 @@
           <t>11.02%</t>
         </is>
       </c>
-      <c r="H594" t="inlineStr">
-        <is>
-          <t>28.95</t>
-        </is>
+      <c r="H594" t="n">
+        <v>28.95</v>
       </c>
     </row>
     <row r="595">
@@ -22163,9 +22141,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H595" t="inlineStr">
-        <is>
-          <t>32.15</t>
+      <c r="H595" t="n">
+        <v>32.15</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C596" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="D596" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>-1.2%</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>200.51%</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>2.11%</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>18.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C597" t="n">
+        <v>20</v>
+      </c>
+      <c r="D597" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>12.68%</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="D598" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>-0.18%</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>-19.05%</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>11.37%</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>36.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C599" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="D599" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>1.74%</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>114.03%</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>3.10%</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>18.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C600" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="D600" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>-0.77%</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>19.70%</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>3.62%</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>18.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C601" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="D601" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>20.69%</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>3.76%</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="D602" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>-0.29%</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>160.31%</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>32.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C603" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="D603" t="n">
+        <v>0</v>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>104.83%</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>1.51%</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>32.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C604" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="D604" t="n">
+        <v>0</v>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>98.69%</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>3.54%</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>30.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C605" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="D605" t="n">
+        <v>0</v>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>133.16%</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>10.86%</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>29.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C606" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="D606" t="n">
+        <v>0</v>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>54.30%</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>32.61</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,37 +482,33 @@
           <t>聯電(2303)</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>123.5</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-1.5</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>200.51%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>17.98</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -520,20 +516,16 @@
           <t>友訊(2332)</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>20</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-0.1</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12.68%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +542,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -558,37 +550,33 @@
           <t>佳世達(2352)</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-0.05</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-19.05%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.37%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36.03</t>
+          <t>35.90</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,37 +584,33 @@
           <t>開發金(2883)</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>32.25</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.55</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>114.03%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>18.48</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -634,37 +618,33 @@
           <t>玉山金(2884)</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-0.3</v>
-      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.70%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>18.18</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -672,37 +652,33 @@
           <t>兆豐金(2886)</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-0.4</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.69%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.56</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -710,20 +686,16 @@
           <t>聯合再生(3576)</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>17.05</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-0.05</v>
-      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>160.31%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +712,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,7 +721,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>105.9</v>
+        <v>106.05</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -761,7 +733,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>104.83%</t>
+          <t>104.15%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -771,14 +743,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>32.15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,7 +759,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>90.40000000000001</v>
+        <v>90.55</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -799,24 +771,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>98.69%</t>
+          <t>98.18%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>3.53%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>30.33</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,7 +797,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.36</v>
+        <v>36.25</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -837,24 +809,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>133.16%</t>
+          <t>131.03%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.86%</t>
+          <t>10.90%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>29.38</t>
+          <t>29.29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +835,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.43</v>
+        <v>15.46</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +847,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>54.30%</t>
+          <t>54.60%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +857,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>32.68</t>
         </is>
       </c>
     </row>
@@ -900,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H606"/>
+  <dimension ref="A1:H617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22177,10 +22149,8 @@
           <t>2.11%</t>
         </is>
       </c>
-      <c r="H596" t="inlineStr">
-        <is>
-          <t>18.74</t>
-        </is>
+      <c r="H596" t="n">
+        <v>18.74</v>
       </c>
     </row>
     <row r="597">
@@ -22215,11 +22185,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H597" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -22253,10 +22219,8 @@
           <t>11.37%</t>
         </is>
       </c>
-      <c r="H598" t="inlineStr">
-        <is>
-          <t>36.03</t>
-        </is>
+      <c r="H598" t="n">
+        <v>36.03</v>
       </c>
     </row>
     <row r="599">
@@ -22291,10 +22255,8 @@
           <t>3.10%</t>
         </is>
       </c>
-      <c r="H599" t="inlineStr">
-        <is>
-          <t>18.53</t>
-        </is>
+      <c r="H599" t="n">
+        <v>18.53</v>
       </c>
     </row>
     <row r="600">
@@ -22329,10 +22291,8 @@
           <t>3.62%</t>
         </is>
       </c>
-      <c r="H600" t="inlineStr">
-        <is>
-          <t>18.25</t>
-        </is>
+      <c r="H600" t="n">
+        <v>18.25</v>
       </c>
     </row>
     <row r="601">
@@ -22367,10 +22327,8 @@
           <t>3.76%</t>
         </is>
       </c>
-      <c r="H601" t="inlineStr">
-        <is>
-          <t>19.75</t>
-        </is>
+      <c r="H601" t="n">
+        <v>19.75</v>
       </c>
     </row>
     <row r="602">
@@ -22405,10 +22363,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H602" t="inlineStr">
-        <is>
-          <t>32.17</t>
-        </is>
+      <c r="H602" t="n">
+        <v>32.17</v>
       </c>
     </row>
     <row r="603">
@@ -22443,10 +22399,8 @@
           <t>1.51%</t>
         </is>
       </c>
-      <c r="H603" t="inlineStr">
-        <is>
-          <t>32.11</t>
-        </is>
+      <c r="H603" t="n">
+        <v>32.11</v>
       </c>
     </row>
     <row r="604">
@@ -22481,10 +22435,8 @@
           <t>3.54%</t>
         </is>
       </c>
-      <c r="H604" t="inlineStr">
-        <is>
-          <t>30.28</t>
-        </is>
+      <c r="H604" t="n">
+        <v>30.28</v>
       </c>
     </row>
     <row r="605">
@@ -22519,10 +22471,8 @@
           <t>10.86%</t>
         </is>
       </c>
-      <c r="H605" t="inlineStr">
-        <is>
-          <t>29.38</t>
-        </is>
+      <c r="H605" t="n">
+        <v>29.38</v>
       </c>
     </row>
     <row r="606">
@@ -22557,9 +22507,397 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H606" t="inlineStr">
-        <is>
-          <t>32.61</t>
+      <c r="H606" t="n">
+        <v>32.61</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr"/>
+      <c r="D607" t="inlineStr"/>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>17.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr"/>
+      <c r="D608" t="inlineStr"/>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr"/>
+      <c r="D609" t="inlineStr"/>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>35.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr"/>
+      <c r="D610" t="inlineStr"/>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>18.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr"/>
+      <c r="D611" t="inlineStr"/>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>18.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr"/>
+      <c r="D612" t="inlineStr"/>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>19.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr"/>
+      <c r="D613" t="inlineStr"/>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>32.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C614" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="D614" t="n">
+        <v>0</v>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>104.15%</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>1.51%</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>32.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C615" t="n">
+        <v>90.55</v>
+      </c>
+      <c r="D615" t="n">
+        <v>0</v>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>98.18%</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>3.53%</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>30.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C616" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="D616" t="n">
+        <v>0</v>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>131.03%</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>10.90%</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>29.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C617" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="D617" t="n">
+        <v>0</v>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>54.60%</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>32.68</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,14 +501,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>19.73</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -542,7 +542,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -569,14 +569,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>35.90</t>
+          <t>36.15</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -603,14 +603,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>18.48</t>
+          <t>18.82</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -637,14 +637,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>18.28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>20.42</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -705,14 +705,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>33.02</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>106.05</v>
+        <v>106.95</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -733,24 +733,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>104.15%</t>
+          <t>107.85%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>32.43</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>90.55</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -771,24 +771,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>98.18%</t>
+          <t>101.22%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>30.62</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.25</v>
+        <v>36.71</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -809,24 +809,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>131.03%</t>
+          <t>134.75%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.90%</t>
+          <t>10.76%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>29.67</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.46</v>
+        <v>15.59</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>54.60%</t>
+          <t>55.90%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32.68</t>
+          <t>32.95</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H617"/>
+  <dimension ref="A1:H628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22539,10 +22539,8 @@
           <t>nan%</t>
         </is>
       </c>
-      <c r="H607" t="inlineStr">
-        <is>
-          <t>17.98</t>
-        </is>
+      <c r="H607" t="n">
+        <v>17.98</v>
       </c>
     </row>
     <row r="608">
@@ -22573,11 +22571,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H608" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H608" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -22607,10 +22601,8 @@
           <t>nan%</t>
         </is>
       </c>
-      <c r="H609" t="inlineStr">
-        <is>
-          <t>35.90</t>
-        </is>
+      <c r="H609" t="n">
+        <v>35.9</v>
       </c>
     </row>
     <row r="610">
@@ -22641,10 +22633,8 @@
           <t>nan%</t>
         </is>
       </c>
-      <c r="H610" t="inlineStr">
-        <is>
-          <t>18.48</t>
-        </is>
+      <c r="H610" t="n">
+        <v>18.48</v>
       </c>
     </row>
     <row r="611">
@@ -22675,10 +22665,8 @@
           <t>nan%</t>
         </is>
       </c>
-      <c r="H611" t="inlineStr">
-        <is>
-          <t>18.18</t>
-        </is>
+      <c r="H611" t="n">
+        <v>18.18</v>
       </c>
     </row>
     <row r="612">
@@ -22709,10 +22697,8 @@
           <t>nan%</t>
         </is>
       </c>
-      <c r="H612" t="inlineStr">
-        <is>
-          <t>19.56</t>
-        </is>
+      <c r="H612" t="n">
+        <v>19.56</v>
       </c>
     </row>
     <row r="613">
@@ -22743,10 +22729,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H613" t="inlineStr">
-        <is>
-          <t>32.17</t>
-        </is>
+      <c r="H613" t="n">
+        <v>32.17</v>
       </c>
     </row>
     <row r="614">
@@ -22781,10 +22765,8 @@
           <t>1.51%</t>
         </is>
       </c>
-      <c r="H614" t="inlineStr">
-        <is>
-          <t>32.15</t>
-        </is>
+      <c r="H614" t="n">
+        <v>32.15</v>
       </c>
     </row>
     <row r="615">
@@ -22819,10 +22801,8 @@
           <t>3.53%</t>
         </is>
       </c>
-      <c r="H615" t="inlineStr">
-        <is>
-          <t>30.33</t>
-        </is>
+      <c r="H615" t="n">
+        <v>30.33</v>
       </c>
     </row>
     <row r="616">
@@ -22857,10 +22837,8 @@
           <t>10.90%</t>
         </is>
       </c>
-      <c r="H616" t="inlineStr">
-        <is>
-          <t>29.29</t>
-        </is>
+      <c r="H616" t="n">
+        <v>29.29</v>
       </c>
     </row>
     <row r="617">
@@ -22895,9 +22873,397 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H617" t="inlineStr">
-        <is>
-          <t>32.68</t>
+      <c r="H617" t="n">
+        <v>32.68</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr"/>
+      <c r="D618" t="inlineStr"/>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>19.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr"/>
+      <c r="D619" t="inlineStr"/>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr"/>
+      <c r="D620" t="inlineStr"/>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>36.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr"/>
+      <c r="D621" t="inlineStr"/>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>18.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr"/>
+      <c r="D622" t="inlineStr"/>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>18.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr"/>
+      <c r="D623" t="inlineStr"/>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>20.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr"/>
+      <c r="D624" t="inlineStr"/>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>33.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C625" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="D625" t="n">
+        <v>0</v>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>107.85%</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>1.50%</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>32.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C626" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="D626" t="n">
+        <v>0</v>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>101.22%</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>30.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C627" t="n">
+        <v>36.71</v>
+      </c>
+      <c r="D627" t="n">
+        <v>0</v>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>134.75%</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>10.76%</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>29.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C628" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="D628" t="n">
+        <v>0</v>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>55.90%</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>32.95</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,33 +482,37 @@
           <t>聯電(2303)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>129</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-1</v>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>221.98%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>19.73</t>
+          <t>19.58</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -516,16 +520,20 @@
           <t>友訊(2332)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>-2.45%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>15.36%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -542,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -550,33 +558,37 @@
           <t>佳世達(2352)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.15</v>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>-16.18%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>11.27%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>36.35</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,33 +596,37 @@
           <t>開發金(2883)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.1</v>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>3.36%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>128.22%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>2.95%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>19.45</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,33 +634,37 @@
           <t>玉山金(2884)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>23.13%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>3.52%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>18.75</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -652,33 +672,37 @@
           <t>兆豐金(2886)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>48.55</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.35</v>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>23.43%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>3.60%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.57</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -686,16 +710,20 @@
           <t>聯合再生(3576)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7</v>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>191.67%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -705,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>33.02</t>
+          <t>34.34</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -721,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>106.95</v>
+        <v>106.25</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -733,24 +761,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>107.85%</t>
+          <t>108.47%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>32.21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -759,7 +787,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>91.40000000000001</v>
+        <v>91</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -771,24 +799,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>101.22%</t>
+          <t>103.64%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.52%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>30.48</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -797,7 +825,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.71</v>
+        <v>35.9</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -809,24 +837,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>134.75%</t>
+          <t>130.08%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.76%</t>
+          <t>11.00%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -835,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.59</v>
+        <v>15.56</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -847,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>55.90%</t>
+          <t>55.60%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -857,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>32.89</t>
         </is>
       </c>
     </row>
@@ -872,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H628"/>
+  <dimension ref="A1:H639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22905,10 +22933,8 @@
           <t>nan%</t>
         </is>
       </c>
-      <c r="H618" t="inlineStr">
-        <is>
-          <t>19.73</t>
-        </is>
+      <c r="H618" t="n">
+        <v>19.73</v>
       </c>
     </row>
     <row r="619">
@@ -22939,11 +22965,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H619" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -22973,10 +22995,8 @@
           <t>nan%</t>
         </is>
       </c>
-      <c r="H620" t="inlineStr">
-        <is>
-          <t>36.15</t>
-        </is>
+      <c r="H620" t="n">
+        <v>36.15</v>
       </c>
     </row>
     <row r="621">
@@ -23007,10 +23027,8 @@
           <t>nan%</t>
         </is>
       </c>
-      <c r="H621" t="inlineStr">
-        <is>
-          <t>18.82</t>
-        </is>
+      <c r="H621" t="n">
+        <v>18.82</v>
       </c>
     </row>
     <row r="622">
@@ -23041,10 +23059,8 @@
           <t>nan%</t>
         </is>
       </c>
-      <c r="H622" t="inlineStr">
-        <is>
-          <t>18.28</t>
-        </is>
+      <c r="H622" t="n">
+        <v>18.28</v>
       </c>
     </row>
     <row r="623">
@@ -23075,10 +23091,8 @@
           <t>nan%</t>
         </is>
       </c>
-      <c r="H623" t="inlineStr">
-        <is>
-          <t>20.42</t>
-        </is>
+      <c r="H623" t="n">
+        <v>20.42</v>
       </c>
     </row>
     <row r="624">
@@ -23109,10 +23123,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H624" t="inlineStr">
-        <is>
-          <t>33.02</t>
-        </is>
+      <c r="H624" t="n">
+        <v>33.02</v>
       </c>
     </row>
     <row r="625">
@@ -23147,10 +23159,8 @@
           <t>1.50%</t>
         </is>
       </c>
-      <c r="H625" t="inlineStr">
-        <is>
-          <t>32.43</t>
-        </is>
+      <c r="H625" t="n">
+        <v>32.43</v>
       </c>
     </row>
     <row r="626">
@@ -23185,10 +23195,8 @@
           <t>3.50%</t>
         </is>
       </c>
-      <c r="H626" t="inlineStr">
-        <is>
-          <t>30.62</t>
-        </is>
+      <c r="H626" t="n">
+        <v>30.62</v>
       </c>
     </row>
     <row r="627">
@@ -23223,10 +23231,8 @@
           <t>10.76%</t>
         </is>
       </c>
-      <c r="H627" t="inlineStr">
-        <is>
-          <t>29.67</t>
-        </is>
+      <c r="H627" t="n">
+        <v>29.67</v>
       </c>
     </row>
     <row r="628">
@@ -23261,9 +23267,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H628" t="inlineStr">
-        <is>
-          <t>32.95</t>
+      <c r="H628" t="n">
+        <v>32.95</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C629" t="n">
+        <v>129</v>
+      </c>
+      <c r="D629" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>-0.77%</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>221.98%</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>2.02%</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>19.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C630" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="D630" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>-2.45%</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>15.36%</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C631" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="D631" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>0.53%</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>-16.18%</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>11.27%</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>36.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C632" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="D632" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>3.36%</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>128.22%</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>2.95%</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>19.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C633" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="D633" t="n">
+        <v>1</v>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>2.58%</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>23.13%</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>3.52%</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C634" t="n">
+        <v>48.55</v>
+      </c>
+      <c r="D634" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>0.73%</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>23.43%</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>3.60%</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>20.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C635" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D635" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>191.67%</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>34.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C636" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="D636" t="n">
+        <v>0</v>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>108.47%</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>1.51%</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>32.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C637" t="n">
+        <v>91</v>
+      </c>
+      <c r="D637" t="n">
+        <v>0</v>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>103.64%</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>3.52%</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>30.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C638" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="D638" t="n">
+        <v>0</v>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>130.08%</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>11.00%</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>29.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C639" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="D639" t="n">
+        <v>0</v>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>55.60%</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>32.89</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>129</v>
+        <v>132.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-1</v>
+        <v>3.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>221.98%</t>
+          <t>230.72%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>19.58</t>
+          <t>20.11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.9</v>
+        <v>19.85</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.5</v>
+        <v>-0.05</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.45%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>15.36%</t>
+          <t>15.07%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.35</v>
+        <v>28.4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.18%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-16.18%</t>
+          <t>-16.04%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.27%</t>
+          <t>11.25%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>36.41</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>33.85</v>
+        <v>34.95</v>
       </c>
       <c r="D5" t="n">
         <v>1.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.36%</t>
+          <t>3.25%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>128.22%</t>
+          <t>135.63%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.86%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>20.09</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>39.75</v>
+        <v>39.9</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.13%</t>
+          <t>23.60%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.51%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.82</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>48.55</v>
+        <v>48.5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.35</v>
+        <v>-0.05</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.43%</t>
+          <t>23.30%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.60%</t>
+          <t>3.61%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>20.55</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18.2</v>
+        <v>17.8</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7</v>
+        <v>-0.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>191.67%</t>
+          <t>185.26%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>34.34</t>
+          <t>33.58</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>106.25</v>
+        <v>108.45</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>108.47%</t>
+          <t>112.79%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>32.88</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>91</v>
+        <v>93.2</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>103.64%</t>
+          <t>108.56%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>31.22</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35.9</v>
+        <v>37.35</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.04%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>130.08%</t>
+          <t>139.38%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.00%</t>
+          <t>10.58%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>29.01</t>
+          <t>30.18</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.56</v>
+        <v>15.89</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>55.60%</t>
+          <t>58.90%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32.89</t>
+          <t>33.59</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H639"/>
+  <dimension ref="A1:H650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23303,10 +23303,8 @@
           <t>2.02%</t>
         </is>
       </c>
-      <c r="H629" t="inlineStr">
-        <is>
-          <t>19.58</t>
-        </is>
+      <c r="H629" t="n">
+        <v>19.58</v>
       </c>
     </row>
     <row r="630">
@@ -23341,11 +23339,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H630" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -23379,10 +23373,8 @@
           <t>11.27%</t>
         </is>
       </c>
-      <c r="H631" t="inlineStr">
-        <is>
-          <t>36.35</t>
-        </is>
+      <c r="H631" t="n">
+        <v>36.35</v>
       </c>
     </row>
     <row r="632">
@@ -23417,10 +23409,8 @@
           <t>2.95%</t>
         </is>
       </c>
-      <c r="H632" t="inlineStr">
-        <is>
-          <t>19.45</t>
-        </is>
+      <c r="H632" t="n">
+        <v>19.45</v>
       </c>
     </row>
     <row r="633">
@@ -23455,10 +23445,8 @@
           <t>3.52%</t>
         </is>
       </c>
-      <c r="H633" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
+      <c r="H633" t="n">
+        <v>18.75</v>
       </c>
     </row>
     <row r="634">
@@ -23493,10 +23481,8 @@
           <t>3.60%</t>
         </is>
       </c>
-      <c r="H634" t="inlineStr">
-        <is>
-          <t>20.57</t>
-        </is>
+      <c r="H634" t="n">
+        <v>20.57</v>
       </c>
     </row>
     <row r="635">
@@ -23531,10 +23517,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H635" t="inlineStr">
-        <is>
-          <t>34.34</t>
-        </is>
+      <c r="H635" t="n">
+        <v>34.34</v>
       </c>
     </row>
     <row r="636">
@@ -23569,10 +23553,8 @@
           <t>1.51%</t>
         </is>
       </c>
-      <c r="H636" t="inlineStr">
-        <is>
-          <t>32.21</t>
-        </is>
+      <c r="H636" t="n">
+        <v>32.21</v>
       </c>
     </row>
     <row r="637">
@@ -23607,10 +23589,8 @@
           <t>3.52%</t>
         </is>
       </c>
-      <c r="H637" t="inlineStr">
-        <is>
-          <t>30.48</t>
-        </is>
+      <c r="H637" t="n">
+        <v>30.48</v>
       </c>
     </row>
     <row r="638">
@@ -23645,10 +23625,8 @@
           <t>11.00%</t>
         </is>
       </c>
-      <c r="H638" t="inlineStr">
-        <is>
-          <t>29.01</t>
-        </is>
+      <c r="H638" t="n">
+        <v>29.01</v>
       </c>
     </row>
     <row r="639">
@@ -23683,9 +23661,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H639" t="inlineStr">
-        <is>
-          <t>32.89</t>
+      <c r="H639" t="n">
+        <v>32.89</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C640" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="D640" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>2.71%</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>230.72%</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>1.97%</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>20.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C641" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="D641" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>-0.25%</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>15.07%</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C642" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="D642" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>-16.04%</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>11.25%</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>36.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C643" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="D643" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>3.25%</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>135.63%</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>2.86%</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>20.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C644" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="D644" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>23.60%</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>3.51%</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>18.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C645" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="D645" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>23.30%</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>3.61%</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C646" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="D646" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>185.26%</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>33.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C647" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="D647" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>2.07%</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>112.79%</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>32.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C648" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="D648" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>2.42%</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>108.56%</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>31.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C649" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="D649" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>4.04%</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>139.38%</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>10.58%</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>30.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C650" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="D650" t="n">
+        <v>0</v>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>58.90%</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>33.59</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>132.5</v>
+        <v>126</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5</v>
+        <v>-6.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>-4.91%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>230.72%</t>
+          <t>213.34%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>19.12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.85</v>
+        <v>19.3</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.05</v>
+        <v>-0.55</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>15.07%</t>
+          <t>11.24%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.4</v>
+        <v>28.7</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-16.04%</t>
+          <t>-15.84%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.25%</t>
+          <t>11.13%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36.41</t>
+          <t>36.79</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34.95</v>
+        <v>35.5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1</v>
+        <v>0.55</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>135.63%</t>
+          <t>136.26%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>2.82%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.40</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>39.9</v>
+        <v>40.5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.60%</t>
+          <t>24.16%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.51%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>19.10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>48.5</v>
+        <v>49</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05</v>
+        <v>0.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.30%</t>
+          <t>23.67%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.61%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.76</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.8</v>
+        <v>17.3</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.81%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>185.26%</t>
+          <t>179.48%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>32.64</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>108.45</v>
+        <v>106.8</v>
       </c>
       <c r="D9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>112.79%</t>
+          <t>109.55%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>32.38</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>93.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>108.56%</t>
+          <t>105.52%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.48%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>30.79</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37.35</v>
+        <v>36.69</v>
       </c>
       <c r="D11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4.04%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>139.38%</t>
+          <t>135.68%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.58%</t>
+          <t>10.77%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30.18</t>
+          <t>29.65</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.89</v>
+        <v>15.65</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>58.90%</t>
+          <t>56.50%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.59</t>
+          <t>33.08</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H650"/>
+  <dimension ref="A1:H661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23697,10 +23697,8 @@
           <t>1.97%</t>
         </is>
       </c>
-      <c r="H640" t="inlineStr">
-        <is>
-          <t>20.11</t>
-        </is>
+      <c r="H640" t="n">
+        <v>20.11</v>
       </c>
     </row>
     <row r="641">
@@ -23735,11 +23733,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H641" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H641" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -23773,10 +23767,8 @@
           <t>11.25%</t>
         </is>
       </c>
-      <c r="H642" t="inlineStr">
-        <is>
-          <t>36.41</t>
-        </is>
+      <c r="H642" t="n">
+        <v>36.41</v>
       </c>
     </row>
     <row r="643">
@@ -23811,10 +23803,8 @@
           <t>2.86%</t>
         </is>
       </c>
-      <c r="H643" t="inlineStr">
-        <is>
-          <t>20.09</t>
-        </is>
+      <c r="H643" t="n">
+        <v>20.09</v>
       </c>
     </row>
     <row r="644">
@@ -23849,10 +23839,8 @@
           <t>3.51%</t>
         </is>
       </c>
-      <c r="H644" t="inlineStr">
-        <is>
-          <t>18.82</t>
-        </is>
+      <c r="H644" t="n">
+        <v>18.82</v>
       </c>
     </row>
     <row r="645">
@@ -23887,10 +23875,8 @@
           <t>3.61%</t>
         </is>
       </c>
-      <c r="H645" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
+      <c r="H645" t="n">
+        <v>20.55</v>
       </c>
     </row>
     <row r="646">
@@ -23925,10 +23911,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H646" t="inlineStr">
-        <is>
-          <t>33.58</t>
-        </is>
+      <c r="H646" t="n">
+        <v>33.58</v>
       </c>
     </row>
     <row r="647">
@@ -23963,10 +23947,8 @@
           <t>1.48%</t>
         </is>
       </c>
-      <c r="H647" t="inlineStr">
-        <is>
-          <t>32.88</t>
-        </is>
+      <c r="H647" t="n">
+        <v>32.88</v>
       </c>
     </row>
     <row r="648">
@@ -24001,10 +23983,8 @@
           <t>3.43%</t>
         </is>
       </c>
-      <c r="H648" t="inlineStr">
-        <is>
-          <t>31.22</t>
-        </is>
+      <c r="H648" t="n">
+        <v>31.22</v>
       </c>
     </row>
     <row r="649">
@@ -24039,10 +24019,8 @@
           <t>10.58%</t>
         </is>
       </c>
-      <c r="H649" t="inlineStr">
-        <is>
-          <t>30.18</t>
-        </is>
+      <c r="H649" t="n">
+        <v>30.18</v>
       </c>
     </row>
     <row r="650">
@@ -24077,9 +24055,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H650" t="inlineStr">
-        <is>
-          <t>33.59</t>
+      <c r="H650" t="n">
+        <v>33.59</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C651" t="n">
+        <v>126</v>
+      </c>
+      <c r="D651" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>-4.91%</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>213.34%</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>2.07%</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>19.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C652" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D652" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>-2.77%</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>11.24%</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C653" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="D653" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>1.06%</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>-15.84%</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>11.13%</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>36.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C654" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="D654" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>1.57%</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>136.26%</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>2.82%</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>20.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C655" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="D655" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>24.16%</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>3.46%</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>19.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C656" t="n">
+        <v>49</v>
+      </c>
+      <c r="D656" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>1.03%</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>23.67%</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>3.57%</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>20.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C657" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="D657" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>-2.81%</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>179.48%</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>32.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C658" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="D658" t="n">
+        <v>0</v>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>109.55%</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>1.50%</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>32.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C659" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="D659" t="n">
+        <v>0</v>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>105.52%</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>3.48%</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>30.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C660" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="D660" t="n">
+        <v>0</v>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>135.68%</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>10.77%</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>29.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C661" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="D661" t="n">
+        <v>0</v>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>56.50%</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>33.08</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D2" t="n">
-        <v>-6.5</v>
+        <v>-1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>213.34%</t>
+          <t>210.85%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>18.97</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.3</v>
+        <v>18.65</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.55</v>
+        <v>-0.65</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.77%</t>
+          <t>-3.37%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>11.24%</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-15.84%</t>
+          <t>-19.19%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.13%</t>
+          <t>11.21%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36.79</t>
+          <t>36.54</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>35.5</v>
+        <v>35.9</v>
       </c>
       <c r="D5" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>136.26%</t>
+          <t>142.83%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.79%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>20.40</t>
+          <t>20.63</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>40.5</v>
+        <v>43.2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>6.67%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.16%</t>
+          <t>32.64%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.24%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>19.10</t>
+          <t>20.38</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49</v>
+        <v>50.4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>2.86%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.67%</t>
+          <t>27.20%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>3.47%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>21.36</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.3</v>
+        <v>17.05</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-2.81%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>179.48%</t>
+          <t>177.69%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>32.17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>106.8</v>
+        <v>106.2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -761,24 +761,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>109.55%</t>
+          <t>108.57%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>32.20</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>91.90000000000001</v>
+        <v>91.05</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -799,24 +799,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>105.52%</t>
+          <t>103.40%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.51%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.79</t>
+          <t>30.50</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.69</v>
+        <v>36.23</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -837,24 +837,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>135.68%</t>
+          <t>130.77%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.77%</t>
+          <t>10.90%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.65</v>
+        <v>15.62</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>56.50%</t>
+          <t>56.20%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.08</t>
+          <t>33.02</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H661"/>
+  <dimension ref="A1:H672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24091,10 +24091,8 @@
           <t>2.07%</t>
         </is>
       </c>
-      <c r="H651" t="inlineStr">
-        <is>
-          <t>19.12</t>
-        </is>
+      <c r="H651" t="n">
+        <v>19.12</v>
       </c>
     </row>
     <row r="652">
@@ -24129,11 +24127,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H652" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H652" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -24167,10 +24161,8 @@
           <t>11.13%</t>
         </is>
       </c>
-      <c r="H653" t="inlineStr">
-        <is>
-          <t>36.79</t>
-        </is>
+      <c r="H653" t="n">
+        <v>36.79</v>
       </c>
     </row>
     <row r="654">
@@ -24205,10 +24197,8 @@
           <t>2.82%</t>
         </is>
       </c>
-      <c r="H654" t="inlineStr">
-        <is>
-          <t>20.40</t>
-        </is>
+      <c r="H654" t="n">
+        <v>20.4</v>
       </c>
     </row>
     <row r="655">
@@ -24243,10 +24233,8 @@
           <t>3.46%</t>
         </is>
       </c>
-      <c r="H655" t="inlineStr">
-        <is>
-          <t>19.10</t>
-        </is>
+      <c r="H655" t="n">
+        <v>19.1</v>
       </c>
     </row>
     <row r="656">
@@ -24281,10 +24269,8 @@
           <t>3.57%</t>
         </is>
       </c>
-      <c r="H656" t="inlineStr">
-        <is>
-          <t>20.76</t>
-        </is>
+      <c r="H656" t="n">
+        <v>20.76</v>
       </c>
     </row>
     <row r="657">
@@ -24319,10 +24305,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H657" t="inlineStr">
-        <is>
-          <t>32.64</t>
-        </is>
+      <c r="H657" t="n">
+        <v>32.64</v>
       </c>
     </row>
     <row r="658">
@@ -24357,10 +24341,8 @@
           <t>1.50%</t>
         </is>
       </c>
-      <c r="H658" t="inlineStr">
-        <is>
-          <t>32.38</t>
-        </is>
+      <c r="H658" t="n">
+        <v>32.38</v>
       </c>
     </row>
     <row r="659">
@@ -24395,10 +24377,8 @@
           <t>3.48%</t>
         </is>
       </c>
-      <c r="H659" t="inlineStr">
-        <is>
-          <t>30.79</t>
-        </is>
+      <c r="H659" t="n">
+        <v>30.79</v>
       </c>
     </row>
     <row r="660">
@@ -24433,10 +24413,8 @@
           <t>10.77%</t>
         </is>
       </c>
-      <c r="H660" t="inlineStr">
-        <is>
-          <t>29.65</t>
-        </is>
+      <c r="H660" t="n">
+        <v>29.65</v>
       </c>
     </row>
     <row r="661">
@@ -24471,9 +24449,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H661" t="inlineStr">
-        <is>
-          <t>33.08</t>
+      <c r="H661" t="n">
+        <v>33.08</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C662" t="n">
+        <v>125</v>
+      </c>
+      <c r="D662" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>-0.79%</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>210.85%</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>2.09%</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>18.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C663" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="D663" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>-3.37%</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>6.27%</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C664" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="D664" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>-19.19%</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>11.21%</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>36.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C665" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="D665" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>1.13%</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>142.83%</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>2.79%</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>20.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C666" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="D666" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>6.67%</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>32.64%</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>3.24%</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>20.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C667" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="D667" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>2.86%</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>27.20%</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>3.47%</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>21.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C668" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="D668" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>-1.45%</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>177.69%</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>32.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C669" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="D669" t="n">
+        <v>0</v>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>108.57%</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>1.51%</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>32.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C670" t="n">
+        <v>91.05</v>
+      </c>
+      <c r="D670" t="n">
+        <v>0</v>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>103.40%</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>3.51%</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>30.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C671" t="n">
+        <v>36.23</v>
+      </c>
+      <c r="D671" t="n">
+        <v>0</v>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>130.77%</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>10.90%</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>29.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C672" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="D672" t="n">
+        <v>0</v>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>56.20%</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>33.02</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D2" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>210.85%</t>
+          <t>214.82%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.73</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.65</v>
+        <v>19.55</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.65</v>
+        <v>0.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-3.37%</t>
+          <t>4.83%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>6.27%</t>
+          <t>11.40%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.5</v>
+        <v>29.25</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2</v>
+        <v>0.75</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>2.63%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-19.19%</t>
+          <t>-14.64%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.21%</t>
+          <t>10.92%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>37.50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>35.9</v>
+        <v>36.7</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>142.83%</t>
+          <t>148.24%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.72%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>21.09</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>43.2</v>
+        <v>43.55</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7</v>
+        <v>0.35</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6.67%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>32.64%</t>
+          <t>33.51%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>20.54</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50.4</v>
+        <v>49.55</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4</v>
+        <v>-0.85</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>-1.69%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>27.20%</t>
+          <t>25.05%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>3.53%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>21.00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.05</v>
+        <v>17.15</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.25</v>
+        <v>0.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>177.69%</t>
+          <t>174.84%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>32.36</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>106.2</v>
+        <v>107.9</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -761,24 +761,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>108.57%</t>
+          <t>110.49%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.20</t>
+          <t>32.71</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>91.05</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -799,24 +799,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>103.40%</t>
+          <t>105.79%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.51%</t>
+          <t>3.45%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.50</t>
+          <t>31.04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.23</v>
+        <v>36.8</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -837,24 +837,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>130.77%</t>
+          <t>134.27%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.90%</t>
+          <t>10.73%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>29.28</t>
+          <t>29.74</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.62</v>
+        <v>15.9</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>56.20%</t>
+          <t>59.00%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.02</t>
+          <t>33.61</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H672"/>
+  <dimension ref="A1:H683"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24485,10 +24485,8 @@
           <t>2.09%</t>
         </is>
       </c>
-      <c r="H662" t="inlineStr">
-        <is>
-          <t>18.97</t>
-        </is>
+      <c r="H662" t="n">
+        <v>18.97</v>
       </c>
     </row>
     <row r="663">
@@ -24523,11 +24521,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H663" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H663" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -24561,10 +24555,8 @@
           <t>11.21%</t>
         </is>
       </c>
-      <c r="H664" t="inlineStr">
-        <is>
-          <t>36.54</t>
-        </is>
+      <c r="H664" t="n">
+        <v>36.54</v>
       </c>
     </row>
     <row r="665">
@@ -24599,10 +24591,8 @@
           <t>2.79%</t>
         </is>
       </c>
-      <c r="H665" t="inlineStr">
-        <is>
-          <t>20.63</t>
-        </is>
+      <c r="H665" t="n">
+        <v>20.63</v>
       </c>
     </row>
     <row r="666">
@@ -24637,10 +24627,8 @@
           <t>3.24%</t>
         </is>
       </c>
-      <c r="H666" t="inlineStr">
-        <is>
-          <t>20.38</t>
-        </is>
+      <c r="H666" t="n">
+        <v>20.38</v>
       </c>
     </row>
     <row r="667">
@@ -24675,10 +24663,8 @@
           <t>3.47%</t>
         </is>
       </c>
-      <c r="H667" t="inlineStr">
-        <is>
-          <t>21.36</t>
-        </is>
+      <c r="H667" t="n">
+        <v>21.36</v>
       </c>
     </row>
     <row r="668">
@@ -24713,10 +24699,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H668" t="inlineStr">
-        <is>
-          <t>32.17</t>
-        </is>
+      <c r="H668" t="n">
+        <v>32.17</v>
       </c>
     </row>
     <row r="669">
@@ -24751,10 +24735,8 @@
           <t>1.51%</t>
         </is>
       </c>
-      <c r="H669" t="inlineStr">
-        <is>
-          <t>32.20</t>
-        </is>
+      <c r="H669" t="n">
+        <v>32.2</v>
       </c>
     </row>
     <row r="670">
@@ -24789,10 +24771,8 @@
           <t>3.51%</t>
         </is>
       </c>
-      <c r="H670" t="inlineStr">
-        <is>
-          <t>30.50</t>
-        </is>
+      <c r="H670" t="n">
+        <v>30.5</v>
       </c>
     </row>
     <row r="671">
@@ -24827,10 +24807,8 @@
           <t>10.90%</t>
         </is>
       </c>
-      <c r="H671" t="inlineStr">
-        <is>
-          <t>29.28</t>
-        </is>
+      <c r="H671" t="n">
+        <v>29.28</v>
       </c>
     </row>
     <row r="672">
@@ -24865,9 +24843,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H672" t="inlineStr">
-        <is>
-          <t>33.02</t>
+      <c r="H672" t="n">
+        <v>33.02</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C673" t="n">
+        <v>130</v>
+      </c>
+      <c r="D673" t="n">
+        <v>5</v>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>214.82%</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>2.01%</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>19.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C674" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="D674" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>4.83%</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>11.40%</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C675" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="D675" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>2.63%</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>-14.64%</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>10.92%</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>37.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C676" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="D676" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>148.24%</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>2.72%</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>21.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C677" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="D677" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>0.81%</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>33.51%</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>3.21%</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>20.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C678" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="D678" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>-1.69%</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>25.05%</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>3.53%</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C679" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="D679" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>0.59%</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>174.84%</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>32.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C680" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="D680" t="n">
+        <v>0</v>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>110.49%</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>32.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C681" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="D681" t="n">
+        <v>0</v>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>105.79%</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>31.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C682" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="D682" t="n">
+        <v>0</v>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>134.27%</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>10.73%</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>29.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C683" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="D683" t="n">
+        <v>0</v>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>59.00%</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>33.61</t>
         </is>
       </c>
     </row>
